--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T11:44:16+00:00</t>
+    <t>2026-07-15T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:32:02+00:00</t>
+    <t>2026-07-15T14:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:55:56+00:00</t>
+    <t>2026-07-16T09:23:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T06:35:14+00:00</t>
+    <t>2026-07-20T14:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:28:37+00:00</t>
+    <t>2026-07-21T08:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:19:16+00:00</t>
+    <t>2026-07-21T08:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:48:20+00:00</t>
+    <t>2026-07-21T09:53:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:53:07+00:00</t>
+    <t>2026-07-21T13:00:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:05+00:00</t>
+    <t>2026-07-27T06:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T06:31:56+00:00</t>
+    <t>2026-07-27T07:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:32:14+00:00</t>
+    <t>2026-07-27T07:43:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:43:34+00:00</t>
+    <t>2026-07-27T08:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T08:58:26+00:00</t>
+    <t>2026-07-27T09:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:29:06+00:00</t>
+    <t>2026-07-27T09:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:54:42+00:00</t>
+    <t>2026-07-27T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:14:55+00:00</t>
+    <t>2026-07-27T10:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:27:19+00:00</t>
+    <t>2026-07-27T10:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:49:55+00:00</t>
+    <t>2026-07-28T05:51:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T05:51:13+00:00</t>
+    <t>2026-07-28T06:19:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:19:15+00:00</t>
+    <t>2026-07-28T06:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:47:20+00:00</t>
+    <t>2026-07-28T13:00:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:00:26+00:00</t>
+    <t>2026-07-28T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:42:50+00:00</t>
+    <t>2026-07-28T14:03:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T14:03:46+00:00</t>
+    <t>2026-07-29T06:44:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T06:44:02+00:00</t>
+    <t>2026-07-29T11:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:08:45+00:00</t>
+    <t>2026-07-29T11:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:32:55+00:00</t>
+    <t>2026-07-29T11:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:56:42+00:00</t>
+    <t>2026-07-30T06:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T06:46:32+00:00</t>
+    <t>2026-07-30T07:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:01:31+00:00</t>
+    <t>2026-07-30T10:22:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:22:13+00:00</t>
+    <t>2026-07-31T07:01:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T07:01:03+00:00</t>
+    <t>2026-07-31T08:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:34:12+00:00</t>
+    <t>2026-07-31T10:47:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T10:47:24+00:00</t>
+    <t>2026-07-31T12:19:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:19:34+00:00</t>
+    <t>2026-08-03T09:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T09:14:34+00:00</t>
+    <t>2026-08-03T10:33:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -50580,7 +50580,7 @@
         <v>77</v>
       </c>
       <c r="H430" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I430" t="s" s="2">
         <v>23</v>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T10:33:06+00:00</t>
+    <t>2026-08-06T10:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8026,7 +8026,7 @@
         <v>77</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>23</v>
@@ -63344,7 +63344,7 @@
         <v>77</v>
       </c>
       <c r="H552" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I552" t="s" s="2">
         <v>23</v>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:46:09+00:00</t>
+    <t>2026-08-07T07:27:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:27:35+00:00</t>
+    <t>2026-08-10T07:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T07:07:45+00:00</t>
+    <t>2026-08-10T09:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T09:07:49+00:00</t>
+    <t>2026-08-10T10:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20594" uniqueCount="1244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20594" uniqueCount="1246">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T10:07:23+00:00</t>
+    <t>2026-08-12T14:05:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1134,7 +1134,7 @@
     <t>AllergyIntolerance.reaction.note</t>
   </si>
   <si>
-    <t>Freitext zur Diagnose für Zusatzinformation</t>
+    <t>Freitext zu Allergie und Intoleranzen als Zusatzinformation</t>
   </si>
   <si>
     <t>Additional text about the adverse reaction event not captured in other fields.</t>
@@ -2693,6 +2693,9 @@
     <t>Condition.note</t>
   </si>
   <si>
+    <t>Freitext zur Diagnose für Zusatzinformation</t>
+  </si>
+  <si>
     <t>Additional information about the Condition. This is a general notes/comments entry  for description of the Condition, its diagnosis and prognosis.</t>
   </si>
   <si>
@@ -3651,6 +3654,9 @@
   </si>
   <si>
     <t>Procedure.note</t>
+  </si>
+  <si>
+    <t>Freitext zur Prozedur für Zusatzinformation</t>
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
@@ -4708,7 +4714,7 @@
         <v>2</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
     </row>
     <row r="91">
@@ -4716,7 +4722,7 @@
         <v>4</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
     </row>
     <row r="92">
@@ -4732,7 +4738,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="94">
@@ -4830,7 +4836,7 @@
         <v>30</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="107">
@@ -4846,7 +4852,7 @@
         <v>34</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="109">
@@ -4867,26 +4873,26 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="114">
@@ -4902,7 +4908,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
     </row>
     <row r="116">
@@ -4910,7 +4916,7 @@
         <v>4</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
     </row>
     <row r="117">
@@ -4926,7 +4932,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
     </row>
     <row r="119">
@@ -4934,7 +4940,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="120">
@@ -4996,7 +5002,7 @@
         <v>24</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="128">
@@ -5032,7 +5038,7 @@
         <v>32</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
     </row>
     <row r="133">
@@ -5040,7 +5046,7 @@
         <v>34</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
     </row>
     <row r="134">
@@ -5072,7 +5078,7 @@
         <v>2</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="138">
@@ -5080,7 +5086,7 @@
         <v>4</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="139">
@@ -5096,7 +5102,7 @@
         <v>8</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="141">
@@ -5104,7 +5110,7 @@
         <v>10</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>1017</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="142">
@@ -5166,7 +5172,7 @@
         <v>24</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="150">
@@ -5202,7 +5208,7 @@
         <v>32</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="155">
@@ -5210,7 +5216,7 @@
         <v>34</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="156">
@@ -5242,7 +5248,7 @@
         <v>2</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="160">
@@ -5250,7 +5256,7 @@
         <v>4</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>1205</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="161">
@@ -5266,7 +5272,7 @@
         <v>8</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>1206</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="163">
@@ -5274,7 +5280,7 @@
         <v>10</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>1207</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="164">
@@ -5364,7 +5370,7 @@
         <v>30</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="176">
@@ -5380,7 +5386,7 @@
         <v>34</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="178">
@@ -5401,10 +5407,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>1208</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="181">
@@ -5420,7 +5426,7 @@
         <v>2</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="183">
@@ -5428,7 +5434,7 @@
         <v>4</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>1210</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="184">
@@ -5444,7 +5450,7 @@
         <v>8</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>1211</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="186">
@@ -5452,7 +5458,7 @@
         <v>10</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>1212</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="187">
@@ -5542,7 +5548,7 @@
         <v>30</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="199">
@@ -5550,7 +5556,7 @@
         <v>32</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>1213</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="200">
@@ -5558,7 +5564,7 @@
         <v>34</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1214</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="201">
@@ -5590,7 +5596,7 @@
         <v>2</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="205">
@@ -5598,7 +5604,7 @@
         <v>4</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>1241</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="206">
@@ -5614,7 +5620,7 @@
         <v>8</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>1242</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="208">
@@ -5712,7 +5718,7 @@
         <v>30</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="221">
@@ -5728,7 +5734,7 @@
         <v>34</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
     </row>
     <row r="223">
@@ -5749,10 +5755,10 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
   </sheetData>
@@ -55526,10 +55532,10 @@
         <v>301</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>355</v>
+        <v>859</v>
       </c>
       <c r="N477" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="O477" s="2"/>
       <c r="P477" s="2"/>
@@ -55600,10 +55606,10 @@
         <v>669</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -55703,10 +55709,10 @@
         <v>669</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -55808,10 +55814,10 @@
         <v>669</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" t="s" s="2">
@@ -55913,10 +55919,10 @@
         <v>669</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -56016,10 +56022,10 @@
         <v>669</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
@@ -56116,7 +56122,7 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B483" t="s" s="2">
         <v>188</v>
@@ -56219,13 +56225,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
@@ -56322,13 +56328,13 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
@@ -56425,16 +56431,16 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B486" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="C486" t="s" s="2">
         <v>876</v>
       </c>
-      <c r="C486" t="s" s="2">
-        <v>875</v>
-      </c>
       <c r="D486" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E486" t="s" s="2">
         <v>23</v>
@@ -56530,13 +56536,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -56633,13 +56639,13 @@
     </row>
     <row r="488">
       <c r="A488" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
@@ -56736,13 +56742,13 @@
     </row>
     <row r="489">
       <c r="A489" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
@@ -56768,13 +56774,13 @@
         <v>126</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N489" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="O489" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="P489" s="2"/>
       <c r="Q489" t="s" s="2">
@@ -56782,7 +56788,7 @@
       </c>
       <c r="R489" s="2"/>
       <c r="S489" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="T489" t="s" s="2">
         <v>23</v>
@@ -56824,7 +56830,7 @@
         <v>23</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>85</v>
@@ -56841,13 +56847,13 @@
     </row>
     <row r="490">
       <c r="A490" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
@@ -56870,13 +56876,13 @@
         <v>23</v>
       </c>
       <c r="L490" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="O490" s="2"/>
       <c r="P490" s="2"/>
@@ -56927,7 +56933,7 @@
         <v>23</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>77</v>
@@ -56944,16 +56950,16 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D491" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="E491" t="s" s="2">
         <v>23</v>
@@ -57049,13 +57055,13 @@
     </row>
     <row r="492">
       <c r="A492" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -57152,13 +57158,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -57255,13 +57261,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -57287,13 +57293,13 @@
         <v>126</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="O494" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="P494" s="2"/>
       <c r="Q494" t="s" s="2">
@@ -57301,7 +57307,7 @@
       </c>
       <c r="R494" s="2"/>
       <c r="S494" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="T494" t="s" s="2">
         <v>23</v>
@@ -57343,7 +57349,7 @@
         <v>23</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>85</v>
@@ -57360,13 +57366,13 @@
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -57392,10 +57398,10 @@
         <v>282</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N495" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="O495" s="2"/>
       <c r="P495" s="2"/>
@@ -57446,7 +57452,7 @@
         <v>23</v>
       </c>
       <c r="AG495" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="AH495" t="s" s="2">
         <v>77</v>
@@ -57463,16 +57469,16 @@
     </row>
     <row r="496">
       <c r="A496" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D496" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="E496" t="s" s="2">
         <v>23</v>
@@ -57568,13 +57574,13 @@
     </row>
     <row r="497">
       <c r="A497" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -57671,13 +57677,13 @@
     </row>
     <row r="498">
       <c r="A498" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -57774,13 +57780,13 @@
     </row>
     <row r="499">
       <c r="A499" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -57806,13 +57812,13 @@
         <v>126</v>
       </c>
       <c r="M499" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N499" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="O499" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="P499" s="2"/>
       <c r="Q499" t="s" s="2">
@@ -57820,7 +57826,7 @@
       </c>
       <c r="R499" s="2"/>
       <c r="S499" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="T499" t="s" s="2">
         <v>23</v>
@@ -57862,7 +57868,7 @@
         <v>23</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>85</v>
@@ -57879,13 +57885,13 @@
     </row>
     <row r="500">
       <c r="A500" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
@@ -57911,10 +57917,10 @@
         <v>99</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N500" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="O500" s="2"/>
       <c r="P500" s="2"/>
@@ -57965,7 +57971,7 @@
         <v>23</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>77</v>
@@ -57982,13 +57988,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
@@ -58014,13 +58020,13 @@
         <v>126</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="O501" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="P501" s="2"/>
       <c r="Q501" t="s" s="2">
@@ -58028,7 +58034,7 @@
       </c>
       <c r="R501" s="2"/>
       <c r="S501" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="T501" t="s" s="2">
         <v>23</v>
@@ -58070,7 +58076,7 @@
         <v>23</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>85</v>
@@ -58087,13 +58093,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
@@ -58116,13 +58122,13 @@
         <v>23</v>
       </c>
       <c r="L502" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="O502" s="2"/>
       <c r="P502" s="2"/>
@@ -58173,7 +58179,7 @@
         <v>23</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="AH502" t="s" s="2">
         <v>77</v>
@@ -58190,13 +58196,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -58276,7 +58282,7 @@
         <v>23</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>77</v>
@@ -58288,18 +58294,18 @@
         <v>23</v>
       </c>
       <c r="AK503" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -58398,13 +58404,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
@@ -58501,13 +58507,13 @@
     </row>
     <row r="506">
       <c r="A506" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
@@ -58606,13 +58612,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -58711,13 +58717,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -58816,13 +58822,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -58921,13 +58927,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -58956,7 +58962,7 @@
         <v>106</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="O510" t="s" s="2">
         <v>108</v>
@@ -59026,13 +59032,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59133,13 +59139,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -59165,10 +59171,10 @@
         <v>208</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="O512" s="2"/>
       <c r="P512" s="2"/>
@@ -59219,7 +59225,7 @@
         <v>23</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>77</v>
@@ -59236,13 +59242,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -59268,13 +59274,13 @@
         <v>165</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="O513" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="P513" s="2"/>
       <c r="Q513" t="s" s="2">
@@ -59304,7 +59310,7 @@
       </c>
       <c r="Z513" s="2"/>
       <c r="AA513" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="AB513" t="s" s="2">
         <v>23</v>
@@ -59322,7 +59328,7 @@
         <v>23</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>85</v>
@@ -59339,13 +59345,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -59371,23 +59377,23 @@
         <v>165</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="O514" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="P514" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="Q514" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R514" s="2"/>
       <c r="S514" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="T514" t="s" s="2">
         <v>23</v>
@@ -59408,10 +59414,10 @@
         <v>157</v>
       </c>
       <c r="Z514" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AA514" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="AB514" t="s" s="2">
         <v>23</v>
@@ -59429,7 +59435,7 @@
         <v>23</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="AH514" t="s" s="2">
         <v>85</v>
@@ -59446,13 +59452,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -59478,14 +59484,14 @@
         <v>99</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="O515" s="2"/>
       <c r="P515" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="Q515" t="s" s="2">
         <v>23</v>
@@ -59498,7 +59504,7 @@
         <v>23</v>
       </c>
       <c r="U515" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="V515" t="s" s="2">
         <v>23</v>
@@ -59534,7 +59540,7 @@
         <v>23</v>
       </c>
       <c r="AG515" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="AH515" t="s" s="2">
         <v>77</v>
@@ -59551,13 +59557,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -59583,16 +59589,16 @@
         <v>214</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="O516" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="P516" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="Q516" t="s" s="2">
         <v>23</v>
@@ -59621,7 +59627,7 @@
       </c>
       <c r="Z516" s="2"/>
       <c r="AA516" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="AB516" t="s" s="2">
         <v>23</v>
@@ -59639,7 +59645,7 @@
         <v>23</v>
       </c>
       <c r="AG516" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="AH516" t="s" s="2">
         <v>77</v>
@@ -59656,13 +59662,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -59688,16 +59694,16 @@
         <v>270</v>
       </c>
       <c r="M517" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="N517" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="O517" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="P517" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="Q517" t="s" s="2">
         <v>23</v>
@@ -59746,7 +59752,7 @@
         <v>23</v>
       </c>
       <c r="AG517" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>77</v>
@@ -59763,13 +59769,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -59795,10 +59801,10 @@
         <v>274</v>
       </c>
       <c r="M518" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="N518" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="O518" s="2"/>
       <c r="P518" s="2"/>
@@ -59849,7 +59855,7 @@
         <v>23</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>77</v>
@@ -59866,13 +59872,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -59898,16 +59904,16 @@
         <v>282</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="O519" t="s" s="2">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="P519" t="s" s="2">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="Q519" t="s" s="2">
         <v>23</v>
@@ -59956,7 +59962,7 @@
         <v>23</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>77</v>
@@ -59973,13 +59979,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60002,19 +60008,19 @@
         <v>86</v>
       </c>
       <c r="L520" t="s" s="2">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="O520" t="s" s="2">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="P520" t="s" s="2">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="Q520" t="s" s="2">
         <v>23</v>
@@ -60063,7 +60069,7 @@
         <v>23</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>77</v>
@@ -60080,13 +60086,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60112,16 +60118,16 @@
         <v>214</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="O521" t="s" s="2">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="P521" t="s" s="2">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="Q521" t="s" s="2">
         <v>23</v>
@@ -60149,10 +60155,10 @@
         <v>169</v>
       </c>
       <c r="Z521" t="s" s="2">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="AA521" t="s" s="2">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="AB521" t="s" s="2">
         <v>23</v>
@@ -60170,7 +60176,7 @@
         <v>23</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>77</v>
@@ -60187,13 +60193,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60219,10 +60225,10 @@
         <v>301</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="O522" s="2"/>
       <c r="P522" s="2"/>
@@ -60273,7 +60279,7 @@
         <v>23</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>77</v>
@@ -60290,13 +60296,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -60322,13 +60328,13 @@
         <v>306</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="O523" t="s" s="2">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="P523" s="2"/>
       <c r="Q523" t="s" s="2">
@@ -60378,7 +60384,7 @@
         <v>23</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>77</v>
@@ -60387,7 +60393,7 @@
         <v>78</v>
       </c>
       <c r="AJ523" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AK523" t="s" s="2">
         <v>97</v>
@@ -60395,13 +60401,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -60498,13 +60504,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -60603,13 +60609,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -60710,13 +60716,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -60742,16 +60748,16 @@
         <v>214</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="O527" t="s" s="2">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="P527" t="s" s="2">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="Q527" t="s" s="2">
         <v>23</v>
@@ -60780,7 +60786,7 @@
       </c>
       <c r="Z527" s="2"/>
       <c r="AA527" t="s" s="2">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="AB527" t="s" s="2">
         <v>23</v>
@@ -60798,7 +60804,7 @@
         <v>23</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>77</v>
@@ -60815,13 +60821,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -60847,68 +60853,68 @@
         <v>770</v>
       </c>
       <c r="M528" t="s" s="2">
+        <v>996</v>
+      </c>
+      <c r="N528" t="s" s="2">
+        <v>997</v>
+      </c>
+      <c r="O528" t="s" s="2">
+        <v>998</v>
+      </c>
+      <c r="P528" t="s" s="2">
+        <v>999</v>
+      </c>
+      <c r="Q528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R528" t="s" s="2">
+        <v>1000</v>
+      </c>
+      <c r="S528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF528" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG528" t="s" s="2">
         <v>995</v>
       </c>
-      <c r="N528" t="s" s="2">
-        <v>996</v>
-      </c>
-      <c r="O528" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="P528" t="s" s="2">
-        <v>998</v>
-      </c>
-      <c r="Q528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R528" t="s" s="2">
-        <v>999</v>
-      </c>
-      <c r="S528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF528" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG528" t="s" s="2">
-        <v>994</v>
-      </c>
       <c r="AH528" t="s" s="2">
         <v>77</v>
       </c>
@@ -60916,7 +60922,7 @@
         <v>85</v>
       </c>
       <c r="AJ528" t="s" s="2">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="AK528" t="s" s="2">
         <v>97</v>
@@ -60924,13 +60930,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -60956,14 +60962,14 @@
         <v>282</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="O529" s="2"/>
       <c r="P529" t="s" s="2">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="Q529" t="s" s="2">
         <v>23</v>
@@ -61012,7 +61018,7 @@
         <v>23</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>77</v>
@@ -61029,13 +61035,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -61061,10 +61067,10 @@
         <v>855</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="O530" s="2"/>
       <c r="P530" s="2"/>
@@ -61115,7 +61121,7 @@
         <v>23</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>85</v>
@@ -61132,13 +61138,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -61164,16 +61170,16 @@
         <v>214</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="O531" t="s" s="2">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="P531" t="s" s="2">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="Q531" t="s" s="2">
         <v>23</v>
@@ -61202,7 +61208,7 @@
       </c>
       <c r="Z531" s="2"/>
       <c r="AA531" t="s" s="2">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="AB531" t="s" s="2">
         <v>23</v>
@@ -61220,7 +61226,7 @@
         <v>23</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>77</v>
@@ -61229,7 +61235,7 @@
         <v>85</v>
       </c>
       <c r="AJ531" t="s" s="2">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="AK531" t="s" s="2">
         <v>97</v>
@@ -61237,13 +61243,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -61323,7 +61329,7 @@
         <v>23</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>77</v>
@@ -61335,18 +61341,18 @@
         <v>23</v>
       </c>
       <c r="AK532" t="s" s="2">
-        <v>1021</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -61445,13 +61451,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -61548,13 +61554,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -61651,13 +61657,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -61756,13 +61762,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -61861,13 +61867,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -61966,13 +61972,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62071,13 +62077,13 @@
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -62176,13 +62182,13 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -62281,13 +62287,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -62384,13 +62390,13 @@
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B543" t="s" s="2">
+        <v>1033</v>
+      </c>
+      <c r="C543" t="s" s="2">
         <v>1032</v>
-      </c>
-      <c r="C543" t="s" s="2">
-        <v>1031</v>
       </c>
       <c r="D543" t="s" s="2">
         <v>156</v>
@@ -62489,13 +62495,13 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
@@ -62594,13 +62600,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -62699,13 +62705,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
@@ -62804,13 +62810,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -62909,13 +62915,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63010,13 +63016,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B549" t="s" s="2">
+        <v>1039</v>
+      </c>
+      <c r="C549" t="s" s="2">
         <v>1038</v>
-      </c>
-      <c r="C549" t="s" s="2">
-        <v>1037</v>
       </c>
       <c r="D549" t="s" s="2">
         <v>192</v>
@@ -63115,13 +63121,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D550" t="s" s="2">
         <v>198</v>
@@ -63220,13 +63226,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -63327,13 +63333,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -63362,13 +63368,13 @@
         <v>697</v>
       </c>
       <c r="N552" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="O552" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="P552" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="Q552" t="s" s="2">
         <v>23</v>
@@ -63417,7 +63423,7 @@
         <v>23</v>
       </c>
       <c r="AG552" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="AH552" t="s" s="2">
         <v>77</v>
@@ -63434,13 +63440,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -63463,13 +63469,13 @@
         <v>86</v>
       </c>
       <c r="L553" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="M553" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="N553" t="s" s="2">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="O553" s="2"/>
       <c r="P553" s="2"/>
@@ -63520,7 +63526,7 @@
         <v>23</v>
       </c>
       <c r="AG553" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="AH553" t="s" s="2">
         <v>77</v>
@@ -63537,13 +63543,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -63569,13 +63575,13 @@
         <v>126</v>
       </c>
       <c r="M554" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="N554" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="O554" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="P554" s="2"/>
       <c r="Q554" t="s" s="2">
@@ -63625,7 +63631,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>77</v>
@@ -63642,17 +63648,17 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="F555" s="2"/>
       <c r="G555" t="s" s="2">
@@ -63671,13 +63677,13 @@
         <v>86</v>
       </c>
       <c r="L555" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="M555" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="N555" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -63728,7 +63734,7 @@
         <v>23</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>77</v>
@@ -63745,17 +63751,17 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="F556" s="2"/>
       <c r="G556" t="s" s="2">
@@ -63774,16 +63780,16 @@
         <v>86</v>
       </c>
       <c r="L556" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="M556" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="N556" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="O556" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="P556" s="2"/>
       <c r="Q556" t="s" s="2">
@@ -63833,7 +63839,7 @@
         <v>23</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>77</v>
@@ -63850,13 +63856,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -63882,13 +63888,13 @@
         <v>165</v>
       </c>
       <c r="M557" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="O557" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="P557" s="2"/>
       <c r="Q557" t="s" s="2">
@@ -63918,7 +63924,7 @@
       </c>
       <c r="Z557" s="2"/>
       <c r="AA557" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="AB557" t="s" s="2">
         <v>23</v>
@@ -63936,7 +63942,7 @@
         <v>23</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>85</v>
@@ -63953,17 +63959,17 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="F558" s="2"/>
       <c r="G558" t="s" s="2">
@@ -63985,13 +63991,13 @@
         <v>214</v>
       </c>
       <c r="M558" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="N558" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="O558" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="P558" s="2"/>
       <c r="Q558" t="s" s="2">
@@ -64020,10 +64026,10 @@
         <v>150</v>
       </c>
       <c r="Z558" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="AA558" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="AB558" t="s" s="2">
         <v>23</v>
@@ -64041,7 +64047,7 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>77</v>
@@ -64058,13 +64064,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -64090,10 +64096,10 @@
         <v>214</v>
       </c>
       <c r="M559" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="N559" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="O559" s="2"/>
       <c r="P559" s="2"/>
@@ -64123,10 +64129,10 @@
         <v>150</v>
       </c>
       <c r="Z559" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AA559" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="AB559" t="s" s="2">
         <v>23</v>
@@ -64144,7 +64150,7 @@
         <v>23</v>
       </c>
       <c r="AG559" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="AH559" t="s" s="2">
         <v>77</v>
@@ -64161,13 +64167,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -64193,10 +64199,10 @@
         <v>214</v>
       </c>
       <c r="M560" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="N560" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="O560" s="2"/>
       <c r="P560" t="s" s="2">
@@ -64229,7 +64235,7 @@
       </c>
       <c r="Z560" s="2"/>
       <c r="AA560" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="AB560" t="s" s="2">
         <v>23</v>
@@ -64247,7 +64253,7 @@
         <v>23</v>
       </c>
       <c r="AG560" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="AH560" t="s" s="2">
         <v>77</v>
@@ -64264,13 +64270,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -64367,13 +64373,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -64472,13 +64478,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -64579,13 +64585,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D564" s="2"/>
       <c r="E564" t="s" s="2">
@@ -64686,13 +64692,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D565" s="2"/>
       <c r="E565" t="s" s="2">
@@ -64718,10 +64724,10 @@
         <v>270</v>
       </c>
       <c r="M565" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="N565" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="O565" s="2"/>
       <c r="P565" s="2"/>
@@ -64772,7 +64778,7 @@
         <v>23</v>
       </c>
       <c r="AG565" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AH565" t="s" s="2">
         <v>85</v>
@@ -64789,13 +64795,13 @@
     </row>
     <row r="566">
       <c r="A566" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" t="s" s="2">
@@ -64824,10 +64830,10 @@
         <v>275</v>
       </c>
       <c r="N566" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="O566" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="P566" s="2"/>
       <c r="Q566" t="s" s="2">
@@ -64877,7 +64883,7 @@
         <v>23</v>
       </c>
       <c r="AG566" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="AH566" t="s" s="2">
         <v>77</v>
@@ -64894,13 +64900,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="D567" s="2"/>
       <c r="E567" t="s" s="2">
@@ -64926,13 +64932,13 @@
         <v>282</v>
       </c>
       <c r="M567" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="N567" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="O567" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="P567" s="2"/>
       <c r="Q567" t="s" s="2">
@@ -64982,7 +64988,7 @@
         <v>23</v>
       </c>
       <c r="AG567" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="AH567" t="s" s="2">
         <v>77</v>
@@ -64999,13 +65005,13 @@
     </row>
     <row r="568">
       <c r="A568" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="D568" s="2"/>
       <c r="E568" t="s" s="2">
@@ -65031,7 +65037,7 @@
         <v>287</v>
       </c>
       <c r="M568" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="N568" t="s" s="2">
         <v>289</v>
@@ -65085,7 +65091,7 @@
         <v>23</v>
       </c>
       <c r="AG568" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="AH568" t="s" s="2">
         <v>77</v>
@@ -65102,13 +65108,13 @@
     </row>
     <row r="569">
       <c r="A569" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="D569" s="2"/>
       <c r="E569" t="s" s="2">
@@ -65134,10 +65140,10 @@
         <v>292</v>
       </c>
       <c r="M569" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="N569" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="O569" s="2"/>
       <c r="P569" s="2"/>
@@ -65188,7 +65194,7 @@
         <v>23</v>
       </c>
       <c r="AG569" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AH569" t="s" s="2">
         <v>77</v>
@@ -65205,13 +65211,13 @@
     </row>
     <row r="570">
       <c r="A570" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="D570" s="2"/>
       <c r="E570" t="s" s="2">
@@ -65237,10 +65243,10 @@
         <v>306</v>
       </c>
       <c r="M570" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="N570" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="O570" s="2"/>
       <c r="P570" s="2"/>
@@ -65291,7 +65297,7 @@
         <v>23</v>
       </c>
       <c r="AG570" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="AH570" t="s" s="2">
         <v>77</v>
@@ -65308,13 +65314,13 @@
     </row>
     <row r="571">
       <c r="A571" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="C571" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="D571" s="2"/>
       <c r="E571" t="s" s="2">
@@ -65411,13 +65417,13 @@
     </row>
     <row r="572">
       <c r="A572" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C572" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="D572" s="2"/>
       <c r="E572" t="s" s="2">
@@ -65516,13 +65522,13 @@
     </row>
     <row r="573">
       <c r="A573" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C573" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D573" s="2"/>
       <c r="E573" t="s" s="2">
@@ -65623,13 +65629,13 @@
     </row>
     <row r="574">
       <c r="A574" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B574" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C574" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="D574" s="2"/>
       <c r="E574" t="s" s="2">
@@ -65655,14 +65661,14 @@
         <v>214</v>
       </c>
       <c r="M574" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="N574" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="O574" s="2"/>
       <c r="P574" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="Q574" t="s" s="2">
         <v>23</v>
@@ -65690,10 +65696,10 @@
         <v>150</v>
       </c>
       <c r="Z574" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="AA574" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="AB574" t="s" s="2">
         <v>23</v>
@@ -65711,7 +65717,7 @@
         <v>23</v>
       </c>
       <c r="AG574" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="AH574" t="s" s="2">
         <v>77</v>
@@ -65728,13 +65734,13 @@
     </row>
     <row r="575">
       <c r="A575" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B575" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C575" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D575" s="2"/>
       <c r="E575" t="s" s="2">
@@ -65757,17 +65763,17 @@
         <v>86</v>
       </c>
       <c r="L575" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="M575" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="N575" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="O575" s="2"/>
       <c r="P575" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="Q575" t="s" s="2">
         <v>23</v>
@@ -65816,7 +65822,7 @@
         <v>23</v>
       </c>
       <c r="AG575" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="AH575" t="s" s="2">
         <v>85</v>
@@ -65833,13 +65839,13 @@
     </row>
     <row r="576">
       <c r="A576" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B576" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C576" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D576" s="2"/>
       <c r="E576" t="s" s="2">
@@ -65862,17 +65868,17 @@
         <v>23</v>
       </c>
       <c r="L576" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="M576" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="N576" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="O576" s="2"/>
       <c r="P576" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="Q576" t="s" s="2">
         <v>23</v>
@@ -65921,7 +65927,7 @@
         <v>23</v>
       </c>
       <c r="AG576" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="AH576" t="s" s="2">
         <v>77</v>
@@ -65938,13 +65944,13 @@
     </row>
     <row r="577">
       <c r="A577" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B577" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C577" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="D577" s="2"/>
       <c r="E577" t="s" s="2">
@@ -65967,17 +65973,17 @@
         <v>86</v>
       </c>
       <c r="L577" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="M577" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="N577" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="O577" s="2"/>
       <c r="P577" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="Q577" t="s" s="2">
         <v>23</v>
@@ -66026,7 +66032,7 @@
         <v>23</v>
       </c>
       <c r="AG577" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="AH577" t="s" s="2">
         <v>77</v>
@@ -66043,13 +66049,13 @@
     </row>
     <row r="578">
       <c r="A578" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B578" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C578" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D578" s="2"/>
       <c r="E578" t="s" s="2">
@@ -66075,13 +66081,13 @@
         <v>214</v>
       </c>
       <c r="M578" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="N578" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="O578" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="P578" s="2"/>
       <c r="Q578" t="s" s="2">
@@ -66110,10 +66116,10 @@
         <v>150</v>
       </c>
       <c r="Z578" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="AA578" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="AB578" t="s" s="2">
         <v>23</v>
@@ -66131,7 +66137,7 @@
         <v>23</v>
       </c>
       <c r="AG578" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="AH578" t="s" s="2">
         <v>77</v>
@@ -66148,13 +66154,13 @@
     </row>
     <row r="579">
       <c r="A579" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B579" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C579" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D579" s="2"/>
       <c r="E579" t="s" s="2">
@@ -66177,16 +66183,16 @@
         <v>86</v>
       </c>
       <c r="L579" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="M579" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="N579" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="O579" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="P579" s="2"/>
       <c r="Q579" t="s" s="2">
@@ -66236,7 +66242,7 @@
         <v>23</v>
       </c>
       <c r="AG579" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="AH579" t="s" s="2">
         <v>77</v>
@@ -66253,13 +66259,13 @@
     </row>
     <row r="580">
       <c r="A580" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C580" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D580" s="2"/>
       <c r="E580" t="s" s="2">
@@ -66285,13 +66291,13 @@
         <v>214</v>
       </c>
       <c r="M580" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="N580" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="O580" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="P580" s="2"/>
       <c r="Q580" t="s" s="2">
@@ -66341,7 +66347,7 @@
         <v>23</v>
       </c>
       <c r="AG580" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="AH580" t="s" s="2">
         <v>77</v>
@@ -66358,13 +66364,13 @@
     </row>
     <row r="581">
       <c r="A581" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B581" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C581" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D581" s="2"/>
       <c r="E581" t="s" s="2">
@@ -66390,13 +66396,13 @@
         <v>214</v>
       </c>
       <c r="M581" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="N581" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="O581" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="P581" s="2"/>
       <c r="Q581" t="s" s="2">
@@ -66425,10 +66431,10 @@
         <v>150</v>
       </c>
       <c r="Z581" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="AA581" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="AB581" t="s" s="2">
         <v>23</v>
@@ -66446,7 +66452,7 @@
         <v>23</v>
       </c>
       <c r="AG581" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="AH581" t="s" s="2">
         <v>77</v>
@@ -66463,13 +66469,13 @@
     </row>
     <row r="582">
       <c r="A582" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B582" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C582" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D582" s="2"/>
       <c r="E582" t="s" s="2">
@@ -66492,16 +66498,16 @@
         <v>23</v>
       </c>
       <c r="L582" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="M582" t="s" s="2">
         <v>841</v>
       </c>
       <c r="N582" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="O582" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="P582" s="2"/>
       <c r="Q582" t="s" s="2">
@@ -66551,7 +66557,7 @@
         <v>23</v>
       </c>
       <c r="AG582" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="AH582" t="s" s="2">
         <v>77</v>
@@ -66568,13 +66574,13 @@
     </row>
     <row r="583">
       <c r="A583" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B583" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="C583" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="D583" s="2"/>
       <c r="E583" t="s" s="2">
@@ -66600,13 +66606,13 @@
         <v>214</v>
       </c>
       <c r="M583" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="N583" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="O583" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="P583" s="2"/>
       <c r="Q583" t="s" s="2">
@@ -66635,7 +66641,7 @@
         <v>150</v>
       </c>
       <c r="Z583" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="AA583" t="s" s="2">
         <v>730</v>
@@ -66656,7 +66662,7 @@
         <v>23</v>
       </c>
       <c r="AG583" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="AH583" t="s" s="2">
         <v>77</v>
@@ -66673,13 +66679,13 @@
     </row>
     <row r="584">
       <c r="A584" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B584" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C584" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D584" s="2"/>
       <c r="E584" t="s" s="2">
@@ -66702,17 +66708,17 @@
         <v>23</v>
       </c>
       <c r="L584" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="M584" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="N584" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="O584" s="2"/>
       <c r="P584" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="Q584" t="s" s="2">
         <v>23</v>
@@ -66761,7 +66767,7 @@
         <v>23</v>
       </c>
       <c r="AG584" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="AH584" t="s" s="2">
         <v>77</v>
@@ -66778,13 +66784,13 @@
     </row>
     <row r="585">
       <c r="A585" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B585" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="C585" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="D585" s="2"/>
       <c r="E585" t="s" s="2">
@@ -66810,10 +66816,10 @@
         <v>214</v>
       </c>
       <c r="M585" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="N585" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="O585" s="2"/>
       <c r="P585" s="2"/>
@@ -66843,10 +66849,10 @@
         <v>150</v>
       </c>
       <c r="Z585" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="AA585" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="AB585" t="s" s="2">
         <v>23</v>
@@ -66864,7 +66870,7 @@
         <v>23</v>
       </c>
       <c r="AG585" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="AH585" t="s" s="2">
         <v>77</v>
@@ -66881,13 +66887,13 @@
     </row>
     <row r="586">
       <c r="A586" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B586" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="C586" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="D586" s="2"/>
       <c r="E586" t="s" s="2">
@@ -66913,10 +66919,10 @@
         <v>301</v>
       </c>
       <c r="M586" t="s" s="2">
-        <v>355</v>
+        <v>1173</v>
       </c>
       <c r="N586" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="O586" s="2"/>
       <c r="P586" s="2"/>
@@ -66967,7 +66973,7 @@
         <v>23</v>
       </c>
       <c r="AG586" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="AH586" t="s" s="2">
         <v>77</v>
@@ -66984,13 +66990,13 @@
     </row>
     <row r="587">
       <c r="A587" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B587" t="s" s="2">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="C587" t="s" s="2">
-        <v>1173</v>
+        <v>1175</v>
       </c>
       <c r="D587" s="2"/>
       <c r="E587" t="s" s="2">
@@ -67087,13 +67093,13 @@
     </row>
     <row r="588">
       <c r="A588" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B588" t="s" s="2">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="C588" t="s" s="2">
-        <v>1174</v>
+        <v>1176</v>
       </c>
       <c r="D588" s="2"/>
       <c r="E588" t="s" s="2">
@@ -67192,13 +67198,13 @@
     </row>
     <row r="589">
       <c r="A589" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B589" t="s" s="2">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="C589" t="s" s="2">
-        <v>1175</v>
+        <v>1177</v>
       </c>
       <c r="D589" s="2"/>
       <c r="E589" t="s" s="2">
@@ -67297,13 +67303,13 @@
     </row>
     <row r="590">
       <c r="A590" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B590" t="s" s="2">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="C590" t="s" s="2">
-        <v>1176</v>
+        <v>1178</v>
       </c>
       <c r="D590" s="2"/>
       <c r="E590" t="s" s="2">
@@ -67400,13 +67406,13 @@
     </row>
     <row r="591">
       <c r="A591" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B591" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="C591" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D591" s="2"/>
       <c r="E591" t="s" s="2">
@@ -67503,13 +67509,13 @@
     </row>
     <row r="592">
       <c r="A592" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B592" t="s" s="2">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="C592" t="s" s="2">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="D592" s="2"/>
       <c r="E592" t="s" s="2">
@@ -67535,10 +67541,10 @@
         <v>306</v>
       </c>
       <c r="M592" t="s" s="2">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="N592" t="s" s="2">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="O592" s="2"/>
       <c r="P592" s="2"/>
@@ -67589,7 +67595,7 @@
         <v>23</v>
       </c>
       <c r="AG592" t="s" s="2">
-        <v>1178</v>
+        <v>1180</v>
       </c>
       <c r="AH592" t="s" s="2">
         <v>77</v>
@@ -67606,13 +67612,13 @@
     </row>
     <row r="593">
       <c r="A593" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B593" t="s" s="2">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C593" t="s" s="2">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="D593" s="2"/>
       <c r="E593" t="s" s="2">
@@ -67709,13 +67715,13 @@
     </row>
     <row r="594">
       <c r="A594" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B594" t="s" s="2">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="C594" t="s" s="2">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="D594" s="2"/>
       <c r="E594" t="s" s="2">
@@ -67814,13 +67820,13 @@
     </row>
     <row r="595">
       <c r="A595" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B595" t="s" s="2">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C595" t="s" s="2">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="D595" s="2"/>
       <c r="E595" t="s" s="2">
@@ -67921,13 +67927,13 @@
     </row>
     <row r="596">
       <c r="A596" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B596" t="s" s="2">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="C596" t="s" s="2">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D596" s="2"/>
       <c r="E596" t="s" s="2">
@@ -67953,10 +67959,10 @@
         <v>214</v>
       </c>
       <c r="M596" t="s" s="2">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="N596" t="s" s="2">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="O596" s="2"/>
       <c r="P596" s="2"/>
@@ -67986,10 +67992,10 @@
         <v>169</v>
       </c>
       <c r="Z596" t="s" s="2">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="AA596" t="s" s="2">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="AB596" t="s" s="2">
         <v>23</v>
@@ -68007,7 +68013,7 @@
         <v>23</v>
       </c>
       <c r="AG596" t="s" s="2">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="AH596" t="s" s="2">
         <v>77</v>
@@ -68024,13 +68030,13 @@
     </row>
     <row r="597">
       <c r="A597" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B597" t="s" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C597" t="s" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D597" s="2"/>
       <c r="E597" t="s" s="2">
@@ -68053,13 +68059,13 @@
         <v>23</v>
       </c>
       <c r="L597" t="s" s="2">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="M597" t="s" s="2">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="N597" t="s" s="2">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="O597" s="2"/>
       <c r="P597" s="2"/>
@@ -68110,7 +68116,7 @@
         <v>23</v>
       </c>
       <c r="AG597" t="s" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="AH597" t="s" s="2">
         <v>85</v>
@@ -68127,13 +68133,13 @@
     </row>
     <row r="598">
       <c r="A598" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B598" t="s" s="2">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="C598" t="s" s="2">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D598" s="2"/>
       <c r="E598" t="s" s="2">
@@ -68156,19 +68162,19 @@
         <v>23</v>
       </c>
       <c r="L598" t="s" s="2">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="M598" t="s" s="2">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="N598" t="s" s="2">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="O598" t="s" s="2">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="P598" t="s" s="2">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="Q598" t="s" s="2">
         <v>23</v>
@@ -68217,7 +68223,7 @@
         <v>23</v>
       </c>
       <c r="AG598" t="s" s="2">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="AH598" t="s" s="2">
         <v>77</v>
@@ -68234,13 +68240,13 @@
     </row>
     <row r="599">
       <c r="A599" t="s" s="2">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B599" t="s" s="2">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C599" t="s" s="2">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="D599" s="2"/>
       <c r="E599" t="s" s="2">
@@ -68266,13 +68272,13 @@
         <v>214</v>
       </c>
       <c r="M599" t="s" s="2">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="N599" t="s" s="2">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="O599" t="s" s="2">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="P599" s="2"/>
       <c r="Q599" t="s" s="2">
@@ -68301,10 +68307,10 @@
         <v>150</v>
       </c>
       <c r="Z599" t="s" s="2">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="AA599" t="s" s="2">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="AB599" t="s" s="2">
         <v>23</v>
@@ -68322,7 +68328,7 @@
         <v>23</v>
       </c>
       <c r="AG599" t="s" s="2">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="AH599" t="s" s="2">
         <v>77</v>
@@ -68339,7 +68345,7 @@
     </row>
     <row r="600">
       <c r="A600" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B600" t="s" s="2">
         <v>188</v>
@@ -68371,7 +68377,7 @@
         <v>79</v>
       </c>
       <c r="M600" t="s" s="2">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="N600" t="s" s="2">
         <v>315</v>
@@ -68442,13 +68448,13 @@
     </row>
     <row r="601">
       <c r="A601" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B601" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C601" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D601" s="2"/>
       <c r="E601" t="s" s="2">
@@ -68545,13 +68551,13 @@
     </row>
     <row r="602">
       <c r="A602" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B602" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C602" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D602" s="2"/>
       <c r="E602" t="s" s="2">
@@ -68648,13 +68654,13 @@
     </row>
     <row r="603">
       <c r="A603" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B603" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C603" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D603" s="2"/>
       <c r="E603" t="s" s="2">
@@ -68680,13 +68686,13 @@
         <v>126</v>
       </c>
       <c r="M603" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N603" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="O603" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="P603" s="2"/>
       <c r="Q603" t="s" s="2">
@@ -68694,7 +68700,7 @@
       </c>
       <c r="R603" s="2"/>
       <c r="S603" t="s" s="2">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="T603" t="s" s="2">
         <v>23</v>
@@ -68736,7 +68742,7 @@
         <v>23</v>
       </c>
       <c r="AG603" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AH603" t="s" s="2">
         <v>85</v>
@@ -68753,13 +68759,13 @@
     </row>
     <row r="604">
       <c r="A604" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="B604" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C604" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D604" s="2"/>
       <c r="E604" t="s" s="2">
@@ -68785,10 +68791,10 @@
         <v>214</v>
       </c>
       <c r="M604" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N604" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="O604" s="2"/>
       <c r="P604" s="2"/>
@@ -68839,7 +68845,7 @@
         <v>23</v>
       </c>
       <c r="AG604" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="AH604" t="s" s="2">
         <v>77</v>
@@ -68856,13 +68862,13 @@
     </row>
     <row r="605">
       <c r="A605" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B605" t="s" s="2">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="C605" t="s" s="2">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D605" s="2"/>
       <c r="E605" t="s" s="2">
@@ -68888,13 +68894,13 @@
         <v>79</v>
       </c>
       <c r="M605" t="s" s="2">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="N605" t="s" s="2">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="O605" t="s" s="2">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="P605" s="2"/>
       <c r="Q605" t="s" s="2">
@@ -68944,7 +68950,7 @@
         <v>23</v>
       </c>
       <c r="AG605" t="s" s="2">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="AH605" t="s" s="2">
         <v>77</v>
@@ -68956,18 +68962,18 @@
         <v>196</v>
       </c>
       <c r="AK605" t="s" s="2">
-        <v>1218</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B606" t="s" s="2">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C606" t="s" s="2">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D606" s="2"/>
       <c r="E606" t="s" s="2">
@@ -69064,13 +69070,13 @@
     </row>
     <row r="607">
       <c r="A607" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B607" t="s" s="2">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="C607" t="s" s="2">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="D607" s="2"/>
       <c r="E607" t="s" s="2">
@@ -69169,13 +69175,13 @@
     </row>
     <row r="608">
       <c r="A608" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B608" t="s" s="2">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="C608" t="s" s="2">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="D608" s="2"/>
       <c r="E608" t="s" s="2">
@@ -69201,13 +69207,13 @@
         <v>99</v>
       </c>
       <c r="M608" t="s" s="2">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="N608" t="s" s="2">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="O608" t="s" s="2">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="P608" s="2"/>
       <c r="Q608" t="s" s="2">
@@ -69257,7 +69263,7 @@
         <v>23</v>
       </c>
       <c r="AG608" t="s" s="2">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="AH608" t="s" s="2">
         <v>77</v>
@@ -69266,7 +69272,7 @@
         <v>85</v>
       </c>
       <c r="AJ608" t="s" s="2">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="AK608" t="s" s="2">
         <v>97</v>
@@ -69274,13 +69280,13 @@
     </row>
     <row r="609">
       <c r="A609" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B609" t="s" s="2">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="C609" t="s" s="2">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="D609" s="2"/>
       <c r="E609" t="s" s="2">
@@ -69306,13 +69312,13 @@
         <v>126</v>
       </c>
       <c r="M609" t="s" s="2">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="N609" t="s" s="2">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="O609" t="s" s="2">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="P609" s="2"/>
       <c r="Q609" t="s" s="2">
@@ -69341,10 +69347,10 @@
         <v>142</v>
       </c>
       <c r="Z609" t="s" s="2">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="AA609" t="s" s="2">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="AB609" t="s" s="2">
         <v>23</v>
@@ -69362,7 +69368,7 @@
         <v>23</v>
       </c>
       <c r="AG609" t="s" s="2">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="AH609" t="s" s="2">
         <v>77</v>
@@ -69379,13 +69385,13 @@
     </row>
     <row r="610">
       <c r="A610" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B610" t="s" s="2">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="C610" t="s" s="2">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D610" s="2"/>
       <c r="E610" t="s" s="2">
@@ -69411,13 +69417,13 @@
         <v>208</v>
       </c>
       <c r="M610" t="s" s="2">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="N610" t="s" s="2">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="O610" t="s" s="2">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="P610" s="2"/>
       <c r="Q610" t="s" s="2">
@@ -69467,7 +69473,7 @@
         <v>23</v>
       </c>
       <c r="AG610" t="s" s="2">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="AH610" t="s" s="2">
         <v>77</v>
@@ -69484,13 +69490,13 @@
     </row>
     <row r="611">
       <c r="A611" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="B611" t="s" s="2">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="C611" t="s" s="2">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="D611" s="2"/>
       <c r="E611" t="s" s="2">
@@ -69516,13 +69522,13 @@
         <v>99</v>
       </c>
       <c r="M611" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="N611" t="s" s="2">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="O611" t="s" s="2">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="P611" s="2"/>
       <c r="Q611" t="s" s="2">
@@ -69572,7 +69578,7 @@
         <v>23</v>
       </c>
       <c r="AG611" t="s" s="2">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="AH611" t="s" s="2">
         <v>77</v>
@@ -69589,7 +69595,7 @@
     </row>
     <row r="612">
       <c r="A612" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B612" t="s" s="2">
         <v>188</v>
@@ -69692,13 +69698,13 @@
     </row>
     <row r="613">
       <c r="A613" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B613" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C613" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D613" s="2"/>
       <c r="E613" t="s" s="2">
@@ -69795,13 +69801,13 @@
     </row>
     <row r="614">
       <c r="A614" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B614" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C614" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="D614" s="2"/>
       <c r="E614" t="s" s="2">
@@ -69898,13 +69904,13 @@
     </row>
     <row r="615">
       <c r="A615" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B615" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C615" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D615" s="2"/>
       <c r="E615" t="s" s="2">
@@ -69930,13 +69936,13 @@
         <v>126</v>
       </c>
       <c r="M615" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="N615" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="O615" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="P615" s="2"/>
       <c r="Q615" t="s" s="2">
@@ -69944,7 +69950,7 @@
       </c>
       <c r="R615" s="2"/>
       <c r="S615" t="s" s="2">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="T615" t="s" s="2">
         <v>23</v>
@@ -69986,7 +69992,7 @@
         <v>23</v>
       </c>
       <c r="AG615" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AH615" t="s" s="2">
         <v>85</v>
@@ -70003,13 +70009,13 @@
     </row>
     <row r="616">
       <c r="A616" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="B616" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C616" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D616" s="2"/>
       <c r="E616" t="s" s="2">
@@ -70035,10 +70041,10 @@
         <v>770</v>
       </c>
       <c r="M616" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="N616" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="O616" s="2"/>
       <c r="P616" s="2"/>
@@ -70089,7 +70095,7 @@
         <v>23</v>
       </c>
       <c r="AG616" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="AH616" t="s" s="2">
         <v>77</v>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T14:05:51+00:00</t>
+    <t>2026-08-12T15:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T10:03:40+00:00</t>
+    <t>2026-08-14T12:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:06:36+00:00</t>
+    <t>2026-08-20T12:53:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9024" uniqueCount="961">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9025" uniqueCount="962">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:53:18+00:00</t>
+    <t>2026-08-26T13:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1961,7 +1961,7 @@
     <t>List</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-list</t>
+    <t>http://hl7.org/fhir/StructureDefinition/List</t>
   </si>
   <si>
     <t>Collection
@@ -2177,7 +2177,7 @@
     <t>List.entry</t>
   </si>
   <si>
-    <t>Die Reihenfolge der Listeneinträge ist fachlich relevant und wird durch den Ersteller durch die Reihung der Eintries festgelegt.</t>
+    <t>Entries in the list</t>
   </si>
   <si>
     <t>Entries in this list.</t>
@@ -2202,7 +2202,7 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Eintrags</t>
+    <t>Status/Workflow information about this item</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -2214,7 +2214,10 @@
     <t>This field is present to support various clinical uses of lists, such as a discharge summary medication list, where flags specify whether the medication was added, modified, or deleted from the list.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListEntryFlagVS</t>
+    <t>Codes that provide further information about the reason and meaning of the item in the list.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-item-flag|4.0.1</t>
   </si>
   <si>
     <t>List.entry.deleted</t>
@@ -3855,7 +3858,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
     </row>
     <row r="94">
@@ -3863,7 +3866,7 @@
         <v>4</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
     </row>
     <row r="95">
@@ -3879,7 +3882,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
     </row>
     <row r="97">
@@ -3887,7 +3890,7 @@
         <v>10</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
     </row>
     <row r="98">
@@ -3949,7 +3952,7 @@
         <v>24</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
     </row>
     <row r="106">
@@ -3985,7 +3988,7 @@
         <v>32</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
     </row>
     <row r="111">
@@ -3993,7 +3996,7 @@
         <v>34</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
     </row>
     <row r="112">
@@ -4025,7 +4028,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="116">
@@ -4033,7 +4036,7 @@
         <v>4</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
     </row>
     <row r="117">
@@ -4049,7 +4052,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>923</v>
+        <v>924</v>
       </c>
     </row>
     <row r="119">
@@ -4057,7 +4060,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
     </row>
     <row r="120">
@@ -4187,7 +4190,7 @@
         <v>581</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>925</v>
+        <v>926</v>
       </c>
     </row>
     <row r="137">
@@ -4203,7 +4206,7 @@
         <v>2</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="139">
@@ -4211,7 +4214,7 @@
         <v>4</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>927</v>
+        <v>928</v>
       </c>
     </row>
     <row r="140">
@@ -4227,7 +4230,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>928</v>
+        <v>929</v>
       </c>
     </row>
     <row r="142">
@@ -4235,7 +4238,7 @@
         <v>10</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>929</v>
+        <v>930</v>
       </c>
     </row>
     <row r="143">
@@ -4333,7 +4336,7 @@
         <v>32</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
     </row>
     <row r="156">
@@ -4341,7 +4344,7 @@
         <v>34</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="157">
@@ -4373,7 +4376,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="161">
@@ -4381,7 +4384,7 @@
         <v>4</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
     </row>
     <row r="162">
@@ -4397,7 +4400,7 @@
         <v>8</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="164">
@@ -4535,7 +4538,7 @@
         <v>581</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
   </sheetData>
@@ -21232,7 +21235,7 @@
         <v>85</v>
       </c>
       <c r="I160" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="J160" t="s" s="2">
         <v>23</v>
@@ -22803,13 +22806,13 @@
       </c>
       <c r="F175" s="2"/>
       <c r="G175" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I175" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="J175" t="s" s="2">
         <v>23</v>
@@ -22855,11 +22858,13 @@
         <v>23</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="Z175" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="Z175" t="s" s="2">
+        <v>707</v>
+      </c>
       <c r="AA175" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="AB175" t="s" s="2">
         <v>23</v>
@@ -22897,10 +22902,10 @@
         <v>618</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -22926,68 +22931,68 @@
         <v>479</v>
       </c>
       <c r="M176" t="s" s="2">
+        <v>710</v>
+      </c>
+      <c r="N176" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="O176" t="s" s="2">
+        <v>712</v>
+      </c>
+      <c r="P176" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="Q176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R176" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="S176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF176" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG176" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="N176" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="O176" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="P176" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="Q176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R176" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="S176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF176" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG176" t="s" s="2">
-        <v>708</v>
-      </c>
       <c r="AH176" t="s" s="2">
         <v>77</v>
       </c>
@@ -22995,7 +23000,7 @@
         <v>85</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AK176" t="s" s="2">
         <v>97</v>
@@ -23006,10 +23011,10 @@
         <v>618</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -23035,14 +23040,14 @@
         <v>282</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O177" s="2"/>
       <c r="P177" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="Q177" t="s" s="2">
         <v>23</v>
@@ -23091,7 +23096,7 @@
         <v>23</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>77</v>
@@ -23111,10 +23116,10 @@
         <v>618</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -23140,10 +23145,10 @@
         <v>564</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="O178" s="2"/>
       <c r="P178" s="2"/>
@@ -23194,7 +23199,7 @@
         <v>23</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AH178" t="s" s="2">
         <v>85</v>
@@ -23214,10 +23219,10 @@
         <v>618</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -23243,16 +23248,16 @@
         <v>214</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="P179" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="Q179" t="s" s="2">
         <v>23</v>
@@ -23281,7 +23286,7 @@
       </c>
       <c r="Z179" s="2"/>
       <c r="AA179" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AB179" t="s" s="2">
         <v>23</v>
@@ -23299,7 +23304,7 @@
         <v>23</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AH179" t="s" s="2">
         <v>77</v>
@@ -23316,13 +23321,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -23348,10 +23353,10 @@
         <v>79</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
@@ -23402,7 +23407,7 @@
         <v>23</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>77</v>
@@ -23414,18 +23419,18 @@
         <v>23</v>
       </c>
       <c r="AK180" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -23524,13 +23529,13 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
@@ -23627,13 +23632,13 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
@@ -23730,13 +23735,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -23835,13 +23840,13 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
@@ -23940,13 +23945,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -24045,13 +24050,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -24150,13 +24155,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -24255,13 +24260,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -24360,13 +24365,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -24463,13 +24468,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B191" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="C191" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="C191" t="s" s="2">
-        <v>747</v>
       </c>
       <c r="D191" t="s" s="2">
         <v>156</v>
@@ -24568,13 +24573,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -24673,13 +24678,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -24778,13 +24783,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -24883,13 +24888,13 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -24988,13 +24993,13 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -25089,13 +25094,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B197" t="s" s="2">
+        <v>755</v>
+      </c>
+      <c r="C197" t="s" s="2">
         <v>754</v>
-      </c>
-      <c r="C197" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="D197" t="s" s="2">
         <v>192</v>
@@ -25194,13 +25199,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="D198" t="s" s="2">
         <v>198</v>
@@ -25299,13 +25304,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -25406,13 +25411,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -25441,13 +25446,13 @@
         <v>405</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P200" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="Q200" t="s" s="2">
         <v>23</v>
@@ -25496,7 +25501,7 @@
         <v>23</v>
       </c>
       <c r="AG200" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="AH200" t="s" s="2">
         <v>77</v>
@@ -25513,13 +25518,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -25542,13 +25547,13 @@
         <v>86</v>
       </c>
       <c r="L201" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" s="2"/>
@@ -25599,7 +25604,7 @@
         <v>23</v>
       </c>
       <c r="AG201" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AH201" t="s" s="2">
         <v>77</v>
@@ -25616,13 +25621,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -25648,13 +25653,13 @@
         <v>126</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="O202" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P202" s="2"/>
       <c r="Q202" t="s" s="2">
@@ -25704,7 +25709,7 @@
         <v>23</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>77</v>
@@ -25721,17 +25726,17 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="F203" s="2"/>
       <c r="G203" t="s" s="2">
@@ -25750,13 +25755,13 @@
         <v>86</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" s="2"/>
@@ -25807,7 +25812,7 @@
         <v>23</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>77</v>
@@ -25824,17 +25829,17 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F204" s="2"/>
       <c r="G204" t="s" s="2">
@@ -25853,16 +25858,16 @@
         <v>86</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="O204" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="P204" s="2"/>
       <c r="Q204" t="s" s="2">
@@ -25912,7 +25917,7 @@
         <v>23</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>77</v>
@@ -25929,13 +25934,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -25961,13 +25966,13 @@
         <v>165</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="O205" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
@@ -25997,7 +26002,7 @@
       </c>
       <c r="Z205" s="2"/>
       <c r="AA205" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="AB205" t="s" s="2">
         <v>23</v>
@@ -26015,7 +26020,7 @@
         <v>23</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>85</v>
@@ -26032,17 +26037,17 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="F206" s="2"/>
       <c r="G206" t="s" s="2">
@@ -26064,13 +26069,13 @@
         <v>214</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="O206" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="P206" s="2"/>
       <c r="Q206" t="s" s="2">
@@ -26099,10 +26104,10 @@
         <v>150</v>
       </c>
       <c r="Z206" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="AA206" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="AB206" t="s" s="2">
         <v>23</v>
@@ -26120,7 +26125,7 @@
         <v>23</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>77</v>
@@ -26137,13 +26142,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -26169,10 +26174,10 @@
         <v>214</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
@@ -26202,10 +26207,10 @@
         <v>150</v>
       </c>
       <c r="Z207" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="AA207" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="AB207" t="s" s="2">
         <v>23</v>
@@ -26223,7 +26228,7 @@
         <v>23</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>77</v>
@@ -26240,13 +26245,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -26272,10 +26277,10 @@
         <v>214</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" t="s" s="2">
@@ -26308,7 +26313,7 @@
       </c>
       <c r="Z208" s="2"/>
       <c r="AA208" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AB208" t="s" s="2">
         <v>23</v>
@@ -26326,7 +26331,7 @@
         <v>23</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>77</v>
@@ -26343,13 +26348,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -26446,13 +26451,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -26551,13 +26556,13 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -26658,13 +26663,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -26765,13 +26770,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -26797,10 +26802,10 @@
         <v>270</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" s="2"/>
@@ -26851,7 +26856,7 @@
         <v>23</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>85</v>
@@ -26868,13 +26873,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -26903,10 +26908,10 @@
         <v>275</v>
       </c>
       <c r="N214" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="O214" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="P214" s="2"/>
       <c r="Q214" t="s" s="2">
@@ -26956,7 +26961,7 @@
         <v>23</v>
       </c>
       <c r="AG214" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="AH214" t="s" s="2">
         <v>77</v>
@@ -26973,13 +26978,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -27005,13 +27010,13 @@
         <v>282</v>
       </c>
       <c r="M215" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="N215" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="O215" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="P215" s="2"/>
       <c r="Q215" t="s" s="2">
@@ -27061,7 +27066,7 @@
         <v>23</v>
       </c>
       <c r="AG215" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="AH215" t="s" s="2">
         <v>77</v>
@@ -27078,13 +27083,13 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -27110,7 +27115,7 @@
         <v>287</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N216" t="s" s="2">
         <v>289</v>
@@ -27164,7 +27169,7 @@
         <v>23</v>
       </c>
       <c r="AG216" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="AH216" t="s" s="2">
         <v>77</v>
@@ -27181,13 +27186,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -27213,10 +27218,10 @@
         <v>292</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="O217" s="2"/>
       <c r="P217" s="2"/>
@@ -27267,7 +27272,7 @@
         <v>23</v>
       </c>
       <c r="AG217" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AH217" t="s" s="2">
         <v>77</v>
@@ -27284,13 +27289,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -27316,10 +27321,10 @@
         <v>306</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="O218" s="2"/>
       <c r="P218" s="2"/>
@@ -27370,7 +27375,7 @@
         <v>23</v>
       </c>
       <c r="AG218" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="AH218" t="s" s="2">
         <v>77</v>
@@ -27387,13 +27392,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -27490,13 +27495,13 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -27595,13 +27600,13 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
@@ -27702,13 +27707,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
@@ -27734,14 +27739,14 @@
         <v>214</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="O222" s="2"/>
       <c r="P222" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="Q222" t="s" s="2">
         <v>23</v>
@@ -27769,10 +27774,10 @@
         <v>150</v>
       </c>
       <c r="Z222" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="AA222" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="AB222" t="s" s="2">
         <v>23</v>
@@ -27790,7 +27795,7 @@
         <v>23</v>
       </c>
       <c r="AG222" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="AH222" t="s" s="2">
         <v>77</v>
@@ -27807,13 +27812,13 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -27836,17 +27841,17 @@
         <v>86</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="Q223" t="s" s="2">
         <v>23</v>
@@ -27895,7 +27900,7 @@
         <v>23</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>85</v>
@@ -27912,13 +27917,13 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -27941,17 +27946,17 @@
         <v>23</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="Q224" t="s" s="2">
         <v>23</v>
@@ -28000,7 +28005,7 @@
         <v>23</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>77</v>
@@ -28017,13 +28022,13 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -28046,17 +28051,17 @@
         <v>86</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="O225" s="2"/>
       <c r="P225" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="Q225" t="s" s="2">
         <v>23</v>
@@ -28105,7 +28110,7 @@
         <v>23</v>
       </c>
       <c r="AG225" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="AH225" t="s" s="2">
         <v>77</v>
@@ -28122,13 +28127,13 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -28154,13 +28159,13 @@
         <v>214</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="O226" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="P226" s="2"/>
       <c r="Q226" t="s" s="2">
@@ -28189,10 +28194,10 @@
         <v>150</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="AA226" t="s" s="2">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="AB226" t="s" s="2">
         <v>23</v>
@@ -28210,7 +28215,7 @@
         <v>23</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>77</v>
@@ -28227,13 +28232,13 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" t="s" s="2">
@@ -28256,16 +28261,16 @@
         <v>86</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="O227" t="s" s="2">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="P227" s="2"/>
       <c r="Q227" t="s" s="2">
@@ -28315,7 +28320,7 @@
         <v>23</v>
       </c>
       <c r="AG227" t="s" s="2">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="AH227" t="s" s="2">
         <v>77</v>
@@ -28332,13 +28337,13 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -28364,13 +28369,13 @@
         <v>214</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="O228" t="s" s="2">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="P228" s="2"/>
       <c r="Q228" t="s" s="2">
@@ -28420,7 +28425,7 @@
         <v>23</v>
       </c>
       <c r="AG228" t="s" s="2">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="AH228" t="s" s="2">
         <v>77</v>
@@ -28437,13 +28442,13 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -28469,13 +28474,13 @@
         <v>214</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="O229" t="s" s="2">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="P229" s="2"/>
       <c r="Q229" t="s" s="2">
@@ -28504,10 +28509,10 @@
         <v>150</v>
       </c>
       <c r="Z229" t="s" s="2">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="AA229" t="s" s="2">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AB229" t="s" s="2">
         <v>23</v>
@@ -28525,7 +28530,7 @@
         <v>23</v>
       </c>
       <c r="AG229" t="s" s="2">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="AH229" t="s" s="2">
         <v>77</v>
@@ -28542,13 +28547,13 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -28571,16 +28576,16 @@
         <v>23</v>
       </c>
       <c r="L230" t="s" s="2">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="M230" t="s" s="2">
         <v>550</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="P230" s="2"/>
       <c r="Q230" t="s" s="2">
@@ -28630,7 +28635,7 @@
         <v>23</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="AH230" t="s" s="2">
         <v>77</v>
@@ -28647,13 +28652,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -28679,13 +28684,13 @@
         <v>214</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="O231" t="s" s="2">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="P231" s="2"/>
       <c r="Q231" t="s" s="2">
@@ -28714,7 +28719,7 @@
         <v>150</v>
       </c>
       <c r="Z231" t="s" s="2">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="AA231" t="s" s="2">
         <v>438</v>
@@ -28735,7 +28740,7 @@
         <v>23</v>
       </c>
       <c r="AG231" t="s" s="2">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="AH231" t="s" s="2">
         <v>77</v>
@@ -28752,13 +28757,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -28781,17 +28786,17 @@
         <v>23</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="Q232" t="s" s="2">
         <v>23</v>
@@ -28840,7 +28845,7 @@
         <v>23</v>
       </c>
       <c r="AG232" t="s" s="2">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="AH232" t="s" s="2">
         <v>77</v>
@@ -28857,13 +28862,13 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -28889,10 +28894,10 @@
         <v>214</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="O233" s="2"/>
       <c r="P233" s="2"/>
@@ -28922,10 +28927,10 @@
         <v>150</v>
       </c>
       <c r="Z233" t="s" s="2">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="AA233" t="s" s="2">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="AB233" t="s" s="2">
         <v>23</v>
@@ -28943,7 +28948,7 @@
         <v>23</v>
       </c>
       <c r="AG233" t="s" s="2">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="AH233" t="s" s="2">
         <v>77</v>
@@ -28960,13 +28965,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -28992,10 +28997,10 @@
         <v>301</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="O234" s="2"/>
       <c r="P234" s="2"/>
@@ -29046,7 +29051,7 @@
         <v>23</v>
       </c>
       <c r="AG234" t="s" s="2">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="AH234" t="s" s="2">
         <v>77</v>
@@ -29063,13 +29068,13 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -29166,13 +29171,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -29271,13 +29276,13 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -29376,13 +29381,13 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" t="s" s="2">
@@ -29479,13 +29484,13 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" t="s" s="2">
@@ -29582,13 +29587,13 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" t="s" s="2">
@@ -29614,10 +29619,10 @@
         <v>306</v>
       </c>
       <c r="M240" t="s" s="2">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="N240" t="s" s="2">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="O240" s="2"/>
       <c r="P240" s="2"/>
@@ -29668,7 +29673,7 @@
         <v>23</v>
       </c>
       <c r="AG240" t="s" s="2">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="AH240" t="s" s="2">
         <v>77</v>
@@ -29685,13 +29690,13 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" t="s" s="2">
@@ -29788,13 +29793,13 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" t="s" s="2">
@@ -29893,13 +29898,13 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" t="s" s="2">
@@ -30000,13 +30005,13 @@
     </row>
     <row r="244">
       <c r="A244" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" t="s" s="2">
@@ -30032,10 +30037,10 @@
         <v>214</v>
       </c>
       <c r="M244" t="s" s="2">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="N244" t="s" s="2">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="O244" s="2"/>
       <c r="P244" s="2"/>
@@ -30065,10 +30070,10 @@
         <v>169</v>
       </c>
       <c r="Z244" t="s" s="2">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="AA244" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="AB244" t="s" s="2">
         <v>23</v>
@@ -30086,7 +30091,7 @@
         <v>23</v>
       </c>
       <c r="AG244" t="s" s="2">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="AH244" t="s" s="2">
         <v>77</v>
@@ -30103,13 +30108,13 @@
     </row>
     <row r="245">
       <c r="A245" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" t="s" s="2">
@@ -30132,13 +30137,13 @@
         <v>23</v>
       </c>
       <c r="L245" t="s" s="2">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="M245" t="s" s="2">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="N245" t="s" s="2">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="O245" s="2"/>
       <c r="P245" s="2"/>
@@ -30189,7 +30194,7 @@
         <v>23</v>
       </c>
       <c r="AG245" t="s" s="2">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="AH245" t="s" s="2">
         <v>85</v>
@@ -30206,13 +30211,13 @@
     </row>
     <row r="246">
       <c r="A246" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="D246" s="2"/>
       <c r="E246" t="s" s="2">
@@ -30235,19 +30240,19 @@
         <v>23</v>
       </c>
       <c r="L246" t="s" s="2">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="M246" t="s" s="2">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="N246" t="s" s="2">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="O246" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="P246" t="s" s="2">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="Q246" t="s" s="2">
         <v>23</v>
@@ -30296,7 +30301,7 @@
         <v>23</v>
       </c>
       <c r="AG246" t="s" s="2">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="AH246" t="s" s="2">
         <v>77</v>
@@ -30313,13 +30318,13 @@
     </row>
     <row r="247">
       <c r="A247" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" t="s" s="2">
@@ -30345,13 +30350,13 @@
         <v>214</v>
       </c>
       <c r="M247" t="s" s="2">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="N247" t="s" s="2">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="O247" t="s" s="2">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="P247" s="2"/>
       <c r="Q247" t="s" s="2">
@@ -30380,10 +30385,10 @@
         <v>150</v>
       </c>
       <c r="Z247" t="s" s="2">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="AA247" t="s" s="2">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="AB247" t="s" s="2">
         <v>23</v>
@@ -30401,7 +30406,7 @@
         <v>23</v>
       </c>
       <c r="AG247" t="s" s="2">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="AH247" t="s" s="2">
         <v>77</v>
@@ -30418,7 +30423,7 @@
     </row>
     <row r="248">
       <c r="A248" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B248" t="s" s="2">
         <v>188</v>
@@ -30450,7 +30455,7 @@
         <v>79</v>
       </c>
       <c r="M248" t="s" s="2">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="N248" t="s" s="2">
         <v>315</v>
@@ -30521,7 +30526,7 @@
     </row>
     <row r="249">
       <c r="A249" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B249" t="s" s="2">
         <v>585</v>
@@ -30624,7 +30629,7 @@
     </row>
     <row r="250">
       <c r="A250" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B250" t="s" s="2">
         <v>586</v>
@@ -30727,7 +30732,7 @@
     </row>
     <row r="251">
       <c r="A251" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B251" t="s" s="2">
         <v>598</v>
@@ -30773,7 +30778,7 @@
       </c>
       <c r="R251" s="2"/>
       <c r="S251" t="s" s="2">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="T251" t="s" s="2">
         <v>23</v>
@@ -30832,7 +30837,7 @@
     </row>
     <row r="252">
       <c r="A252" t="s" s="2">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B252" t="s" s="2">
         <v>604</v>
@@ -30935,13 +30940,13 @@
     </row>
     <row r="253">
       <c r="A253" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" t="s" s="2">
@@ -30967,13 +30972,13 @@
         <v>79</v>
       </c>
       <c r="M253" t="s" s="2">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="N253" t="s" s="2">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="O253" t="s" s="2">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="P253" s="2"/>
       <c r="Q253" t="s" s="2">
@@ -31023,7 +31028,7 @@
         <v>23</v>
       </c>
       <c r="AG253" t="s" s="2">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="AH253" t="s" s="2">
         <v>77</v>
@@ -31035,18 +31040,18 @@
         <v>196</v>
       </c>
       <c r="AK253" t="s" s="2">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" t="s" s="2">
@@ -31143,13 +31148,13 @@
     </row>
     <row r="255">
       <c r="A255" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="D255" s="2"/>
       <c r="E255" t="s" s="2">
@@ -31248,13 +31253,13 @@
     </row>
     <row r="256">
       <c r="A256" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="D256" s="2"/>
       <c r="E256" t="s" s="2">
@@ -31280,13 +31285,13 @@
         <v>99</v>
       </c>
       <c r="M256" t="s" s="2">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="N256" t="s" s="2">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="O256" t="s" s="2">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="P256" s="2"/>
       <c r="Q256" t="s" s="2">
@@ -31336,7 +31341,7 @@
         <v>23</v>
       </c>
       <c r="AG256" t="s" s="2">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="AH256" t="s" s="2">
         <v>77</v>
@@ -31345,7 +31350,7 @@
         <v>85</v>
       </c>
       <c r="AJ256" t="s" s="2">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="AK256" t="s" s="2">
         <v>97</v>
@@ -31353,13 +31358,13 @@
     </row>
     <row r="257">
       <c r="A257" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="D257" s="2"/>
       <c r="E257" t="s" s="2">
@@ -31385,13 +31390,13 @@
         <v>126</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="N257" t="s" s="2">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="O257" t="s" s="2">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="P257" s="2"/>
       <c r="Q257" t="s" s="2">
@@ -31420,10 +31425,10 @@
         <v>142</v>
       </c>
       <c r="Z257" t="s" s="2">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="AA257" t="s" s="2">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="AB257" t="s" s="2">
         <v>23</v>
@@ -31441,7 +31446,7 @@
         <v>23</v>
       </c>
       <c r="AG257" t="s" s="2">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="AH257" t="s" s="2">
         <v>77</v>
@@ -31458,13 +31463,13 @@
     </row>
     <row r="258">
       <c r="A258" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="D258" s="2"/>
       <c r="E258" t="s" s="2">
@@ -31490,13 +31495,13 @@
         <v>208</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="N258" t="s" s="2">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="O258" t="s" s="2">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="P258" s="2"/>
       <c r="Q258" t="s" s="2">
@@ -31546,7 +31551,7 @@
         <v>23</v>
       </c>
       <c r="AG258" t="s" s="2">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="AH258" t="s" s="2">
         <v>77</v>
@@ -31563,13 +31568,13 @@
     </row>
     <row r="259">
       <c r="A259" t="s" s="2">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D259" s="2"/>
       <c r="E259" t="s" s="2">
@@ -31595,13 +31600,13 @@
         <v>99</v>
       </c>
       <c r="M259" t="s" s="2">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="N259" t="s" s="2">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="O259" t="s" s="2">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="P259" s="2"/>
       <c r="Q259" t="s" s="2">
@@ -31651,7 +31656,7 @@
         <v>23</v>
       </c>
       <c r="AG259" t="s" s="2">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="AH259" t="s" s="2">
         <v>77</v>
@@ -31668,7 +31673,7 @@
     </row>
     <row r="260">
       <c r="A260" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B260" t="s" s="2">
         <v>188</v>
@@ -31771,7 +31776,7 @@
     </row>
     <row r="261">
       <c r="A261" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B261" t="s" s="2">
         <v>585</v>
@@ -31874,7 +31879,7 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B262" t="s" s="2">
         <v>586</v>
@@ -31977,7 +31982,7 @@
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B263" t="s" s="2">
         <v>598</v>
@@ -32023,7 +32028,7 @@
       </c>
       <c r="R263" s="2"/>
       <c r="S263" t="s" s="2">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="T263" t="s" s="2">
         <v>23</v>
@@ -32082,7 +32087,7 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B264" t="s" s="2">
         <v>604</v>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8140" uniqueCount="902">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8338" uniqueCount="911">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T05:58:13+00:00</t>
+    <t>2026-08-28T07:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1798,7 +1798,7 @@
     <t>AT ELGA e-Diagnose List</t>
   </si>
   <si>
-    <t>Das AT e-Diagnose List-Profil leitet sich vom HL7-AT-Core-R4-Profil ab und dient der strukturierten Listung von Einträgen.</t>
+    <t>Das AT e-Diagnose List-Profil dient der strukturierten Listung von Einträgen.</t>
   </si>
   <si>
     <t>List</t>
@@ -1818,7 +1818,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lst-1:A list can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}lst-2:The deleted flag can only be used if the mode of the list is "changes" {mode = 'changes' or entry.deleted.empty()}lst-3:An entry date can only be used if the mode of the list is "working" {mode = 'working' or entry.date.empty()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lst-1:A list can only have an emptyReason if it is empty {emptyReason.empty() or entry.empty()}lst-2:The deleted flag can only be used if the mode of the list is "changes" {mode = 'changes' or entry.deleted.empty()}lst-3:An entry date can only be used if the mode of the list is "working" {mode = 'working' or entry.date.empty()}list-integrity:Die Liste darf nur Referenzen (List.entry.item) enthalten, die dem Code der Liste (List.code) entsprechen. {(code.coding.exists(system='http://loinc.org' and code='11450-4') implies entry.item.all(reference.matches('(^|/)Condition/'))) and (code.coding.exists(system='http://loinc.org' and code='47519-4') implies entry.item.all(reference.matches('(^|/)Procedure/'))) and (code.coding.exists(system='http://loinc.org' and code='48765-2') implies entry.item.all(reference.matches('(^|/)AllergyIntolerance/')))}list-emptyreason-required:Begründung für leere Liste ist erforderlich. {entry.empty() implies emptyReason.exists()}</t>
   </si>
   <si>
     <t>List.id</t>
@@ -1851,7 +1851,7 @@
     <t>List.identifier</t>
   </si>
   <si>
-    <t>Logischer Identfier der Liste zur Integritätsprüfung beim Schreibvorgang.</t>
+    <t>Kein logischer Identifier für die Liste erforderlich.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -1869,13 +1869,19 @@
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListStatusVS</t>
+    <t>current</t>
+  </si>
+  <si>
+    <t>The current state of the list.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/list-status|4.0.1</t>
   </si>
   <si>
     <t>List.mode</t>
   </si>
   <si>
-    <t>Die Liste ist ein laufend gepflegtes Dokument. Fixer Wert: working.</t>
+    <t>Die Liste wird laufend gepflegt, hat daher den fixen Wert: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -1899,7 +1905,7 @@
     <t>List.title</t>
   </si>
   <si>
-    <t>Titel der Liste</t>
+    <t>Die Liste hat keinen Titel.</t>
   </si>
   <si>
     <t>A label for the list assigned by the author.</t>
@@ -1932,7 +1938,8 @@
     <t>List.subject</t>
   </si>
   <si>
-    <t>Patient, für den die Liste erstellt werden soll, der über den Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Diagnose ist.</t>
+    <t>Patient, für den die Liste geführt wird, der über den 
+Zentralen Patientenindex identifizierbar und Teilnehmer der e-Diagnose ist.</t>
   </si>
   <si>
     <t>The common subject (or patient) of the resources that are in the list if there is one.</t>
@@ -1947,7 +1954,7 @@
     <t>List.encounter</t>
   </si>
   <si>
-    <t>Patientenkontakt</t>
+    <t>Es wird kein Behandlungskontext dokumentiert.</t>
   </si>
   <si>
     <t>The encounter that is the context in which this list was created.</t>
@@ -1956,7 +1963,7 @@
     <t>List.date</t>
   </si>
   <si>
-    <t>Letzte Aktualisierung der Liste.</t>
+    <t>Datum der letzten Aktualisierung der Liste.</t>
   </si>
   <si>
     <t>The date that the list was prepared.</t>
@@ -1975,7 +1982,8 @@
 </t>
   </si>
   <si>
-    <t>Arzt oder Ärztin, die die Liste erstellt und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Diagnose des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung. Patient nur nachdem er Einträge gelöscht hat.</t>
+    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. Im Falle eines GDA: eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA-Anwendung 
+des Patienten zuzugreifen. Im Falle eines Patienten: eindeutig identifiziert durch den Z-PI.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -1990,7 +1998,7 @@
     <t>List.orderedBy</t>
   </si>
   <si>
-    <t>Die Reihenfolge der Einträge in der Liste.</t>
+    <t>Die Reihenfolge der Einträge wird über die List.entries durch den Ersteller vorgegeben.</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -2011,7 +2019,7 @@
     <t>List.note</t>
   </si>
   <si>
-    <t>Freitextliche Anmerkungen zur Liste.</t>
+    <t>Keine Freitext-Anmerkungen auf Listenebene.</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -2020,7 +2028,7 @@
     <t>List.entry</t>
   </si>
   <si>
-    <t>Entries in the list</t>
+    <t>Die Reihenfolge der Listeneinträge kann in die Fachanwendung zurückgeschrieben werden. Gleichzeitig kann die Sortierung in lokalen Systemen erfolgen.</t>
   </si>
   <si>
     <t>Entries in this list.</t>
@@ -2045,7 +2053,7 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Status/Workflow information about this item</t>
+    <t>Kennzeichnung des Status entsprechend Workflow nicht relevant.</t>
   </si>
   <si>
     <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
@@ -2066,7 +2074,7 @@
     <t>List.entry.deleted</t>
   </si>
   <si>
-    <t>Gibt an, ob der referenzierte Eintrag zur Entfernung markiert wurde. Wird durch Flag 'removed' gelöst.</t>
+    <t>Kennzeichnung, dass der Eintrag gelöscht wurde, ist nicht erlaubt (siehe Invariant lst-2).</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -2088,7 +2096,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme des Eintrags in die Liste.</t>
+    <t>Datum der Aufnahme des Eintrags in die Liste wird nicht dokumentiert, da die Liste laufend gepflegt wird und das Datum der letzten Aktualisierung der Liste (List.date) dokumentiert wird.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -2100,668 +2108,42 @@
     <t>List.entry.item</t>
   </si>
   <si>
-    <t>Referenz auf einen Eintrag. Zu klären: reicht ein List-Profil oder braucht es jeweils eines für die integren Listen, die Gesamtliste, Liste für Allergien, Alerts?</t>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-condition|https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-procedure|https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-allergyintolerance)
+</t>
+  </si>
+  <si>
+    <t>Referenz auf einen Eintrag.</t>
   </si>
   <si>
     <t>A reference to the actual resource from which data was derived.</t>
   </si>
   <si>
-    <t>List.emptyReason</t>
-  </si>
-  <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Für Patient gibt es zurzeit keine Einträge</t>
-  </si>
-  <si>
-    <t>If the list is empty, why the list is empty.</t>
-  </si>
-  <si>
-    <t>The various reasons for an empty list make a significant interpretation to its interpretation. Note that this code is for use when the entire list has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
-  </si>
-  <si>
-    <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListEmptyReasonVS</t>
-  </si>
-  <si>
-    <t>at-elga-ediag-procedure</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-procedure</t>
-  </si>
-  <si>
-    <t>AtEdiagProcedure</t>
-  </si>
-  <si>
-    <t>AT ELGA e-Diagnose Procedure</t>
-  </si>
-  <si>
-    <t>Das AT e-Diagnose Procedure-Profil leitet sich vom Procedure-Profil ab und passt dieses für die Anforderungen der e-Diagnose an.</t>
-  </si>
-  <si>
-    <t>Procedure</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Procedure</t>
-  </si>
-  <si>
-    <t>AT e-Diagnose Procedure</t>
-  </si>
-  <si>
-    <t>An action that is or was performed on or for a patient. This can be a physical intervention like an operation, or less invasive like long term services, counseling, or hypnotherapy.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
-  </si>
-  <si>
-    <t>Procedure.id</t>
-  </si>
-  <si>
-    <t>Procedure.meta</t>
-  </si>
-  <si>
-    <t>Procedure.implicitRules</t>
-  </si>
-  <si>
-    <t>Procedure.language</t>
-  </si>
-  <si>
-    <t>Procedure.text</t>
-  </si>
-  <si>
-    <t>Procedure.contained</t>
-  </si>
-  <si>
-    <t>Procedure.extension</t>
-  </si>
-  <si>
-    <t>Procedure.extension:reported</t>
-  </si>
-  <si>
-    <t>Procedure.extension:entered-in-error</t>
-  </si>
-  <si>
-    <t>Procedure.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.identifier</t>
-  </si>
-  <si>
-    <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
-  </si>
-  <si>
-    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and Person resource instances might share the same social insurance number.</t>
-  </si>
-  <si>
-    <t>Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t>Procedure.instantiatesCanonical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll</t>
-  </si>
-  <si>
-    <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
-  </si>
-  <si>
-    <t>Procedure.instantiatesUri</t>
-  </si>
-  <si>
-    <t>Verweis auf ein externes Dokument</t>
-  </si>
-  <si>
-    <t>The URL pointing to an externally maintained protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
-  </si>
-  <si>
-    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
-  </si>
-  <si>
-    <t>Procedure.basedOn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fulfills
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Verweis auf eine Anforderung</t>
-  </si>
-  <si>
-    <t>A reference to a resource that contains details of the request for this procedure.</t>
-  </si>
-  <si>
-    <t>Procedure.partOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">container
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Procedure|4.0.1|Observation|4.0.1|MedicationAdministration|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Verweis der Ressource auf eine andere, übergreordnete Ressource</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular procedure is a component or step.</t>
-  </si>
-  <si>
-    <t>The MedicationAdministration resource has a partOf reference to Procedure, but this is not a circular reference.   For example, the anesthesia MedicationAdministration is part of the surgical Procedure (MedicationAdministration.partOf = Procedure).  For example, the procedure to insert the IV port for an IV medication administration is part of the medication administration (Procedure.partOf = MedicationAdministration).</t>
-  </si>
-  <si>
-    <t>Procedure.status</t>
-  </si>
-  <si>
-    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren</t>
-  </si>
-  <si>
-    <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
-  </si>
-  <si>
-    <t>The "unknown" code is not to be used to convey other statuses.  The "unknown" code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the procedure.
-This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-procedure-status</t>
-  </si>
-  <si>
-    <t>Procedure.statusReason</t>
-  </si>
-  <si>
-    <t>Suspended Reason
-Cancelled Reason</t>
-  </si>
-  <si>
-    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung</t>
-  </si>
-  <si>
-    <t>Captures the reason for the current state of the procedure.</t>
-  </si>
-  <si>
-    <t>This is generally only used for "exception" statuses such as "not-done", "suspended" or "aborted". The reason for performing the event at all is captured in reasonCode, not here.</t>
-  </si>
-  <si>
-    <t>A code that identifies the reason a procedure was not performed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-not-performed-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>Procedure.category</t>
-  </si>
-  <si>
-    <t>Kategorisierung nach Verfahren</t>
-  </si>
-  <si>
-    <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
-  </si>
-  <si>
-    <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-category|4.0.1</t>
-  </si>
-  <si>
-    <t>Procedure.code</t>
-  </si>
-  <si>
-    <t>Prozedurencode der durchgeführten Prozedur</t>
-  </si>
-  <si>
-    <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-prozeduren-codes</t>
-  </si>
-  <si>
-    <t>Procedure.code.id</t>
-  </si>
-  <si>
-    <t>Procedure.code.extension</t>
-  </si>
-  <si>
-    <t>Procedure.code.coding</t>
-  </si>
-  <si>
-    <t>Procedure.code.text</t>
-  </si>
-  <si>
-    <t>Procedure.subject</t>
-  </si>
-  <si>
-    <t>Person, auf die sich die Prozedur bezieht</t>
-  </si>
-  <si>
-    <t>The person, animal or group on which the procedure was performed.</t>
-  </si>
-  <si>
-    <t>Procedure.encounter</t>
-  </si>
-  <si>
-    <t>The Encounter during which this Procedure was created or performed or to which the creation of this record is tightly associated.</t>
-  </si>
-  <si>
-    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
-  </si>
-  <si>
-    <t>Procedure.performed[x]</t>
-  </si>
-  <si>
-    <t>Zeitpunkt der Durchführung</t>
-  </si>
-  <si>
-    <t>Estimated or actual date, date-time, period, or age when the procedure was performed.  Allows a period to support complex procedures that span more than one date, and also allows for the length of the procedure to be captured.</t>
-  </si>
-  <si>
-    <t>Age is generally used when the patient reports an age at which the procedure was performed. Range is generally used when the patient reports an age range when the procedure was performed, such as sometime between 20-25 years old.  dateTime supports a range of precision due to some procedures being reported as past procedures that might not have millisecond precision while other procedures performed and documented during the encounter might have more precise UTC timestamps with timezone.</t>
-  </si>
-  <si>
-    <t>Procedure.recorder</t>
-  </si>
-  <si>
-    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen/dokumentiert hat</t>
-  </si>
-  <si>
-    <t>Procedure.asserter</t>
-  </si>
-  <si>
-    <t>Quelle der Information zur Prozedur (z. B. behandelnde Person, Patient oder Dritter)</t>
-  </si>
-  <si>
-    <t>Individual who is making the procedure statement.</t>
-  </si>
-  <si>
-    <t>Procedure.performer</t>
-  </si>
-  <si>
-    <t>Diese Person hat die Prozedur durchgeführt</t>
-  </si>
-  <si>
-    <t>Limited to "real" people rather than equipment.</t>
-  </si>
-  <si>
-    <t>Procedure.performer.id</t>
-  </si>
-  <si>
-    <t>Procedure.performer.extension</t>
-  </si>
-  <si>
-    <t>Procedure.performer.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.performer.function</t>
-  </si>
-  <si>
-    <t>Type of performance</t>
-  </si>
-  <si>
-    <t>Distinguishes the type of involvement of the performer in the procedure. For example, surgeon, anaesthetist, endoscopist.</t>
-  </si>
-  <si>
-    <t>Allows disambiguation of the types of involvement of different performers.</t>
-  </si>
-  <si>
-    <t>A code that identifies the role of a performer of the procedure.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role|4.0.1</t>
-  </si>
-  <si>
-    <t>Procedure.performer.actor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>The reference to the practitioner</t>
-  </si>
-  <si>
-    <t>The practitioner who was involved in the procedure.</t>
-  </si>
-  <si>
-    <t>A reference to Device supports use cases, such as pacemakers.</t>
-  </si>
-  <si>
-    <t>Procedure.performer.onBehalfOf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Organization the device or practitioner was acting for</t>
-  </si>
-  <si>
-    <t>The organization the device or practitioner was acting on behalf of.</t>
-  </si>
-  <si>
-    <t>Practitioners and Devices can be associated with multiple organizations.  This element indicates which organization they were acting on behalf of when performing the action.</t>
-  </si>
-  <si>
-    <t>Procedure.location</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Location|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Durchführungsort</t>
-  </si>
-  <si>
-    <t>The location where the procedure actually happened.  E.g. a newborn at home, a tracheostomy at a restaurant.</t>
-  </si>
-  <si>
-    <t>Ties a procedure to where the records are likely kept.</t>
-  </si>
-  <si>
-    <t>Procedure.reasonCode</t>
-  </si>
-  <si>
-    <t>Code, des med. Grundes für die Durchführung der Prozedur</t>
-  </si>
-  <si>
-    <t>The coded reason why the procedure was performed. This may be a coded entity of some type, or may simply be present as text.</t>
-  </si>
-  <si>
-    <t>Use Procedure.reasonCode when a code sufficiently describes the reason.  Use Procedure.reasonReference when referencing a resource, which allows more information to be conveyed, such as onset date. Procedure.reasonCode and Procedure.reasonReference are not meant to be duplicative.  For a single reason, either Procedure.reasonCode or Procedure.reasonReference can be used.  Procedure.reasonCode may be a summary code, or Procedure.reasonReference may be used to reference a very precise definition of the reason using Condition | Observation | Procedure | DiagnosticReport | DocumentReference.  Both Procedure.reasonCode and Procedure.reasonReference can be used if they are describing different reasons for the procedure.</t>
-  </si>
-  <si>
-    <t>A code that identifies the reason a procedure is  required.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
-  </si>
-  <si>
-    <t>Procedure.reasonReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|Procedure|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Begründung dass die Prozedur durchgeführt worden ist - Verweis auf eine andere R. wie Condition, Observation,...</t>
-  </si>
-  <si>
-    <t>The justification of why the procedure was performed.</t>
-  </si>
-  <si>
-    <t>It is possible for a procedure to be a reason (such as C-Section) for another procedure (such as an epidural). Other examples include endoscopy for dilatation and biopsy (a combination of diagnostic and therapeutic use). 
-Use Procedure.reasonCode when a code sufficiently describes the reason.  Use Procedure.reasonReference when referencing a resource, which allows more information to be conveyed, such as onset date. Procedure.reasonCode and Procedure.reasonReference are not meant to be duplicative.  For a single reason, either Procedure.reasonCode or Procedure.reasonReference can be used.  Procedure.reasonCode may be a summary code, or Procedure.reasonReference may be used to reference a very precise definition of the reason using Condition | Observation | Procedure | DiagnosticReport | DocumentReference.  Both Procedure.reasonCode and Procedure.reasonReference can be used if they are describing different reasons for the procedure.</t>
-  </si>
-  <si>
-    <t>Procedure.bodySite</t>
-  </si>
-  <si>
-    <t>Betroffene Körperstelle</t>
-  </si>
-  <si>
-    <t>Detailed and structured anatomical location information. Multiple locations are allowed - e.g. multiple punch biopsies of a lesion.</t>
-  </si>
-  <si>
-    <t>If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [procedure-targetbodystructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
-  </si>
-  <si>
-    <t>Procedure.outcome</t>
-  </si>
-  <si>
-    <t>Ergebnis der Prozedur</t>
-  </si>
-  <si>
-    <t>The outcome of the procedure - did it resolve the reasons for the procedure being performed?</t>
-  </si>
-  <si>
-    <t>If outcome contains narrative text only, it can be captured using the CodeableConcept.text.</t>
-  </si>
-  <si>
-    <t>An outcome of a procedure - whether it was resolved or otherwise.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-outcome|4.0.1</t>
-  </si>
-  <si>
-    <t>Procedure.report</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DiagnosticReport|4.0.1|DocumentReference|4.0.1|Composition|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>This could be a histology result, pathology report, surgical report, etc.</t>
-  </si>
-  <si>
-    <t>There could potentially be multiple reports - e.g. if this was a procedure which took multiple biopsies resulting in a number of anatomical pathology reports.</t>
-  </si>
-  <si>
-    <t>Procedure.complication</t>
-  </si>
-  <si>
-    <t>Komplikation/en während dem Eingriff</t>
-  </si>
-  <si>
-    <t>Any complications that occurred during the procedure, or in the immediate post-performance period. These are generally tracked separately from the notes, which will typically describe the procedure itself rather than any 'post procedure' issues.</t>
-  </si>
-  <si>
-    <t>If complications are only expressed by the narrative text, they can be captured using the CodeableConcept.text.</t>
-  </si>
-  <si>
-    <t>Codes describing complications that resulted from a procedure.</t>
-  </si>
-  <si>
-    <t>Procedure.complicationDetail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Condition|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Eine Diagnose die durch die durchgeführte Prozedur entstanden ist</t>
-  </si>
-  <si>
-    <t>Any complications that occurred during the procedure, or in the immediate post-performance period.</t>
-  </si>
-  <si>
-    <t>This is used to document a condition that is a result of the procedure, not the condition that was the reason for the procedure.</t>
-  </si>
-  <si>
-    <t>Procedure.followUp</t>
-  </si>
-  <si>
-    <t>Nachkontrolle (Code)</t>
-  </si>
-  <si>
-    <t>If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
-  </si>
-  <si>
-    <t>Specific follow up required for a procedure e.g. removal of sutures.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-followup|4.0.1</t>
-  </si>
-  <si>
-    <t>Procedure.note</t>
-  </si>
-  <si>
-    <t>Freitext zur Prozedur für Zusatzinformation</t>
-  </si>
-  <si>
-    <t>Any other notes and comments about the procedure.</t>
-  </si>
-  <si>
-    <t>Procedure.note.id</t>
-  </si>
-  <si>
-    <t>Procedure.note.extension</t>
-  </si>
-  <si>
-    <t>Procedure.note.author[x]</t>
-  </si>
-  <si>
-    <t>Procedure.note.time</t>
-  </si>
-  <si>
-    <t>Procedure.note.text</t>
-  </si>
-  <si>
-    <t>Procedure.focalDevice</t>
-  </si>
-  <si>
-    <t>Prozedurendurchführendes Gerät</t>
-  </si>
-  <si>
-    <t>A device that is implanted, removed or otherwise manipulated (calibration, battery replacement, fitting a prosthesis, attaching a wound-vac, etc.) as a focal portion of the Procedure.</t>
-  </si>
-  <si>
-    <t>Procedure.focalDevice.id</t>
-  </si>
-  <si>
-    <t>Procedure.focalDevice.extension</t>
-  </si>
-  <si>
-    <t>Procedure.focalDevice.modifierExtension</t>
-  </si>
-  <si>
-    <t>Procedure.focalDevice.action</t>
-  </si>
-  <si>
-    <t>Kind of change to device</t>
-  </si>
-  <si>
-    <t>The kind of change that happened to the device during the procedure.</t>
-  </si>
-  <si>
-    <t>A kind of change that happened to the device during the procedure.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/device-action|4.0.1</t>
-  </si>
-  <si>
-    <t>Procedure.focalDevice.manipulated</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Device that was changed</t>
-  </si>
-  <si>
-    <t>The device that was manipulated (changed) during the procedure.</t>
-  </si>
-  <si>
-    <t>Procedure.usedReference</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|Medication|4.0.1|Substance|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Verweis auf verwendete Materialien während der Prozedur (z.b. Medikamente)</t>
-  </si>
-  <si>
-    <t>Identifies medications, devices and any other substance used as part of the procedure.</t>
-  </si>
-  <si>
-    <t>For devices actually implanted or removed, use Procedure.device.</t>
-  </si>
-  <si>
-    <t>Used for tracking contamination, etc.</t>
-  </si>
-  <si>
-    <t>Procedure.usedCode</t>
-  </si>
-  <si>
-    <t>Code der Materialien, die während der Prozedur verwendetet wurden</t>
-  </si>
-  <si>
-    <t>Identifies coded items that were used as part of the procedure.</t>
-  </si>
-  <si>
-    <t>Codes describing items used during a procedure.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/device-kind|4.0.1</t>
-  </si>
-  <si>
-    <t>at-elga-ediag-reaction-time</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reaction-time</t>
-  </si>
-  <si>
-    <t>AtEdiagReactionTime</t>
-  </si>
-  <si>
-    <t>AT ELGA Reaktionszeit</t>
-  </si>
-  <si>
-    <t>element:AllergyIntolerance.reaction</t>
-  </si>
-  <si>
-    <t>at-elga-ediag-reference</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reference</t>
-  </si>
-  <si>
-    <t>AtEdiagReference</t>
-  </si>
-  <si>
-    <t>AT ELGA e-Diagnose Reference</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Reference</t>
-  </si>
-  <si>
-    <t>AT e-Diagnose Reference</t>
-  </si>
-  <si>
-    <t>A reference from one resource to another.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>Reference.id</t>
-  </si>
-  <si>
-    <t>Reference.extension</t>
+    <t>List.entry.item.id</t>
+  </si>
+  <si>
+    <t>List.entry.item.extension</t>
+  </si>
+  <si>
+    <t>List.entry.item.reference</t>
+  </si>
+  <si>
+    <t>Literal reference, Relative, internal or absolute URL</t>
+  </si>
+  <si>
+    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
+  </si>
+  <si>
+    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
   </si>
   <si>
     <t>Reference.reference</t>
-  </si>
-  <si>
-    <t>Literal reference, Relative, internal or absolute URL</t>
-  </si>
-  <si>
-    <t>A reference to a location at which the other resource is found. The reference may be a relative reference, in which case it is relative to the service base URL, or an absolute URL that resolves to the location where the resource is found. The reference may be version specific or not. If the reference is not to a FHIR RESTful server, then it should be assumed to be version specific. Internal fragment references (start with '#') refer to contained resources.</t>
-  </si>
-  <si>
-    <t>Using absolute URLs provides a stable scalable approach suitable for a cloud/web context, while using relative/logical references provides a flexible approach suitable for use when trading across closed eco-system boundaries.   Absolute URLs do not need to point to a FHIR RESTful server, though this is the preferred approach. If the URL conforms to the structure "/[type]/[id]" then it should be assumed that the reference is to a FHIR RESTful server.</t>
   </si>
   <si>
     <t xml:space="preserve">ref-1
 </t>
   </si>
   <si>
-    <t>Reference.type</t>
+    <t>List.entry.item.type</t>
   </si>
   <si>
     <t>Type the reference refers to (e.g. "Patient")</t>
@@ -2780,7 +2162,10 @@
     <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
-    <t>Reference.identifier</t>
+    <t>Reference.type</t>
+  </si>
+  <si>
+    <t>List.entry.item.identifier</t>
   </si>
   <si>
     <t>Logical reference, when literal reference is not known</t>
@@ -2795,16 +2180,661 @@
 Reference is intended to point to a structure that can potentially be expressed as a FHIR resource, though there is no need for it to exist as an actual FHIR resource instance - except in as much as an application wishes to actual find the target of the reference. The content referred to be the identifier must meet the logical constraints implied by any limitations on what resource types are permitted for the reference.  For example, it would not be legitimate to send the identifier for a drug prescription if the type were Reference(Observation|DiagnosticReport).  One of the use-cases for Reference.identifier is the situation where no FHIR representation exists (where the type is Reference (Any).</t>
   </si>
   <si>
+    <t>Reference.identifier</t>
+  </si>
+  <si>
+    <t>List.entry.item.display</t>
+  </si>
+  <si>
+    <t>Text alternative for the resource</t>
+  </si>
+  <si>
+    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
+  </si>
+  <si>
+    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+  </si>
+  <si>
     <t>Reference.display</t>
   </si>
   <si>
-    <t>Text alternative for the resource</t>
-  </si>
-  <si>
-    <t>Plain text narrative that identifies the resource in addition to the resource reference.</t>
-  </si>
-  <si>
-    <t>This is generally not the same as the Resource.text of the referenced resource.  The purpose is to identify what's being referenced, not to fully describe it.</t>
+    <t>List.emptyReason</t>
+  </si>
+  <si>
+    <t>Begründung, warum die Summary-Liste leer ist.</t>
+  </si>
+  <si>
+    <t>If the list is empty, why the list is empty.</t>
+  </si>
+  <si>
+    <t>The various reasons for an empty list make a significant interpretation to its interpretation. Note that this code is for use when the entire list has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
+  </si>
+  <si>
+    <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListEmptyReasonVS</t>
+  </si>
+  <si>
+    <t>at-elga-ediag-procedure</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-procedure</t>
+  </si>
+  <si>
+    <t>AtEdiagProcedure</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Diagnose Procedure</t>
+  </si>
+  <si>
+    <t>Das AT e-Diagnose Procedure-Profil leitet sich vom Procedure-Profil ab und passt dieses für die Anforderungen der e-Diagnose an.</t>
+  </si>
+  <si>
+    <t>Procedure</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Procedure</t>
+  </si>
+  <si>
+    <t>AT e-Diagnose Procedure</t>
+  </si>
+  <si>
+    <t>An action that is or was performed on or for a patient. This can be a physical intervention like an operation, or less invasive like long term services, counseling, or hypnotherapy.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+  </si>
+  <si>
+    <t>Procedure.id</t>
+  </si>
+  <si>
+    <t>Procedure.meta</t>
+  </si>
+  <si>
+    <t>Procedure.implicitRules</t>
+  </si>
+  <si>
+    <t>Procedure.language</t>
+  </si>
+  <si>
+    <t>Procedure.text</t>
+  </si>
+  <si>
+    <t>Procedure.contained</t>
+  </si>
+  <si>
+    <t>Procedure.extension</t>
+  </si>
+  <si>
+    <t>Procedure.extension:reported</t>
+  </si>
+  <si>
+    <t>Procedure.extension:entered-in-error</t>
+  </si>
+  <si>
+    <t>Procedure.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.identifier</t>
+  </si>
+  <si>
+    <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
+  </si>
+  <si>
+    <t>This is a business identifier, not a resource identifier (see [discussion](http://hl7.org/fhir/R4/resource.html#identifiers)).  It is best practice for the identifier to only appear on a single resource instance, however business practices may occasionally dictate that multiple resource instances with the same identifier can exist - possibly even with different resource types.  For example, multiple Patient and Person resource instances might share the same social insurance number.</t>
+  </si>
+  <si>
+    <t>Allows identification of the procedure as it is known by various participating systems and in a way that remains consistent across servers.</t>
+  </si>
+  <si>
+    <t>Procedure.instantiatesCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(PlanDefinition|4.0.1|ActivityDefinition|4.0.1|Measure|4.0.1|OperationDefinition|4.0.1|Questionnaire|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll</t>
+  </si>
+  <si>
+    <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
+  </si>
+  <si>
+    <t>Procedure.instantiatesUri</t>
+  </si>
+  <si>
+    <t>Verweis auf ein externes Dokument</t>
+  </si>
+  <si>
+    <t>The URL pointing to an externally maintained protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
+  </si>
+  <si>
+    <t>This might be an HTML page, PDF, etc. or could just be a non-resolvable URI identifier.</t>
+  </si>
+  <si>
+    <t>Procedure.basedOn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fulfills
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Verweis auf eine Anforderung</t>
+  </si>
+  <si>
+    <t>A reference to a resource that contains details of the request for this procedure.</t>
+  </si>
+  <si>
+    <t>Procedure.partOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">container
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Procedure|4.0.1|Observation|4.0.1|MedicationAdministration|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Verweis der Ressource auf eine andere, übergreordnete Ressource</t>
+  </si>
+  <si>
+    <t>A larger event of which this particular procedure is a component or step.</t>
+  </si>
+  <si>
+    <t>The MedicationAdministration resource has a partOf reference to Procedure, but this is not a circular reference.   For example, the anesthesia MedicationAdministration is part of the surgical Procedure (MedicationAdministration.partOf = Procedure).  For example, the procedure to insert the IV port for an IV medication administration is part of the medication administration (Procedure.partOf = MedicationAdministration).</t>
+  </si>
+  <si>
+    <t>Procedure.status</t>
+  </si>
+  <si>
+    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren</t>
+  </si>
+  <si>
+    <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
+  </si>
+  <si>
+    <t>The "unknown" code is not to be used to convey other statuses.  The "unknown" code should be used when one of the statuses applies, but the authoring system doesn't know the current state of the procedure.
+This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-procedure-status</t>
+  </si>
+  <si>
+    <t>Procedure.statusReason</t>
+  </si>
+  <si>
+    <t>Suspended Reason
+Cancelled Reason</t>
+  </si>
+  <si>
+    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung</t>
+  </si>
+  <si>
+    <t>Captures the reason for the current state of the procedure.</t>
+  </si>
+  <si>
+    <t>This is generally only used for "exception" statuses such as "not-done", "suspended" or "aborted". The reason for performing the event at all is captured in reasonCode, not here.</t>
+  </si>
+  <si>
+    <t>A code that identifies the reason a procedure was not performed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-not-performed-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>Procedure.category</t>
+  </si>
+  <si>
+    <t>Kategorisierung nach Verfahren</t>
+  </si>
+  <si>
+    <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
+  </si>
+  <si>
+    <t>A code that classifies a procedure for searching, sorting and display purposes.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-category|4.0.1</t>
+  </si>
+  <si>
+    <t>Procedure.code</t>
+  </si>
+  <si>
+    <t>Prozedurencode der durchgeführten Prozedur</t>
+  </si>
+  <si>
+    <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-prozeduren-codes</t>
+  </si>
+  <si>
+    <t>Procedure.code.id</t>
+  </si>
+  <si>
+    <t>Procedure.code.extension</t>
+  </si>
+  <si>
+    <t>Procedure.code.coding</t>
+  </si>
+  <si>
+    <t>Procedure.code.text</t>
+  </si>
+  <si>
+    <t>Procedure.subject</t>
+  </si>
+  <si>
+    <t>Person, auf die sich die Prozedur bezieht</t>
+  </si>
+  <si>
+    <t>The person, animal or group on which the procedure was performed.</t>
+  </si>
+  <si>
+    <t>Procedure.encounter</t>
+  </si>
+  <si>
+    <t>The Encounter during which this Procedure was created or performed or to which the creation of this record is tightly associated.</t>
+  </si>
+  <si>
+    <t>This will typically be the encounter the event occurred within, but some activities may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter.</t>
+  </si>
+  <si>
+    <t>Procedure.performed[x]</t>
+  </si>
+  <si>
+    <t>Zeitpunkt der Durchführung</t>
+  </si>
+  <si>
+    <t>Estimated or actual date, date-time, period, or age when the procedure was performed.  Allows a period to support complex procedures that span more than one date, and also allows for the length of the procedure to be captured.</t>
+  </si>
+  <si>
+    <t>Age is generally used when the patient reports an age at which the procedure was performed. Range is generally used when the patient reports an age range when the procedure was performed, such as sometime between 20-25 years old.  dateTime supports a range of precision due to some procedures being reported as past procedures that might not have millisecond precision while other procedures performed and documented during the encounter might have more precise UTC timestamps with timezone.</t>
+  </si>
+  <si>
+    <t>Procedure.recorder</t>
+  </si>
+  <si>
+    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen/dokumentiert hat</t>
+  </si>
+  <si>
+    <t>Procedure.asserter</t>
+  </si>
+  <si>
+    <t>Quelle der Information zur Prozedur (z. B. behandelnde Person, Patient oder Dritter)</t>
+  </si>
+  <si>
+    <t>Individual who is making the procedure statement.</t>
+  </si>
+  <si>
+    <t>Procedure.performer</t>
+  </si>
+  <si>
+    <t>Diese Person hat die Prozedur durchgeführt</t>
+  </si>
+  <si>
+    <t>Limited to "real" people rather than equipment.</t>
+  </si>
+  <si>
+    <t>Procedure.performer.id</t>
+  </si>
+  <si>
+    <t>Procedure.performer.extension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.performer.function</t>
+  </si>
+  <si>
+    <t>Type of performance</t>
+  </si>
+  <si>
+    <t>Distinguishes the type of involvement of the performer in the procedure. For example, surgeon, anaesthetist, endoscopist.</t>
+  </si>
+  <si>
+    <t>Allows disambiguation of the types of involvement of different performers.</t>
+  </si>
+  <si>
+    <t>A code that identifies the role of a performer of the procedure.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/performer-role|4.0.1</t>
+  </si>
+  <si>
+    <t>Procedure.performer.actor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Device|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>The reference to the practitioner</t>
+  </si>
+  <si>
+    <t>The practitioner who was involved in the procedure.</t>
+  </si>
+  <si>
+    <t>A reference to Device supports use cases, such as pacemakers.</t>
+  </si>
+  <si>
+    <t>Procedure.performer.onBehalfOf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Organization the device or practitioner was acting for</t>
+  </si>
+  <si>
+    <t>The organization the device or practitioner was acting on behalf of.</t>
+  </si>
+  <si>
+    <t>Practitioners and Devices can be associated with multiple organizations.  This element indicates which organization they were acting on behalf of when performing the action.</t>
+  </si>
+  <si>
+    <t>Procedure.location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Location|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Durchführungsort</t>
+  </si>
+  <si>
+    <t>The location where the procedure actually happened.  E.g. a newborn at home, a tracheostomy at a restaurant.</t>
+  </si>
+  <si>
+    <t>Ties a procedure to where the records are likely kept.</t>
+  </si>
+  <si>
+    <t>Procedure.reasonCode</t>
+  </si>
+  <si>
+    <t>Code, des med. Grundes für die Durchführung der Prozedur</t>
+  </si>
+  <si>
+    <t>The coded reason why the procedure was performed. This may be a coded entity of some type, or may simply be present as text.</t>
+  </si>
+  <si>
+    <t>Use Procedure.reasonCode when a code sufficiently describes the reason.  Use Procedure.reasonReference when referencing a resource, which allows more information to be conveyed, such as onset date. Procedure.reasonCode and Procedure.reasonReference are not meant to be duplicative.  For a single reason, either Procedure.reasonCode or Procedure.reasonReference can be used.  Procedure.reasonCode may be a summary code, or Procedure.reasonReference may be used to reference a very precise definition of the reason using Condition | Observation | Procedure | DiagnosticReport | DocumentReference.  Both Procedure.reasonCode and Procedure.reasonReference can be used if they are describing different reasons for the procedure.</t>
+  </si>
+  <si>
+    <t>A code that identifies the reason a procedure is  required.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
+  </si>
+  <si>
+    <t>Procedure.reasonReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|Procedure|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Begründung dass die Prozedur durchgeführt worden ist - Verweis auf eine andere R. wie Condition, Observation,...</t>
+  </si>
+  <si>
+    <t>The justification of why the procedure was performed.</t>
+  </si>
+  <si>
+    <t>It is possible for a procedure to be a reason (such as C-Section) for another procedure (such as an epidural). Other examples include endoscopy for dilatation and biopsy (a combination of diagnostic and therapeutic use). 
+Use Procedure.reasonCode when a code sufficiently describes the reason.  Use Procedure.reasonReference when referencing a resource, which allows more information to be conveyed, such as onset date. Procedure.reasonCode and Procedure.reasonReference are not meant to be duplicative.  For a single reason, either Procedure.reasonCode or Procedure.reasonReference can be used.  Procedure.reasonCode may be a summary code, or Procedure.reasonReference may be used to reference a very precise definition of the reason using Condition | Observation | Procedure | DiagnosticReport | DocumentReference.  Both Procedure.reasonCode and Procedure.reasonReference can be used if they are describing different reasons for the procedure.</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite</t>
+  </si>
+  <si>
+    <t>Betroffene Körperstelle</t>
+  </si>
+  <si>
+    <t>Detailed and structured anatomical location information. Multiple locations are allowed - e.g. multiple punch biopsies of a lesion.</t>
+  </si>
+  <si>
+    <t>If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [procedure-targetbodystructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
+  </si>
+  <si>
+    <t>Procedure.outcome</t>
+  </si>
+  <si>
+    <t>Ergebnis der Prozedur</t>
+  </si>
+  <si>
+    <t>The outcome of the procedure - did it resolve the reasons for the procedure being performed?</t>
+  </si>
+  <si>
+    <t>If outcome contains narrative text only, it can be captured using the CodeableConcept.text.</t>
+  </si>
+  <si>
+    <t>An outcome of a procedure - whether it was resolved or otherwise.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-outcome|4.0.1</t>
+  </si>
+  <si>
+    <t>Procedure.report</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DiagnosticReport|4.0.1|DocumentReference|4.0.1|Composition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>This could be a histology result, pathology report, surgical report, etc.</t>
+  </si>
+  <si>
+    <t>There could potentially be multiple reports - e.g. if this was a procedure which took multiple biopsies resulting in a number of anatomical pathology reports.</t>
+  </si>
+  <si>
+    <t>Procedure.complication</t>
+  </si>
+  <si>
+    <t>Komplikation/en während dem Eingriff</t>
+  </si>
+  <si>
+    <t>Any complications that occurred during the procedure, or in the immediate post-performance period. These are generally tracked separately from the notes, which will typically describe the procedure itself rather than any 'post procedure' issues.</t>
+  </si>
+  <si>
+    <t>If complications are only expressed by the narrative text, they can be captured using the CodeableConcept.text.</t>
+  </si>
+  <si>
+    <t>Codes describing complications that resulted from a procedure.</t>
+  </si>
+  <si>
+    <t>Procedure.complicationDetail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Condition|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Eine Diagnose die durch die durchgeführte Prozedur entstanden ist</t>
+  </si>
+  <si>
+    <t>Any complications that occurred during the procedure, or in the immediate post-performance period.</t>
+  </si>
+  <si>
+    <t>This is used to document a condition that is a result of the procedure, not the condition that was the reason for the procedure.</t>
+  </si>
+  <si>
+    <t>Procedure.followUp</t>
+  </si>
+  <si>
+    <t>Nachkontrolle (Code)</t>
+  </si>
+  <si>
+    <t>If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
+  </si>
+  <si>
+    <t>Specific follow up required for a procedure e.g. removal of sutures.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/procedure-followup|4.0.1</t>
+  </si>
+  <si>
+    <t>Procedure.note</t>
+  </si>
+  <si>
+    <t>Freitext zur Prozedur für Zusatzinformation</t>
+  </si>
+  <si>
+    <t>Any other notes and comments about the procedure.</t>
+  </si>
+  <si>
+    <t>Procedure.note.id</t>
+  </si>
+  <si>
+    <t>Procedure.note.extension</t>
+  </si>
+  <si>
+    <t>Procedure.note.author[x]</t>
+  </si>
+  <si>
+    <t>Procedure.note.time</t>
+  </si>
+  <si>
+    <t>Procedure.note.text</t>
+  </si>
+  <si>
+    <t>Procedure.focalDevice</t>
+  </si>
+  <si>
+    <t>Prozedurendurchführendes Gerät</t>
+  </si>
+  <si>
+    <t>A device that is implanted, removed or otherwise manipulated (calibration, battery replacement, fitting a prosthesis, attaching a wound-vac, etc.) as a focal portion of the Procedure.</t>
+  </si>
+  <si>
+    <t>Procedure.focalDevice.id</t>
+  </si>
+  <si>
+    <t>Procedure.focalDevice.extension</t>
+  </si>
+  <si>
+    <t>Procedure.focalDevice.modifierExtension</t>
+  </si>
+  <si>
+    <t>Procedure.focalDevice.action</t>
+  </si>
+  <si>
+    <t>Kind of change to device</t>
+  </si>
+  <si>
+    <t>The kind of change that happened to the device during the procedure.</t>
+  </si>
+  <si>
+    <t>A kind of change that happened to the device during the procedure.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/device-action|4.0.1</t>
+  </si>
+  <si>
+    <t>Procedure.focalDevice.manipulated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Device that was changed</t>
+  </si>
+  <si>
+    <t>The device that was manipulated (changed) during the procedure.</t>
+  </si>
+  <si>
+    <t>Procedure.usedReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|4.0.1|Medication|4.0.1|Substance|4.0.1)
+</t>
+  </si>
+  <si>
+    <t>Verweis auf verwendete Materialien während der Prozedur (z.b. Medikamente)</t>
+  </si>
+  <si>
+    <t>Identifies medications, devices and any other substance used as part of the procedure.</t>
+  </si>
+  <si>
+    <t>For devices actually implanted or removed, use Procedure.device.</t>
+  </si>
+  <si>
+    <t>Used for tracking contamination, etc.</t>
+  </si>
+  <si>
+    <t>Procedure.usedCode</t>
+  </si>
+  <si>
+    <t>Code der Materialien, die während der Prozedur verwendetet wurden</t>
+  </si>
+  <si>
+    <t>Identifies coded items that were used as part of the procedure.</t>
+  </si>
+  <si>
+    <t>Codes describing items used during a procedure.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/device-kind|4.0.1</t>
+  </si>
+  <si>
+    <t>at-elga-ediag-reaction-time</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reaction-time</t>
+  </si>
+  <si>
+    <t>AtEdiagReactionTime</t>
+  </si>
+  <si>
+    <t>AT ELGA Reaktionszeit</t>
+  </si>
+  <si>
+    <t>element:AllergyIntolerance.reaction</t>
+  </si>
+  <si>
+    <t>at-elga-ediag-reference</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reference</t>
+  </si>
+  <si>
+    <t>AtEdiagReference</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Diagnose Reference</t>
+  </si>
+  <si>
+    <t>Reference</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/Reference</t>
+  </si>
+  <si>
+    <t>AT e-Diagnose Reference</t>
+  </si>
+  <si>
+    <t>A reference from one resource to another.</t>
+  </si>
+  <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>Reference.id</t>
+  </si>
+  <si>
+    <t>Reference.extension</t>
   </si>
   <si>
     <t>at-elga-ediag-reported</t>
@@ -3674,7 +3704,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
     </row>
     <row r="94">
@@ -3682,7 +3712,7 @@
         <v>4</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>679</v>
+        <v>707</v>
       </c>
     </row>
     <row r="95">
@@ -3698,7 +3728,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>680</v>
+        <v>708</v>
       </c>
     </row>
     <row r="97">
@@ -3706,7 +3736,7 @@
         <v>10</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>681</v>
+        <v>709</v>
       </c>
     </row>
     <row r="98">
@@ -3768,7 +3798,7 @@
         <v>24</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>682</v>
+        <v>710</v>
       </c>
     </row>
     <row r="106">
@@ -3804,7 +3834,7 @@
         <v>32</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>683</v>
+        <v>711</v>
       </c>
     </row>
     <row r="111">
@@ -3812,7 +3842,7 @@
         <v>34</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>684</v>
+        <v>712</v>
       </c>
     </row>
     <row r="112">
@@ -3844,7 +3874,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>862</v>
+        <v>890</v>
       </c>
     </row>
     <row r="116">
@@ -3852,7 +3882,7 @@
         <v>4</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>863</v>
+        <v>891</v>
       </c>
     </row>
     <row r="117">
@@ -3868,7 +3898,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>864</v>
+        <v>892</v>
       </c>
     </row>
     <row r="119">
@@ -3876,7 +3906,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>865</v>
+        <v>893</v>
       </c>
     </row>
     <row r="120">
@@ -4006,7 +4036,7 @@
         <v>530</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>866</v>
+        <v>894</v>
       </c>
     </row>
     <row r="137">
@@ -4022,7 +4052,7 @@
         <v>2</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>867</v>
+        <v>895</v>
       </c>
     </row>
     <row r="139">
@@ -4030,7 +4060,7 @@
         <v>4</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>868</v>
+        <v>896</v>
       </c>
     </row>
     <row r="140">
@@ -4046,7 +4076,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>869</v>
+        <v>897</v>
       </c>
     </row>
     <row r="142">
@@ -4054,7 +4084,7 @@
         <v>10</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>870</v>
+        <v>898</v>
       </c>
     </row>
     <row r="143">
@@ -4152,7 +4182,7 @@
         <v>32</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>871</v>
+        <v>899</v>
       </c>
     </row>
     <row r="156">
@@ -4160,7 +4190,7 @@
         <v>34</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>872</v>
+        <v>900</v>
       </c>
     </row>
     <row r="157">
@@ -4192,7 +4222,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>898</v>
+        <v>907</v>
       </c>
     </row>
     <row r="161">
@@ -4200,7 +4230,7 @@
         <v>4</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>899</v>
+        <v>908</v>
       </c>
     </row>
     <row r="162">
@@ -4216,7 +4246,7 @@
         <v>8</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>900</v>
+        <v>909</v>
       </c>
     </row>
     <row r="164">
@@ -4354,7 +4384,7 @@
         <v>530</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>901</v>
+        <v>910</v>
       </c>
     </row>
   </sheetData>
@@ -4364,7 +4394,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK237"/>
+  <dimension ref="A1:AK243"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="27.57421875" customWidth="true" bestFit="true"/>
@@ -19163,10 +19193,10 @@
       </c>
       <c r="F142" s="2"/>
       <c r="G142" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H142" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I142" t="s" s="2">
         <v>23</v>
@@ -19298,7 +19328,7 @@
       </c>
       <c r="R143" s="2"/>
       <c r="S143" t="s" s="2">
-        <v>23</v>
+        <v>594</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>23</v>
@@ -19318,9 +19348,11 @@
       <c r="Y143" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="Z143" s="2"/>
+      <c r="Z143" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="AA143" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AB143" t="s" s="2">
         <v>23</v>
@@ -19358,10 +19390,10 @@
         <v>567</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -19387,23 +19419,23 @@
         <v>105</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="P144" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="Q144" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R144" s="2"/>
       <c r="S144" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>23</v>
@@ -19424,10 +19456,10 @@
         <v>164</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="AA144" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AB144" t="s" s="2">
         <v>23</v>
@@ -19445,7 +19477,7 @@
         <v>23</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>85</v>
@@ -19465,10 +19497,10 @@
         <v>567</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -19494,14 +19526,14 @@
         <v>203</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="Q145" t="s" s="2">
         <v>23</v>
@@ -19514,7 +19546,7 @@
         <v>23</v>
       </c>
       <c r="U145" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="V145" t="s" s="2">
         <v>23</v>
@@ -19550,7 +19582,7 @@
         <v>23</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>77</v>
@@ -19570,10 +19602,10 @@
         <v>567</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -19599,16 +19631,16 @@
         <v>160</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="P146" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="Q146" t="s" s="2">
         <v>23</v>
@@ -19637,7 +19669,7 @@
       </c>
       <c r="Z146" s="2"/>
       <c r="AA146" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AB146" t="s" s="2">
         <v>23</v>
@@ -19655,7 +19687,7 @@
         <v>23</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>77</v>
@@ -19675,10 +19707,10 @@
         <v>567</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -19704,16 +19736,16 @@
         <v>227</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="P147" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="Q147" t="s" s="2">
         <v>23</v>
@@ -19762,7 +19794,7 @@
         <v>23</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>77</v>
@@ -19782,10 +19814,10 @@
         <v>567</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -19811,10 +19843,10 @@
         <v>231</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
@@ -19865,7 +19897,7 @@
         <v>23</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>77</v>
@@ -19885,10 +19917,10 @@
         <v>567</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -19914,16 +19946,16 @@
         <v>239</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="P149" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="Q149" t="s" s="2">
         <v>23</v>
@@ -19972,7 +20004,7 @@
         <v>23</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>77</v>
@@ -19992,10 +20024,10 @@
         <v>567</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -20018,19 +20050,19 @@
         <v>86</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="P150" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="Q150" t="s" s="2">
         <v>23</v>
@@ -20079,7 +20111,7 @@
         <v>23</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>77</v>
@@ -20099,10 +20131,10 @@
         <v>567</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -20128,16 +20160,16 @@
         <v>160</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="P151" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="Q151" t="s" s="2">
         <v>23</v>
@@ -20165,10 +20197,10 @@
         <v>109</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="AA151" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="AB151" t="s" s="2">
         <v>23</v>
@@ -20186,7 +20218,7 @@
         <v>23</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>77</v>
@@ -20206,10 +20238,10 @@
         <v>567</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -20235,10 +20267,10 @@
         <v>258</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -20289,7 +20321,7 @@
         <v>23</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>77</v>
@@ -20309,10 +20341,10 @@
         <v>567</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -20338,13 +20370,13 @@
         <v>263</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="P153" s="2"/>
       <c r="Q153" t="s" s="2">
@@ -20394,7 +20426,7 @@
         <v>23</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>77</v>
@@ -20403,7 +20435,7 @@
         <v>78</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>97</v>
@@ -20414,10 +20446,10 @@
         <v>567</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -20517,10 +20549,10 @@
         <v>567</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -20622,10 +20654,10 @@
         <v>567</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -20729,10 +20761,10 @@
         <v>567</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -20758,16 +20790,16 @@
         <v>160</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="P157" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="Q157" t="s" s="2">
         <v>23</v>
@@ -20795,10 +20827,10 @@
         <v>199</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="AA157" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="AB157" t="s" s="2">
         <v>23</v>
@@ -20816,7 +20848,7 @@
         <v>23</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>77</v>
@@ -20836,10 +20868,10 @@
         <v>567</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -20865,68 +20897,68 @@
         <v>428</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="N158" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="P158" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="Q158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R158" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG158" t="s" s="2">
         <v>660</v>
       </c>
-      <c r="O158" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="P158" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="Q158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R158" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>658</v>
-      </c>
       <c r="AH158" t="s" s="2">
         <v>77</v>
       </c>
@@ -20934,7 +20966,7 @@
         <v>85</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>97</v>
@@ -20945,10 +20977,10 @@
         <v>567</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -20974,14 +21006,14 @@
         <v>239</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="Q159" t="s" s="2">
         <v>23</v>
@@ -21030,7 +21062,7 @@
         <v>23</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>77</v>
@@ -21050,10 +21082,10 @@
         <v>567</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -21076,13 +21108,13 @@
         <v>23</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>513</v>
+        <v>672</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
@@ -21133,7 +21165,7 @@
         <v>23</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>85</v>
@@ -21153,10 +21185,10 @@
         <v>567</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -21170,7 +21202,7 @@
         <v>85</v>
       </c>
       <c r="I161" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="J161" t="s" s="2">
         <v>23</v>
@@ -21179,20 +21211,16 @@
         <v>23</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>673</v>
+        <v>204</v>
       </c>
       <c r="N161" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="O161" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="P161" t="s" s="2">
-        <v>676</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="O161" s="2"/>
+      <c r="P161" s="2"/>
       <c r="Q161" t="s" s="2">
         <v>23</v>
       </c>
@@ -21216,11 +21244,13 @@
         <v>23</v>
       </c>
       <c r="Y161" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Z161" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z161" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AA161" t="s" s="2">
-        <v>677</v>
+        <v>23</v>
       </c>
       <c r="AB161" t="s" s="2">
         <v>23</v>
@@ -21238,7 +21268,7 @@
         <v>23</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>672</v>
+        <v>206</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>77</v>
@@ -21247,25 +21277,25 @@
         <v>85</v>
       </c>
       <c r="AJ161" t="s" s="2">
-        <v>647</v>
+        <v>23</v>
       </c>
       <c r="AK161" t="s" s="2">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>678</v>
+        <v>567</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>683</v>
+        <v>676</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="F162" s="2"/>
       <c r="G162" t="s" s="2">
@@ -21284,15 +21314,17 @@
         <v>23</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>685</v>
+        <v>208</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>686</v>
-      </c>
-      <c r="O162" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O162" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P162" s="2"/>
       <c r="Q162" t="s" s="2">
         <v>23</v>
@@ -21329,19 +21361,19 @@
         <v>23</v>
       </c>
       <c r="AC162" t="s" s="2">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="AD162" t="s" s="2">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="AE162" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>683</v>
+        <v>211</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>77</v>
@@ -21353,18 +21385,18 @@
         <v>23</v>
       </c>
       <c r="AK162" t="s" s="2">
-        <v>687</v>
+        <v>134</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>678</v>
+        <v>567</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -21372,7 +21404,7 @@
       </c>
       <c r="F163" s="2"/>
       <c r="G163" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H163" t="s" s="2">
         <v>85</v>
@@ -21387,16 +21419,16 @@
         <v>86</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>88</v>
+        <v>678</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>89</v>
+        <v>679</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>90</v>
+        <v>680</v>
       </c>
       <c r="P163" s="2"/>
       <c r="Q163" t="s" s="2">
@@ -21446,7 +21478,7 @@
         <v>23</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>91</v>
+        <v>681</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>77</v>
@@ -21455,21 +21487,21 @@
         <v>85</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>23</v>
+        <v>682</v>
       </c>
       <c r="AK163" t="s" s="2">
-        <v>23</v>
+        <v>97</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>678</v>
+        <v>567</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -21492,15 +21524,17 @@
         <v>86</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>94</v>
+        <v>684</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="O164" s="2"/>
+        <v>685</v>
+      </c>
+      <c r="O164" t="s" s="2">
+        <v>686</v>
+      </c>
       <c r="P164" s="2"/>
       <c r="Q164" t="s" s="2">
         <v>23</v>
@@ -21525,13 +21559,13 @@
         <v>23</v>
       </c>
       <c r="Y164" t="s" s="2">
-        <v>23</v>
+        <v>374</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>23</v>
+        <v>687</v>
       </c>
       <c r="AA164" t="s" s="2">
-        <v>23</v>
+        <v>688</v>
       </c>
       <c r="AB164" t="s" s="2">
         <v>23</v>
@@ -21549,7 +21583,7 @@
         <v>23</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>96</v>
+        <v>689</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>77</v>
@@ -21566,7 +21600,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>678</v>
+        <v>567</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>690</v>
@@ -21589,22 +21623,22 @@
         <v>23</v>
       </c>
       <c r="J165" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="K165" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>99</v>
+        <v>154</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>100</v>
+        <v>691</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>101</v>
+        <v>692</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>102</v>
+        <v>693</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
@@ -21654,7 +21688,7 @@
         <v>23</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>103</v>
+        <v>694</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>77</v>
@@ -21671,13 +21705,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>678</v>
+        <v>567</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -21697,19 +21731,19 @@
         <v>23</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>105</v>
+        <v>203</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>106</v>
+        <v>696</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>107</v>
+        <v>697</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>108</v>
+        <v>698</v>
       </c>
       <c r="P166" s="2"/>
       <c r="Q166" t="s" s="2">
@@ -21735,13 +21769,13 @@
         <v>23</v>
       </c>
       <c r="Y166" t="s" s="2">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="Z166" t="s" s="2">
-        <v>110</v>
+        <v>23</v>
       </c>
       <c r="AA166" t="s" s="2">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="AB166" t="s" s="2">
         <v>23</v>
@@ -21759,7 +21793,7 @@
         <v>23</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>112</v>
+        <v>699</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>77</v>
@@ -21776,17 +21810,17 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>678</v>
+        <v>567</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
-        <v>114</v>
+        <v>23</v>
       </c>
       <c r="F167" s="2"/>
       <c r="G167" t="s" s="2">
@@ -21796,7 +21830,7 @@
         <v>85</v>
       </c>
       <c r="I167" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="J167" t="s" s="2">
         <v>23</v>
@@ -21805,18 +21839,20 @@
         <v>23</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>116</v>
+        <v>701</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>117</v>
+        <v>702</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="P167" s="2"/>
+        <v>703</v>
+      </c>
+      <c r="P167" t="s" s="2">
+        <v>704</v>
+      </c>
       <c r="Q167" t="s" s="2">
         <v>23</v>
       </c>
@@ -21840,13 +21876,11 @@
         <v>23</v>
       </c>
       <c r="Y167" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z167" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Z167" s="2"/>
       <c r="AA167" t="s" s="2">
-        <v>23</v>
+        <v>705</v>
       </c>
       <c r="AB167" t="s" s="2">
         <v>23</v>
@@ -21864,7 +21898,7 @@
         <v>23</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>119</v>
+        <v>700</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>77</v>
@@ -21873,7 +21907,7 @@
         <v>85</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>23</v>
+        <v>649</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>97</v>
@@ -21881,17 +21915,17 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>693</v>
+        <v>711</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>693</v>
+        <v>711</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="F168" s="2"/>
       <c r="G168" t="s" s="2">
@@ -21910,17 +21944,15 @@
         <v>23</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>123</v>
+        <v>713</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="O168" t="s" s="2">
-        <v>125</v>
-      </c>
+        <v>714</v>
+      </c>
+      <c r="O168" s="2"/>
       <c r="P168" s="2"/>
       <c r="Q168" t="s" s="2">
         <v>23</v>
@@ -21969,7 +22001,7 @@
         <v>23</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>126</v>
+        <v>711</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>77</v>
@@ -21981,18 +22013,18 @@
         <v>23</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>23</v>
+        <v>715</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>694</v>
+        <v>716</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>694</v>
+        <v>716</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -22003,7 +22035,7 @@
         <v>77</v>
       </c>
       <c r="H169" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I169" t="s" s="2">
         <v>23</v>
@@ -22012,18 +22044,20 @@
         <v>23</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O169" s="2"/>
+        <v>89</v>
+      </c>
+      <c r="O169" t="s" s="2">
+        <v>90</v>
+      </c>
       <c r="P169" s="2"/>
       <c r="Q169" t="s" s="2">
         <v>23</v>
@@ -22060,44 +22094,44 @@
         <v>23</v>
       </c>
       <c r="AC169" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AD169" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="AD169" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AE169" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>133</v>
+        <v>91</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI169" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ169" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK169" t="s" s="2">
-        <v>134</v>
+        <v>23</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>695</v>
+        <v>717</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="D170" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>717</v>
+      </c>
+      <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
         <v>23</v>
       </c>
@@ -22115,16 +22149,16 @@
         <v>23</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>137</v>
+        <v>93</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>138</v>
+        <v>94</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>139</v>
+        <v>95</v>
       </c>
       <c r="O170" s="2"/>
       <c r="P170" s="2"/>
@@ -22175,34 +22209,32 @@
         <v>23</v>
       </c>
       <c r="AG170" t="s" s="2">
-        <v>133</v>
+        <v>96</v>
       </c>
       <c r="AH170" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI170" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ170" t="s" s="2">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="AK170" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>696</v>
+        <v>718</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="D171" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>718</v>
+      </c>
+      <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
         <v>23</v>
       </c>
@@ -22217,21 +22249,23 @@
         <v>23</v>
       </c>
       <c r="J171" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>143</v>
+        <v>99</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>144</v>
+        <v>100</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="O171" s="2"/>
+        <v>101</v>
+      </c>
+      <c r="O171" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="P171" s="2"/>
       <c r="Q171" t="s" s="2">
         <v>23</v>
@@ -22280,66 +22314,64 @@
         <v>23</v>
       </c>
       <c r="AG171" t="s" s="2">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="AH171" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI171" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ171" t="s" s="2">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="AK171" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>697</v>
+        <v>719</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="F172" s="2"/>
       <c r="G172" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H172" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I172" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J172" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="K172" t="s" s="2">
         <v>23</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>148</v>
+        <v>106</v>
       </c>
       <c r="N172" t="s" s="2">
-        <v>149</v>
+        <v>107</v>
       </c>
       <c r="O172" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P172" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="P172" s="2"/>
       <c r="Q172" t="s" s="2">
         <v>23</v>
       </c>
@@ -22363,13 +22395,13 @@
         <v>23</v>
       </c>
       <c r="Y172" t="s" s="2">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="Z172" t="s" s="2">
-        <v>23</v>
+        <v>110</v>
       </c>
       <c r="AA172" t="s" s="2">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="AB172" t="s" s="2">
         <v>23</v>
@@ -22387,41 +22419,41 @@
         <v>23</v>
       </c>
       <c r="AG172" t="s" s="2">
-        <v>152</v>
+        <v>112</v>
       </c>
       <c r="AH172" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI172" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ172" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK172" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>698</v>
+        <v>720</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>698</v>
+        <v>720</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
-        <v>23</v>
+        <v>114</v>
       </c>
       <c r="F173" s="2"/>
       <c r="G173" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H173" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I173" t="s" s="2">
         <v>23</v>
@@ -22430,23 +22462,21 @@
         <v>23</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>154</v>
+        <v>115</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>353</v>
+        <v>116</v>
       </c>
       <c r="N173" t="s" s="2">
-        <v>699</v>
+        <v>117</v>
       </c>
       <c r="O173" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="P173" t="s" s="2">
-        <v>701</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="P173" s="2"/>
       <c r="Q173" t="s" s="2">
         <v>23</v>
       </c>
@@ -22494,13 +22524,13 @@
         <v>23</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>698</v>
+        <v>119</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI173" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ173" t="s" s="2">
         <v>23</v>
@@ -22511,24 +22541,24 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>702</v>
+        <v>721</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>702</v>
+        <v>721</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="F174" s="2"/>
       <c r="G174" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H174" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I174" t="s" s="2">
         <v>23</v>
@@ -22537,18 +22567,20 @@
         <v>23</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>703</v>
+        <v>122</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>704</v>
+        <v>123</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="O174" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="O174" t="s" s="2">
+        <v>125</v>
+      </c>
       <c r="P174" s="2"/>
       <c r="Q174" t="s" s="2">
         <v>23</v>
@@ -22597,7 +22629,7 @@
         <v>23</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>702</v>
+        <v>126</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>77</v>
@@ -22609,18 +22641,18 @@
         <v>23</v>
       </c>
       <c r="AK174" t="s" s="2">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>706</v>
+        <v>722</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -22631,7 +22663,7 @@
         <v>77</v>
       </c>
       <c r="H175" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I175" t="s" s="2">
         <v>23</v>
@@ -22640,20 +22672,18 @@
         <v>23</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>99</v>
+        <v>128</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>707</v>
+        <v>129</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="O175" t="s" s="2">
-        <v>709</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O175" s="2"/>
       <c r="P175" s="2"/>
       <c r="Q175" t="s" s="2">
         <v>23</v>
@@ -22690,19 +22720,17 @@
         <v>23</v>
       </c>
       <c r="AC175" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD175" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>131</v>
+      </c>
+      <c r="AD175" s="2"/>
       <c r="AE175" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>706</v>
+        <v>133</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>77</v>
@@ -22714,29 +22742,31 @@
         <v>23</v>
       </c>
       <c r="AK175" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>710</v>
+        <v>723</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="D176" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="D176" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="E176" t="s" s="2">
-        <v>711</v>
+        <v>23</v>
       </c>
       <c r="F176" s="2"/>
       <c r="G176" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H176" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I176" t="s" s="2">
         <v>23</v>
@@ -22745,16 +22775,16 @@
         <v>23</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>712</v>
+        <v>137</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>713</v>
+        <v>138</v>
       </c>
       <c r="N176" t="s" s="2">
-        <v>714</v>
+        <v>139</v>
       </c>
       <c r="O176" s="2"/>
       <c r="P176" s="2"/>
@@ -22805,7 +22835,7 @@
         <v>23</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>710</v>
+        <v>133</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>77</v>
@@ -22814,32 +22844,34 @@
         <v>78</v>
       </c>
       <c r="AJ176" t="s" s="2">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="AK176" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>715</v>
+        <v>724</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="D177" s="2"/>
+        <v>722</v>
+      </c>
+      <c r="D177" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="E177" t="s" s="2">
-        <v>716</v>
+        <v>23</v>
       </c>
       <c r="F177" s="2"/>
       <c r="G177" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H177" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I177" t="s" s="2">
         <v>23</v>
@@ -22848,20 +22880,18 @@
         <v>23</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>717</v>
+        <v>143</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>718</v>
+        <v>144</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>720</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="O177" s="2"/>
       <c r="P177" s="2"/>
       <c r="Q177" t="s" s="2">
         <v>23</v>
@@ -22910,7 +22940,7 @@
         <v>23</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>715</v>
+        <v>133</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>77</v>
@@ -22919,55 +22949,57 @@
         <v>78</v>
       </c>
       <c r="AJ177" t="s" s="2">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="AK177" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="F178" s="2"/>
       <c r="G178" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H178" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I178" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="J178" t="s" s="2">
         <v>86</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>722</v>
+        <v>148</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>723</v>
+        <v>149</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="P178" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="P178" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="Q178" t="s" s="2">
         <v>23</v>
       </c>
@@ -22991,11 +23023,13 @@
         <v>23</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Z178" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z178" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AA178" t="s" s="2">
-        <v>725</v>
+        <v>23</v>
       </c>
       <c r="AB178" t="s" s="2">
         <v>23</v>
@@ -23013,24 +23047,24 @@
         <v>23</v>
       </c>
       <c r="AG178" t="s" s="2">
-        <v>721</v>
+        <v>152</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI178" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ178" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK178" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>726</v>
@@ -23040,14 +23074,14 @@
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
-        <v>727</v>
+        <v>23</v>
       </c>
       <c r="F179" s="2"/>
       <c r="G179" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H179" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I179" t="s" s="2">
         <v>23</v>
@@ -23059,18 +23093,20 @@
         <v>86</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="M179" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="O179" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="P179" t="s" s="2">
         <v>729</v>
       </c>
-      <c r="O179" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="P179" s="2"/>
       <c r="Q179" t="s" s="2">
         <v>23</v>
       </c>
@@ -23094,13 +23130,13 @@
         <v>23</v>
       </c>
       <c r="Y179" t="s" s="2">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="Z179" t="s" s="2">
-        <v>731</v>
+        <v>23</v>
       </c>
       <c r="AA179" t="s" s="2">
-        <v>732</v>
+        <v>23</v>
       </c>
       <c r="AB179" t="s" s="2">
         <v>23</v>
@@ -23124,7 +23160,7 @@
         <v>77</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>23</v>
@@ -23135,13 +23171,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -23164,13 +23200,13 @@
         <v>86</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>160</v>
+        <v>731</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
@@ -23197,13 +23233,13 @@
         <v>23</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>736</v>
+        <v>23</v>
       </c>
       <c r="AA180" t="s" s="2">
-        <v>737</v>
+        <v>23</v>
       </c>
       <c r="AB180" t="s" s="2">
         <v>23</v>
@@ -23221,13 +23257,13 @@
         <v>23</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI180" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ180" t="s" s="2">
         <v>23</v>
@@ -23238,27 +23274,27 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
-        <v>382</v>
+        <v>23</v>
       </c>
       <c r="F181" s="2"/>
       <c r="G181" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H181" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I181" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="J181" t="s" s="2">
         <v>23</v>
@@ -23267,18 +23303,18 @@
         <v>86</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>160</v>
+        <v>99</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="O181" s="2"/>
-      <c r="P181" t="s" s="2">
-        <v>385</v>
-      </c>
+        <v>736</v>
+      </c>
+      <c r="O181" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="P181" s="2"/>
       <c r="Q181" t="s" s="2">
         <v>23</v>
       </c>
@@ -23302,11 +23338,13 @@
         <v>23</v>
       </c>
       <c r="Y181" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="Z181" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z181" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AA181" t="s" s="2">
-        <v>741</v>
+        <v>23</v>
       </c>
       <c r="AB181" t="s" s="2">
         <v>23</v>
@@ -23324,13 +23362,13 @@
         <v>23</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI181" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ181" t="s" s="2">
         <v>23</v>
@@ -23341,24 +23379,24 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
-        <v>23</v>
+        <v>739</v>
       </c>
       <c r="F182" s="2"/>
       <c r="G182" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H182" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I182" t="s" s="2">
         <v>23</v>
@@ -23367,16 +23405,16 @@
         <v>23</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>203</v>
+        <v>740</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>204</v>
+        <v>741</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>205</v>
+        <v>742</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
@@ -23427,24 +23465,24 @@
         <v>23</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>206</v>
+        <v>738</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI182" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ182" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK182" t="s" s="2">
-        <v>23</v>
+        <v>97</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>743</v>
@@ -23454,14 +23492,14 @@
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
-        <v>147</v>
+        <v>744</v>
       </c>
       <c r="F183" s="2"/>
       <c r="G183" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H183" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I183" t="s" s="2">
         <v>23</v>
@@ -23470,19 +23508,19 @@
         <v>23</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>128</v>
+        <v>745</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>208</v>
+        <v>746</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>209</v>
+        <v>747</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>150</v>
+        <v>748</v>
       </c>
       <c r="P183" s="2"/>
       <c r="Q183" t="s" s="2">
@@ -23520,19 +23558,19 @@
         <v>23</v>
       </c>
       <c r="AC183" t="s" s="2">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="AD183" t="s" s="2">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="AE183" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>211</v>
+        <v>743</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>77</v>
@@ -23544,18 +23582,18 @@
         <v>23</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>744</v>
+        <v>749</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -23563,35 +23601,33 @@
       </c>
       <c r="F184" s="2"/>
       <c r="G184" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H184" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I184" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="J184" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="K184" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>213</v>
+        <v>105</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>214</v>
+        <v>750</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>215</v>
+        <v>751</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>216</v>
-      </c>
-      <c r="P184" t="s" s="2">
-        <v>217</v>
-      </c>
+        <v>752</v>
+      </c>
+      <c r="P184" s="2"/>
       <c r="Q184" t="s" s="2">
         <v>23</v>
       </c>
@@ -23615,13 +23651,11 @@
         <v>23</v>
       </c>
       <c r="Y184" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z184" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Z184" s="2"/>
       <c r="AA184" t="s" s="2">
-        <v>23</v>
+        <v>753</v>
       </c>
       <c r="AB184" t="s" s="2">
         <v>23</v>
@@ -23639,13 +23673,13 @@
         <v>23</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>218</v>
+        <v>749</v>
       </c>
       <c r="AH184" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI184" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ184" t="s" s="2">
         <v>23</v>
@@ -23656,24 +23690,24 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>745</v>
+        <v>754</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
-        <v>23</v>
+        <v>755</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H185" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I185" t="s" s="2">
         <v>23</v>
@@ -23685,20 +23719,18 @@
         <v>86</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>203</v>
+        <v>160</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>220</v>
+        <v>756</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>221</v>
+        <v>757</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="P185" t="s" s="2">
-        <v>223</v>
-      </c>
+        <v>758</v>
+      </c>
+      <c r="P185" s="2"/>
       <c r="Q185" t="s" s="2">
         <v>23</v>
       </c>
@@ -23722,13 +23754,13 @@
         <v>23</v>
       </c>
       <c r="Y185" t="s" s="2">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>23</v>
+        <v>759</v>
       </c>
       <c r="AA185" t="s" s="2">
-        <v>23</v>
+        <v>760</v>
       </c>
       <c r="AB185" t="s" s="2">
         <v>23</v>
@@ -23746,7 +23778,7 @@
         <v>23</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>224</v>
+        <v>754</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>77</v>
@@ -23763,27 +23795,27 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
-        <v>452</v>
+        <v>23</v>
       </c>
       <c r="F186" s="2"/>
       <c r="G186" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H186" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I186" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="J186" t="s" s="2">
         <v>23</v>
@@ -23792,13 +23824,13 @@
         <v>86</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>227</v>
+        <v>160</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>748</v>
+        <v>763</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" s="2"/>
@@ -23825,13 +23857,13 @@
         <v>23</v>
       </c>
       <c r="Y186" t="s" s="2">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>23</v>
+        <v>764</v>
       </c>
       <c r="AA186" t="s" s="2">
-        <v>23</v>
+        <v>765</v>
       </c>
       <c r="AB186" t="s" s="2">
         <v>23</v>
@@ -23849,10 +23881,10 @@
         <v>23</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>746</v>
+        <v>761</v>
       </c>
       <c r="AH186" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI186" t="s" s="2">
         <v>85</v>
@@ -23866,27 +23898,27 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>749</v>
+        <v>766</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>749</v>
+        <v>766</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
-        <v>23</v>
+        <v>382</v>
       </c>
       <c r="F187" s="2"/>
       <c r="G187" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H187" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I187" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="J187" t="s" s="2">
         <v>23</v>
@@ -23895,18 +23927,18 @@
         <v>86</v>
       </c>
       <c r="L187" t="s" s="2">
-        <v>231</v>
+        <v>160</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>232</v>
+        <v>767</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>750</v>
-      </c>
-      <c r="O187" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="P187" s="2"/>
+        <v>768</v>
+      </c>
+      <c r="O187" s="2"/>
+      <c r="P187" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="Q187" t="s" s="2">
         <v>23</v>
       </c>
@@ -23930,13 +23962,11 @@
         <v>23</v>
       </c>
       <c r="Y187" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z187" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="Z187" s="2"/>
       <c r="AA187" t="s" s="2">
-        <v>23</v>
+        <v>769</v>
       </c>
       <c r="AB187" t="s" s="2">
         <v>23</v>
@@ -23954,7 +23984,7 @@
         <v>23</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>749</v>
+        <v>766</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>77</v>
@@ -23971,13 +24001,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>752</v>
+        <v>770</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>752</v>
+        <v>770</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -23997,20 +24027,18 @@
         <v>23</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L188" t="s" s="2">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>753</v>
+        <v>204</v>
       </c>
       <c r="N188" t="s" s="2">
-        <v>754</v>
-      </c>
-      <c r="O188" t="s" s="2">
-        <v>755</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="O188" s="2"/>
       <c r="P188" s="2"/>
       <c r="Q188" t="s" s="2">
         <v>23</v>
@@ -24059,7 +24087,7 @@
         <v>23</v>
       </c>
       <c r="AG188" t="s" s="2">
-        <v>752</v>
+        <v>206</v>
       </c>
       <c r="AH188" t="s" s="2">
         <v>77</v>
@@ -24071,49 +24099,51 @@
         <v>23</v>
       </c>
       <c r="AK188" t="s" s="2">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>756</v>
+        <v>771</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="F189" s="2"/>
       <c r="G189" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H189" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I189" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="J189" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L189" t="s" s="2">
-        <v>244</v>
+        <v>128</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>757</v>
+        <v>208</v>
       </c>
       <c r="N189" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O189" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O189" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P189" s="2"/>
       <c r="Q189" t="s" s="2">
         <v>23</v>
@@ -24150,42 +24180,42 @@
         <v>23</v>
       </c>
       <c r="AC189" t="s" s="2">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="AD189" t="s" s="2">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="AE189" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="AG189" t="s" s="2">
-        <v>756</v>
+        <v>211</v>
       </c>
       <c r="AH189" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI189" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ189" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK189" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>758</v>
+        <v>772</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -24196,7 +24226,7 @@
         <v>77</v>
       </c>
       <c r="H190" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I190" t="s" s="2">
         <v>23</v>
@@ -24208,16 +24238,20 @@
         <v>86</v>
       </c>
       <c r="L190" t="s" s="2">
-        <v>249</v>
+        <v>213</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>759</v>
+        <v>214</v>
       </c>
       <c r="N190" t="s" s="2">
-        <v>760</v>
-      </c>
-      <c r="O190" s="2"/>
-      <c r="P190" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="O190" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="P190" t="s" s="2">
+        <v>217</v>
+      </c>
       <c r="Q190" t="s" s="2">
         <v>23</v>
       </c>
@@ -24265,13 +24299,13 @@
         <v>23</v>
       </c>
       <c r="AG190" t="s" s="2">
-        <v>758</v>
+        <v>218</v>
       </c>
       <c r="AH190" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI190" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ190" t="s" s="2">
         <v>23</v>
@@ -24282,13 +24316,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -24311,16 +24345,20 @@
         <v>86</v>
       </c>
       <c r="L191" t="s" s="2">
-        <v>263</v>
+        <v>203</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>762</v>
+        <v>220</v>
       </c>
       <c r="N191" t="s" s="2">
-        <v>763</v>
-      </c>
-      <c r="O191" s="2"/>
-      <c r="P191" s="2"/>
+        <v>221</v>
+      </c>
+      <c r="O191" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="P191" t="s" s="2">
+        <v>223</v>
+      </c>
       <c r="Q191" t="s" s="2">
         <v>23</v>
       </c>
@@ -24368,13 +24406,13 @@
         <v>23</v>
       </c>
       <c r="AG191" t="s" s="2">
-        <v>761</v>
+        <v>224</v>
       </c>
       <c r="AH191" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI191" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ191" t="s" s="2">
         <v>23</v>
@@ -24385,42 +24423,42 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>764</v>
+        <v>774</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
-        <v>23</v>
+        <v>452</v>
       </c>
       <c r="F192" s="2"/>
       <c r="G192" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H192" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I192" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="J192" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L192" t="s" s="2">
-        <v>203</v>
+        <v>227</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>204</v>
+        <v>775</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>205</v>
+        <v>776</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
@@ -24471,10 +24509,10 @@
         <v>23</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>206</v>
+        <v>774</v>
       </c>
       <c r="AH192" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI192" t="s" s="2">
         <v>85</v>
@@ -24483,29 +24521,29 @@
         <v>23</v>
       </c>
       <c r="AK192" t="s" s="2">
-        <v>23</v>
+        <v>97</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="F193" s="2"/>
       <c r="G193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H193" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I193" t="s" s="2">
         <v>23</v>
@@ -24514,19 +24552,19 @@
         <v>23</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L193" t="s" s="2">
-        <v>128</v>
+        <v>231</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>209</v>
+        <v>778</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>150</v>
+        <v>779</v>
       </c>
       <c r="P193" s="2"/>
       <c r="Q193" t="s" s="2">
@@ -24576,66 +24614,64 @@
         <v>23</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>211</v>
+        <v>777</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI193" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ193" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK193" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>766</v>
+        <v>780</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>766</v>
+        <v>780</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
-        <v>274</v>
+        <v>23</v>
       </c>
       <c r="F194" s="2"/>
       <c r="G194" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H194" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I194" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J194" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="K194" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L194" t="s" s="2">
-        <v>128</v>
+        <v>239</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>275</v>
+        <v>781</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>276</v>
+        <v>782</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P194" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>783</v>
+      </c>
+      <c r="P194" s="2"/>
       <c r="Q194" t="s" s="2">
         <v>23</v>
       </c>
@@ -24683,30 +24719,30 @@
         <v>23</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>277</v>
+        <v>780</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI194" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ194" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK194" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>767</v>
+        <v>784</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>767</v>
+        <v>784</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -24714,13 +24750,13 @@
       </c>
       <c r="F195" s="2"/>
       <c r="G195" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H195" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I195" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="J195" t="s" s="2">
         <v>23</v>
@@ -24729,18 +24765,16 @@
         <v>86</v>
       </c>
       <c r="L195" t="s" s="2">
-        <v>160</v>
+        <v>244</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>768</v>
+        <v>785</v>
       </c>
       <c r="N195" t="s" s="2">
-        <v>769</v>
+        <v>246</v>
       </c>
       <c r="O195" s="2"/>
-      <c r="P195" t="s" s="2">
-        <v>770</v>
-      </c>
+      <c r="P195" s="2"/>
       <c r="Q195" t="s" s="2">
         <v>23</v>
       </c>
@@ -24764,13 +24798,13 @@
         <v>23</v>
       </c>
       <c r="Y195" t="s" s="2">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="Z195" t="s" s="2">
-        <v>771</v>
+        <v>23</v>
       </c>
       <c r="AA195" t="s" s="2">
-        <v>772</v>
+        <v>23</v>
       </c>
       <c r="AB195" t="s" s="2">
         <v>23</v>
@@ -24788,7 +24822,7 @@
         <v>23</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>767</v>
+        <v>784</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>77</v>
@@ -24805,13 +24839,13 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -24819,7 +24853,7 @@
       </c>
       <c r="F196" s="2"/>
       <c r="G196" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>85</v>
@@ -24834,18 +24868,16 @@
         <v>86</v>
       </c>
       <c r="L196" t="s" s="2">
-        <v>774</v>
+        <v>249</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>776</v>
+        <v>788</v>
       </c>
       <c r="O196" s="2"/>
-      <c r="P196" t="s" s="2">
-        <v>777</v>
-      </c>
+      <c r="P196" s="2"/>
       <c r="Q196" t="s" s="2">
         <v>23</v>
       </c>
@@ -24893,10 +24925,10 @@
         <v>23</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>773</v>
+        <v>786</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>85</v>
@@ -24910,13 +24942,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -24927,7 +24959,7 @@
         <v>77</v>
       </c>
       <c r="H197" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I197" t="s" s="2">
         <v>23</v>
@@ -24936,21 +24968,19 @@
         <v>23</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L197" t="s" s="2">
-        <v>779</v>
+        <v>263</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>780</v>
+        <v>790</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>781</v>
+        <v>791</v>
       </c>
       <c r="O197" s="2"/>
-      <c r="P197" t="s" s="2">
-        <v>782</v>
-      </c>
+      <c r="P197" s="2"/>
       <c r="Q197" t="s" s="2">
         <v>23</v>
       </c>
@@ -24998,13 +25028,13 @@
         <v>23</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>778</v>
+        <v>789</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI197" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ197" t="s" s="2">
         <v>23</v>
@@ -25015,13 +25045,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>783</v>
+        <v>792</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -25032,7 +25062,7 @@
         <v>77</v>
       </c>
       <c r="H198" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I198" t="s" s="2">
         <v>23</v>
@@ -25041,21 +25071,19 @@
         <v>23</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L198" t="s" s="2">
-        <v>784</v>
+        <v>203</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>785</v>
+        <v>204</v>
       </c>
       <c r="N198" t="s" s="2">
-        <v>786</v>
+        <v>205</v>
       </c>
       <c r="O198" s="2"/>
-      <c r="P198" t="s" s="2">
-        <v>787</v>
-      </c>
+      <c r="P198" s="2"/>
       <c r="Q198" t="s" s="2">
         <v>23</v>
       </c>
@@ -25103,7 +25131,7 @@
         <v>23</v>
       </c>
       <c r="AG198" t="s" s="2">
-        <v>783</v>
+        <v>206</v>
       </c>
       <c r="AH198" t="s" s="2">
         <v>77</v>
@@ -25115,29 +25143,29 @@
         <v>23</v>
       </c>
       <c r="AK198" t="s" s="2">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>788</v>
+        <v>793</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="F199" s="2"/>
       <c r="G199" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H199" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I199" t="s" s="2">
         <v>23</v>
@@ -25146,19 +25174,19 @@
         <v>23</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L199" t="s" s="2">
-        <v>160</v>
+        <v>128</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>789</v>
+        <v>208</v>
       </c>
       <c r="N199" t="s" s="2">
-        <v>790</v>
+        <v>209</v>
       </c>
       <c r="O199" t="s" s="2">
-        <v>791</v>
+        <v>150</v>
       </c>
       <c r="P199" s="2"/>
       <c r="Q199" t="s" s="2">
@@ -25184,13 +25212,13 @@
         <v>23</v>
       </c>
       <c r="Y199" t="s" s="2">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="Z199" t="s" s="2">
-        <v>792</v>
+        <v>23</v>
       </c>
       <c r="AA199" t="s" s="2">
-        <v>793</v>
+        <v>23</v>
       </c>
       <c r="AB199" t="s" s="2">
         <v>23</v>
@@ -25208,7 +25236,7 @@
         <v>23</v>
       </c>
       <c r="AG199" t="s" s="2">
-        <v>788</v>
+        <v>211</v>
       </c>
       <c r="AH199" t="s" s="2">
         <v>77</v>
@@ -25220,12 +25248,12 @@
         <v>23</v>
       </c>
       <c r="AK199" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>794</v>
@@ -25235,37 +25263,39 @@
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
-        <v>23</v>
+        <v>274</v>
       </c>
       <c r="F200" s="2"/>
       <c r="G200" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H200" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I200" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J200" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="K200" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L200" t="s" s="2">
-        <v>795</v>
+        <v>128</v>
       </c>
       <c r="M200" t="s" s="2">
-        <v>796</v>
+        <v>275</v>
       </c>
       <c r="N200" t="s" s="2">
-        <v>797</v>
+        <v>276</v>
       </c>
       <c r="O200" t="s" s="2">
-        <v>798</v>
-      </c>
-      <c r="P200" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="P200" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="Q200" t="s" s="2">
         <v>23</v>
       </c>
@@ -25313,7 +25343,7 @@
         <v>23</v>
       </c>
       <c r="AG200" t="s" s="2">
-        <v>794</v>
+        <v>277</v>
       </c>
       <c r="AH200" t="s" s="2">
         <v>77</v>
@@ -25325,18 +25355,18 @@
         <v>23</v>
       </c>
       <c r="AK200" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -25347,7 +25377,7 @@
         <v>77</v>
       </c>
       <c r="H201" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I201" t="s" s="2">
         <v>23</v>
@@ -25362,15 +25392,15 @@
         <v>160</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>801</v>
-      </c>
-      <c r="O201" t="s" s="2">
-        <v>802</v>
-      </c>
-      <c r="P201" s="2"/>
+        <v>797</v>
+      </c>
+      <c r="O201" s="2"/>
+      <c r="P201" t="s" s="2">
+        <v>798</v>
+      </c>
       <c r="Q201" t="s" s="2">
         <v>23</v>
       </c>
@@ -25397,10 +25427,10 @@
         <v>199</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>449</v>
+        <v>799</v>
       </c>
       <c r="AA201" t="s" s="2">
-        <v>450</v>
+        <v>800</v>
       </c>
       <c r="AB201" t="s" s="2">
         <v>23</v>
@@ -25418,13 +25448,13 @@
         <v>23</v>
       </c>
       <c r="AG201" t="s" s="2">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="AH201" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI201" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ201" t="s" s="2">
         <v>23</v>
@@ -25435,13 +25465,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -25449,10 +25479,10 @@
       </c>
       <c r="F202" s="2"/>
       <c r="G202" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H202" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I202" t="s" s="2">
         <v>23</v>
@@ -25464,18 +25494,18 @@
         <v>86</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>160</v>
+        <v>802</v>
       </c>
       <c r="M202" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="N202" t="s" s="2">
         <v>804</v>
       </c>
-      <c r="N202" t="s" s="2">
+      <c r="O202" s="2"/>
+      <c r="P202" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="O202" t="s" s="2">
-        <v>806</v>
-      </c>
-      <c r="P202" s="2"/>
       <c r="Q202" t="s" s="2">
         <v>23</v>
       </c>
@@ -25499,13 +25529,13 @@
         <v>23</v>
       </c>
       <c r="Y202" t="s" s="2">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="Z202" t="s" s="2">
-        <v>807</v>
+        <v>23</v>
       </c>
       <c r="AA202" t="s" s="2">
-        <v>808</v>
+        <v>23</v>
       </c>
       <c r="AB202" t="s" s="2">
         <v>23</v>
@@ -25523,10 +25553,10 @@
         <v>23</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="AH202" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI202" t="s" s="2">
         <v>85</v>
@@ -25540,13 +25570,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -25557,7 +25587,7 @@
         <v>77</v>
       </c>
       <c r="H203" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I203" t="s" s="2">
         <v>23</v>
@@ -25569,18 +25599,18 @@
         <v>23</v>
       </c>
       <c r="L203" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="M203" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="N203" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="O203" s="2"/>
+      <c r="P203" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="M203" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>811</v>
-      </c>
-      <c r="O203" t="s" s="2">
-        <v>812</v>
-      </c>
-      <c r="P203" s="2"/>
       <c r="Q203" t="s" s="2">
         <v>23</v>
       </c>
@@ -25628,13 +25658,13 @@
         <v>23</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI203" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ203" t="s" s="2">
         <v>23</v>
@@ -25645,13 +25675,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -25671,21 +25701,21 @@
         <v>23</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>160</v>
+        <v>812</v>
       </c>
       <c r="M204" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="N204" t="s" s="2">
         <v>814</v>
       </c>
-      <c r="N204" t="s" s="2">
+      <c r="O204" s="2"/>
+      <c r="P204" t="s" s="2">
         <v>815</v>
       </c>
-      <c r="O204" t="s" s="2">
-        <v>816</v>
-      </c>
-      <c r="P204" s="2"/>
       <c r="Q204" t="s" s="2">
         <v>23</v>
       </c>
@@ -25709,13 +25739,13 @@
         <v>23</v>
       </c>
       <c r="Y204" t="s" s="2">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="Z204" t="s" s="2">
-        <v>817</v>
+        <v>23</v>
       </c>
       <c r="AA204" t="s" s="2">
-        <v>387</v>
+        <v>23</v>
       </c>
       <c r="AB204" t="s" s="2">
         <v>23</v>
@@ -25733,13 +25763,13 @@
         <v>23</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI204" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ204" t="s" s="2">
         <v>23</v>
@@ -25750,13 +25780,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -25776,21 +25806,21 @@
         <v>23</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L205" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="M205" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="N205" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="O205" t="s" s="2">
         <v>819</v>
       </c>
-      <c r="M205" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="N205" t="s" s="2">
-        <v>821</v>
-      </c>
-      <c r="O205" s="2"/>
-      <c r="P205" t="s" s="2">
-        <v>822</v>
-      </c>
+      <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
         <v>23</v>
       </c>
@@ -25814,13 +25844,13 @@
         <v>23</v>
       </c>
       <c r="Y205" t="s" s="2">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="Z205" t="s" s="2">
-        <v>23</v>
+        <v>820</v>
       </c>
       <c r="AA205" t="s" s="2">
-        <v>23</v>
+        <v>821</v>
       </c>
       <c r="AB205" t="s" s="2">
         <v>23</v>
@@ -25838,7 +25868,7 @@
         <v>23</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>77</v>
@@ -25855,13 +25885,13 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -25881,10 +25911,10 @@
         <v>23</v>
       </c>
       <c r="K206" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>160</v>
+        <v>823</v>
       </c>
       <c r="M206" t="s" s="2">
         <v>824</v>
@@ -25892,7 +25922,9 @@
       <c r="N206" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="O206" s="2"/>
+      <c r="O206" t="s" s="2">
+        <v>826</v>
+      </c>
       <c r="P206" s="2"/>
       <c r="Q206" t="s" s="2">
         <v>23</v>
@@ -25917,13 +25949,13 @@
         <v>23</v>
       </c>
       <c r="Y206" t="s" s="2">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="Z206" t="s" s="2">
-        <v>826</v>
+        <v>23</v>
       </c>
       <c r="AA206" t="s" s="2">
-        <v>827</v>
+        <v>23</v>
       </c>
       <c r="AB206" t="s" s="2">
         <v>23</v>
@@ -25941,7 +25973,7 @@
         <v>23</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>77</v>
@@ -25958,13 +25990,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -25975,7 +26007,7 @@
         <v>77</v>
       </c>
       <c r="H207" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I207" t="s" s="2">
         <v>23</v>
@@ -25984,18 +26016,20 @@
         <v>23</v>
       </c>
       <c r="K207" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L207" t="s" s="2">
-        <v>258</v>
+        <v>160</v>
       </c>
       <c r="M207" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="N207" t="s" s="2">
         <v>829</v>
       </c>
-      <c r="N207" t="s" s="2">
+      <c r="O207" t="s" s="2">
         <v>830</v>
       </c>
-      <c r="O207" s="2"/>
       <c r="P207" s="2"/>
       <c r="Q207" t="s" s="2">
         <v>23</v>
@@ -26020,13 +26054,13 @@
         <v>23</v>
       </c>
       <c r="Y207" t="s" s="2">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="Z207" t="s" s="2">
-        <v>23</v>
+        <v>449</v>
       </c>
       <c r="AA207" t="s" s="2">
-        <v>23</v>
+        <v>450</v>
       </c>
       <c r="AB207" t="s" s="2">
         <v>23</v>
@@ -26044,7 +26078,7 @@
         <v>23</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>77</v>
@@ -26061,7 +26095,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>831</v>
@@ -26078,7 +26112,7 @@
         <v>77</v>
       </c>
       <c r="H208" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I208" t="s" s="2">
         <v>23</v>
@@ -26087,18 +26121,20 @@
         <v>23</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L208" t="s" s="2">
-        <v>203</v>
+        <v>160</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>204</v>
+        <v>832</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O208" s="2"/>
+        <v>833</v>
+      </c>
+      <c r="O208" t="s" s="2">
+        <v>834</v>
+      </c>
       <c r="P208" s="2"/>
       <c r="Q208" t="s" s="2">
         <v>23</v>
@@ -26123,13 +26159,13 @@
         <v>23</v>
       </c>
       <c r="Y208" t="s" s="2">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>23</v>
+        <v>835</v>
       </c>
       <c r="AA208" t="s" s="2">
-        <v>23</v>
+        <v>836</v>
       </c>
       <c r="AB208" t="s" s="2">
         <v>23</v>
@@ -26147,7 +26183,7 @@
         <v>23</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>206</v>
+        <v>831</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>77</v>
@@ -26159,22 +26195,22 @@
         <v>23</v>
       </c>
       <c r="AK208" t="s" s="2">
-        <v>23</v>
+        <v>97</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>832</v>
+        <v>837</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="F209" s="2"/>
       <c r="G209" t="s" s="2">
@@ -26193,16 +26229,16 @@
         <v>23</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>128</v>
+        <v>838</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>208</v>
+        <v>499</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>209</v>
+        <v>839</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>150</v>
+        <v>840</v>
       </c>
       <c r="P209" s="2"/>
       <c r="Q209" t="s" s="2">
@@ -26240,19 +26276,19 @@
         <v>23</v>
       </c>
       <c r="AC209" t="s" s="2">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="AD209" t="s" s="2">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="AE209" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF209" t="s" s="2">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>211</v>
+        <v>837</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>77</v>
@@ -26264,18 +26300,18 @@
         <v>23</v>
       </c>
       <c r="AK209" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -26295,19 +26331,19 @@
         <v>23</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L210" t="s" s="2">
-        <v>318</v>
+        <v>160</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>319</v>
+        <v>842</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>320</v>
+        <v>843</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>321</v>
+        <v>844</v>
       </c>
       <c r="P210" s="2"/>
       <c r="Q210" t="s" s="2">
@@ -26333,13 +26369,13 @@
         <v>23</v>
       </c>
       <c r="Y210" t="s" s="2">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>23</v>
+        <v>845</v>
       </c>
       <c r="AA210" t="s" s="2">
-        <v>23</v>
+        <v>387</v>
       </c>
       <c r="AB210" t="s" s="2">
         <v>23</v>
@@ -26357,13 +26393,13 @@
         <v>23</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>322</v>
+        <v>841</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI210" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ210" t="s" s="2">
         <v>23</v>
@@ -26374,13 +26410,13 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -26400,19 +26436,21 @@
         <v>23</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>239</v>
+        <v>847</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>324</v>
+        <v>848</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>325</v>
+        <v>849</v>
       </c>
       <c r="O211" s="2"/>
-      <c r="P211" s="2"/>
+      <c r="P211" t="s" s="2">
+        <v>850</v>
+      </c>
       <c r="Q211" t="s" s="2">
         <v>23</v>
       </c>
@@ -26460,13 +26498,13 @@
         <v>23</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>326</v>
+        <v>846</v>
       </c>
       <c r="AH211" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI211" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ211" t="s" s="2">
         <v>23</v>
@@ -26477,13 +26515,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>835</v>
+        <v>851</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>835</v>
+        <v>851</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -26491,10 +26529,10 @@
       </c>
       <c r="F212" s="2"/>
       <c r="G212" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H212" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I212" t="s" s="2">
         <v>23</v>
@@ -26503,16 +26541,16 @@
         <v>23</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L212" t="s" s="2">
-        <v>328</v>
+        <v>160</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>329</v>
+        <v>852</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>330</v>
+        <v>853</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" s="2"/>
@@ -26539,13 +26577,13 @@
         <v>23</v>
       </c>
       <c r="Y212" t="s" s="2">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>23</v>
+        <v>854</v>
       </c>
       <c r="AA212" t="s" s="2">
-        <v>23</v>
+        <v>855</v>
       </c>
       <c r="AB212" t="s" s="2">
         <v>23</v>
@@ -26563,13 +26601,13 @@
         <v>23</v>
       </c>
       <c r="AG212" t="s" s="2">
-        <v>331</v>
+        <v>851</v>
       </c>
       <c r="AH212" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI212" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ212" t="s" s="2">
         <v>23</v>
@@ -26580,13 +26618,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -26597,7 +26635,7 @@
         <v>77</v>
       </c>
       <c r="H213" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I213" t="s" s="2">
         <v>23</v>
@@ -26609,13 +26647,13 @@
         <v>23</v>
       </c>
       <c r="L213" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>838</v>
+        <v>858</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" s="2"/>
@@ -26666,7 +26704,7 @@
         <v>23</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>77</v>
@@ -26683,13 +26721,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -26786,13 +26824,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -26862,16 +26900,16 @@
         <v>23</v>
       </c>
       <c r="AC215" t="s" s="2">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="AD215" t="s" s="2">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="AE215" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>211</v>
@@ -26891,49 +26929,47 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
-        <v>274</v>
+        <v>23</v>
       </c>
       <c r="F216" s="2"/>
       <c r="G216" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H216" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I216" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J216" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="K216" t="s" s="2">
         <v>86</v>
       </c>
       <c r="L216" t="s" s="2">
-        <v>128</v>
+        <v>318</v>
       </c>
       <c r="M216" t="s" s="2">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="N216" t="s" s="2">
-        <v>276</v>
+        <v>320</v>
       </c>
       <c r="O216" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P216" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="P216" s="2"/>
       <c r="Q216" t="s" s="2">
         <v>23</v>
       </c>
@@ -26981,30 +27017,30 @@
         <v>23</v>
       </c>
       <c r="AG216" t="s" s="2">
-        <v>277</v>
+        <v>322</v>
       </c>
       <c r="AH216" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI216" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ216" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK216" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -27015,7 +27051,7 @@
         <v>77</v>
       </c>
       <c r="H217" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I217" t="s" s="2">
         <v>23</v>
@@ -27024,16 +27060,16 @@
         <v>23</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L217" t="s" s="2">
-        <v>160</v>
+        <v>239</v>
       </c>
       <c r="M217" t="s" s="2">
-        <v>843</v>
+        <v>324</v>
       </c>
       <c r="N217" t="s" s="2">
-        <v>844</v>
+        <v>325</v>
       </c>
       <c r="O217" s="2"/>
       <c r="P217" s="2"/>
@@ -27060,13 +27096,13 @@
         <v>23</v>
       </c>
       <c r="Y217" t="s" s="2">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="Z217" t="s" s="2">
-        <v>845</v>
+        <v>23</v>
       </c>
       <c r="AA217" t="s" s="2">
-        <v>846</v>
+        <v>23</v>
       </c>
       <c r="AB217" t="s" s="2">
         <v>23</v>
@@ -27084,7 +27120,7 @@
         <v>23</v>
       </c>
       <c r="AG217" t="s" s="2">
-        <v>842</v>
+        <v>326</v>
       </c>
       <c r="AH217" t="s" s="2">
         <v>77</v>
@@ -27101,13 +27137,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>847</v>
+        <v>863</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -27127,16 +27163,16 @@
         <v>23</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L218" t="s" s="2">
-        <v>848</v>
+        <v>328</v>
       </c>
       <c r="M218" t="s" s="2">
-        <v>849</v>
+        <v>329</v>
       </c>
       <c r="N218" t="s" s="2">
-        <v>850</v>
+        <v>330</v>
       </c>
       <c r="O218" s="2"/>
       <c r="P218" s="2"/>
@@ -27187,7 +27223,7 @@
         <v>23</v>
       </c>
       <c r="AG218" t="s" s="2">
-        <v>847</v>
+        <v>331</v>
       </c>
       <c r="AH218" t="s" s="2">
         <v>85</v>
@@ -27204,13 +27240,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>851</v>
+        <v>864</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>851</v>
+        <v>864</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -27233,20 +27269,16 @@
         <v>23</v>
       </c>
       <c r="L219" t="s" s="2">
-        <v>852</v>
+        <v>263</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>854</v>
-      </c>
-      <c r="O219" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="P219" t="s" s="2">
-        <v>856</v>
-      </c>
+        <v>866</v>
+      </c>
+      <c r="O219" s="2"/>
+      <c r="P219" s="2"/>
       <c r="Q219" t="s" s="2">
         <v>23</v>
       </c>
@@ -27294,7 +27326,7 @@
         <v>23</v>
       </c>
       <c r="AG219" t="s" s="2">
-        <v>851</v>
+        <v>864</v>
       </c>
       <c r="AH219" t="s" s="2">
         <v>77</v>
@@ -27311,13 +27343,13 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>678</v>
+        <v>706</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>857</v>
+        <v>867</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -27328,7 +27360,7 @@
         <v>77</v>
       </c>
       <c r="H220" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I220" t="s" s="2">
         <v>23</v>
@@ -27340,17 +27372,15 @@
         <v>23</v>
       </c>
       <c r="L220" t="s" s="2">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="M220" t="s" s="2">
-        <v>858</v>
+        <v>204</v>
       </c>
       <c r="N220" t="s" s="2">
-        <v>859</v>
-      </c>
-      <c r="O220" t="s" s="2">
-        <v>855</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="O220" s="2"/>
       <c r="P220" s="2"/>
       <c r="Q220" t="s" s="2">
         <v>23</v>
@@ -27375,13 +27405,13 @@
         <v>23</v>
       </c>
       <c r="Y220" t="s" s="2">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="Z220" t="s" s="2">
-        <v>860</v>
+        <v>23</v>
       </c>
       <c r="AA220" t="s" s="2">
-        <v>861</v>
+        <v>23</v>
       </c>
       <c r="AB220" t="s" s="2">
         <v>23</v>
@@ -27399,34 +27429,34 @@
         <v>23</v>
       </c>
       <c r="AG220" t="s" s="2">
-        <v>857</v>
+        <v>206</v>
       </c>
       <c r="AH220" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI220" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ220" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK220" t="s" s="2">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>862</v>
+        <v>706</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>129</v>
+        <v>868</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>129</v>
+        <v>868</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" t="s" s="2">
@@ -27445,15 +27475,17 @@
         <v>23</v>
       </c>
       <c r="L221" t="s" s="2">
-        <v>79</v>
+        <v>128</v>
       </c>
       <c r="M221" t="s" s="2">
-        <v>865</v>
+        <v>208</v>
       </c>
       <c r="N221" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="O221" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O221" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P221" s="2"/>
       <c r="Q221" t="s" s="2">
         <v>23</v>
@@ -27502,7 +27534,7 @@
         <v>23</v>
       </c>
       <c r="AG221" t="s" s="2">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="AH221" t="s" s="2">
         <v>77</v>
@@ -27511,7 +27543,7 @@
         <v>78</v>
       </c>
       <c r="AJ221" t="s" s="2">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="AK221" t="s" s="2">
         <v>134</v>
@@ -27519,45 +27551,49 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>862</v>
+        <v>706</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>534</v>
+        <v>869</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>534</v>
+        <v>869</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
-        <v>23</v>
+        <v>274</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H222" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I222" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J222" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L222" t="s" s="2">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="M222" t="s" s="2">
-        <v>204</v>
+        <v>275</v>
       </c>
       <c r="N222" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O222" s="2"/>
-      <c r="P222" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O222" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P222" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="Q222" t="s" s="2">
         <v>23</v>
       </c>
@@ -27605,30 +27641,30 @@
         <v>23</v>
       </c>
       <c r="AG222" t="s" s="2">
-        <v>206</v>
+        <v>277</v>
       </c>
       <c r="AH222" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI222" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ222" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK222" t="s" s="2">
-        <v>23</v>
+        <v>134</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>862</v>
+        <v>706</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>535</v>
+        <v>870</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>535</v>
+        <v>870</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -27639,7 +27675,7 @@
         <v>77</v>
       </c>
       <c r="H223" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I223" t="s" s="2">
         <v>23</v>
@@ -27651,13 +27687,13 @@
         <v>23</v>
       </c>
       <c r="L223" t="s" s="2">
-        <v>128</v>
+        <v>160</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>129</v>
+        <v>871</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>130</v>
+        <v>872</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
@@ -27684,54 +27720,54 @@
         <v>23</v>
       </c>
       <c r="Y223" t="s" s="2">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>23</v>
+        <v>873</v>
       </c>
       <c r="AA223" t="s" s="2">
-        <v>23</v>
+        <v>874</v>
       </c>
       <c r="AB223" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AC223" t="s" s="2">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="AD223" t="s" s="2">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="AE223" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>211</v>
+        <v>870</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI223" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ223" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK223" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>862</v>
+        <v>706</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>547</v>
+        <v>875</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>547</v>
+        <v>875</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -27754,24 +27790,22 @@
         <v>23</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>99</v>
+        <v>876</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>544</v>
+        <v>877</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O224" t="s" s="2">
-        <v>546</v>
-      </c>
+        <v>878</v>
+      </c>
+      <c r="O224" s="2"/>
       <c r="P224" s="2"/>
       <c r="Q224" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R224" s="2"/>
       <c r="S224" t="s" s="2">
-        <v>863</v>
+        <v>23</v>
       </c>
       <c r="T224" t="s" s="2">
         <v>23</v>
@@ -27813,7 +27847,7 @@
         <v>23</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>547</v>
+        <v>875</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>85</v>
@@ -27825,18 +27859,18 @@
         <v>23</v>
       </c>
       <c r="AK224" t="s" s="2">
-        <v>23</v>
+        <v>97</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>862</v>
+        <v>706</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>553</v>
+        <v>879</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>553</v>
+        <v>879</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -27847,7 +27881,7 @@
         <v>77</v>
       </c>
       <c r="H225" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I225" t="s" s="2">
         <v>23</v>
@@ -27859,16 +27893,20 @@
         <v>23</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>160</v>
+        <v>880</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>551</v>
+        <v>881</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O225" s="2"/>
-      <c r="P225" s="2"/>
+        <v>882</v>
+      </c>
+      <c r="O225" t="s" s="2">
+        <v>883</v>
+      </c>
+      <c r="P225" t="s" s="2">
+        <v>884</v>
+      </c>
       <c r="Q225" t="s" s="2">
         <v>23</v>
       </c>
@@ -27916,13 +27954,13 @@
         <v>23</v>
       </c>
       <c r="AG225" t="s" s="2">
-        <v>553</v>
+        <v>879</v>
       </c>
       <c r="AH225" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI225" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ225" t="s" s="2">
         <v>23</v>
@@ -27933,13 +27971,13 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>867</v>
+        <v>706</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>871</v>
+        <v>885</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>871</v>
+        <v>885</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -27950,7 +27988,7 @@
         <v>77</v>
       </c>
       <c r="H226" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I226" t="s" s="2">
         <v>23</v>
@@ -27962,16 +28000,16 @@
         <v>23</v>
       </c>
       <c r="L226" t="s" s="2">
-        <v>79</v>
+        <v>160</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>873</v>
+        <v>886</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>874</v>
+        <v>887</v>
       </c>
       <c r="O226" t="s" s="2">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="P226" s="2"/>
       <c r="Q226" t="s" s="2">
@@ -27997,13 +28035,13 @@
         <v>23</v>
       </c>
       <c r="Y226" t="s" s="2">
-        <v>23</v>
+        <v>199</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>23</v>
+        <v>888</v>
       </c>
       <c r="AA226" t="s" s="2">
-        <v>23</v>
+        <v>889</v>
       </c>
       <c r="AB226" t="s" s="2">
         <v>23</v>
@@ -28021,7 +28059,7 @@
         <v>23</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>871</v>
+        <v>885</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>77</v>
@@ -28030,21 +28068,21 @@
         <v>78</v>
       </c>
       <c r="AJ226" t="s" s="2">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="AK226" t="s" s="2">
-        <v>876</v>
+        <v>97</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>867</v>
+        <v>890</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>877</v>
+        <v>129</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>877</v>
+        <v>129</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" t="s" s="2">
@@ -28055,7 +28093,7 @@
         <v>77</v>
       </c>
       <c r="H227" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I227" t="s" s="2">
         <v>23</v>
@@ -28067,13 +28105,13 @@
         <v>23</v>
       </c>
       <c r="L227" t="s" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>204</v>
+        <v>893</v>
       </c>
       <c r="N227" t="s" s="2">
-        <v>205</v>
+        <v>272</v>
       </c>
       <c r="O227" s="2"/>
       <c r="P227" s="2"/>
@@ -28124,41 +28162,41 @@
         <v>23</v>
       </c>
       <c r="AG227" t="s" s="2">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="AH227" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI227" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ227" t="s" s="2">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="AK227" t="s" s="2">
-        <v>23</v>
+        <v>134</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>867</v>
+        <v>890</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>878</v>
+        <v>534</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>878</v>
+        <v>534</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="F228" s="2"/>
       <c r="G228" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H228" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I228" t="s" s="2">
         <v>23</v>
@@ -28170,17 +28208,15 @@
         <v>23</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>128</v>
+        <v>203</v>
       </c>
       <c r="M228" t="s" s="2">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="N228" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O228" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="O228" s="2"/>
       <c r="P228" s="2"/>
       <c r="Q228" t="s" s="2">
         <v>23</v>
@@ -28217,42 +28253,42 @@
         <v>23</v>
       </c>
       <c r="AC228" t="s" s="2">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="AD228" t="s" s="2">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="AE228" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="AG228" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AH228" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI228" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ228" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK228" t="s" s="2">
-        <v>134</v>
+        <v>23</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>867</v>
+        <v>890</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>879</v>
+        <v>535</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>879</v>
+        <v>535</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -28272,20 +28308,18 @@
         <v>23</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L229" t="s" s="2">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="M229" t="s" s="2">
-        <v>880</v>
+        <v>129</v>
       </c>
       <c r="N229" t="s" s="2">
-        <v>881</v>
-      </c>
-      <c r="O229" t="s" s="2">
-        <v>882</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O229" s="2"/>
       <c r="P229" s="2"/>
       <c r="Q229" t="s" s="2">
         <v>23</v>
@@ -28322,42 +28356,42 @@
         <v>23</v>
       </c>
       <c r="AC229" t="s" s="2">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="AD229" t="s" s="2">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="AE229" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="AG229" t="s" s="2">
-        <v>879</v>
+        <v>211</v>
       </c>
       <c r="AH229" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI229" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ229" t="s" s="2">
-        <v>883</v>
+        <v>23</v>
       </c>
       <c r="AK229" t="s" s="2">
-        <v>97</v>
+        <v>134</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>867</v>
+        <v>890</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>884</v>
+        <v>547</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>884</v>
+        <v>547</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -28365,7 +28399,7 @@
       </c>
       <c r="F230" s="2"/>
       <c r="G230" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H230" t="s" s="2">
         <v>85</v>
@@ -28377,19 +28411,19 @@
         <v>23</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L230" t="s" s="2">
         <v>99</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>885</v>
+        <v>544</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>886</v>
+        <v>545</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>887</v>
+        <v>546</v>
       </c>
       <c r="P230" s="2"/>
       <c r="Q230" t="s" s="2">
@@ -28397,7 +28431,7 @@
       </c>
       <c r="R230" s="2"/>
       <c r="S230" t="s" s="2">
-        <v>23</v>
+        <v>891</v>
       </c>
       <c r="T230" t="s" s="2">
         <v>23</v>
@@ -28415,13 +28449,13 @@
         <v>23</v>
       </c>
       <c r="Y230" t="s" s="2">
-        <v>374</v>
+        <v>23</v>
       </c>
       <c r="Z230" t="s" s="2">
-        <v>888</v>
+        <v>23</v>
       </c>
       <c r="AA230" t="s" s="2">
-        <v>889</v>
+        <v>23</v>
       </c>
       <c r="AB230" t="s" s="2">
         <v>23</v>
@@ -28439,10 +28473,10 @@
         <v>23</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>884</v>
+        <v>547</v>
       </c>
       <c r="AH230" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI230" t="s" s="2">
         <v>85</v>
@@ -28451,18 +28485,18 @@
         <v>23</v>
       </c>
       <c r="AK230" t="s" s="2">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>867</v>
+        <v>890</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>890</v>
+        <v>553</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>890</v>
+        <v>553</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -28470,7 +28504,7 @@
       </c>
       <c r="F231" s="2"/>
       <c r="G231" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H231" t="s" s="2">
         <v>85</v>
@@ -28482,20 +28516,18 @@
         <v>23</v>
       </c>
       <c r="K231" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L231" t="s" s="2">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>891</v>
+        <v>551</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>892</v>
-      </c>
-      <c r="O231" t="s" s="2">
-        <v>893</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="O231" s="2"/>
       <c r="P231" s="2"/>
       <c r="Q231" t="s" s="2">
         <v>23</v>
@@ -28544,7 +28576,7 @@
         <v>23</v>
       </c>
       <c r="AG231" t="s" s="2">
-        <v>890</v>
+        <v>553</v>
       </c>
       <c r="AH231" t="s" s="2">
         <v>77</v>
@@ -28561,13 +28593,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>867</v>
+        <v>895</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -28578,7 +28610,7 @@
         <v>77</v>
       </c>
       <c r="H232" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I232" t="s" s="2">
         <v>23</v>
@@ -28587,19 +28619,19 @@
         <v>23</v>
       </c>
       <c r="K232" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L232" t="s" s="2">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>895</v>
+        <v>901</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>896</v>
+        <v>902</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>897</v>
+        <v>903</v>
       </c>
       <c r="P232" s="2"/>
       <c r="Q232" t="s" s="2">
@@ -28649,30 +28681,30 @@
         <v>23</v>
       </c>
       <c r="AG232" t="s" s="2">
-        <v>894</v>
+        <v>899</v>
       </c>
       <c r="AH232" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI232" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ232" t="s" s="2">
-        <v>23</v>
+        <v>140</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>97</v>
+        <v>904</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>129</v>
+        <v>905</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>129</v>
+        <v>905</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -28683,7 +28715,7 @@
         <v>77</v>
       </c>
       <c r="H233" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="I233" t="s" s="2">
         <v>23</v>
@@ -28695,13 +28727,13 @@
         <v>23</v>
       </c>
       <c r="L233" t="s" s="2">
-        <v>79</v>
+        <v>203</v>
       </c>
       <c r="M233" t="s" s="2">
-        <v>138</v>
+        <v>204</v>
       </c>
       <c r="N233" t="s" s="2">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="O233" s="2"/>
       <c r="P233" s="2"/>
@@ -28752,41 +28784,41 @@
         <v>23</v>
       </c>
       <c r="AG233" t="s" s="2">
-        <v>129</v>
+        <v>206</v>
       </c>
       <c r="AH233" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI233" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ233" t="s" s="2">
-        <v>140</v>
+        <v>23</v>
       </c>
       <c r="AK233" t="s" s="2">
-        <v>134</v>
+        <v>23</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>534</v>
+        <v>906</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>534</v>
+        <v>906</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="F234" s="2"/>
       <c r="G234" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H234" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="I234" t="s" s="2">
         <v>23</v>
@@ -28798,15 +28830,17 @@
         <v>23</v>
       </c>
       <c r="L234" t="s" s="2">
-        <v>203</v>
+        <v>128</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O234" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="O234" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P234" s="2"/>
       <c r="Q234" t="s" s="2">
         <v>23</v>
@@ -28843,42 +28877,42 @@
         <v>23</v>
       </c>
       <c r="AC234" t="s" s="2">
-        <v>23</v>
+        <v>131</v>
       </c>
       <c r="AD234" t="s" s="2">
-        <v>23</v>
+        <v>210</v>
       </c>
       <c r="AE234" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF234" t="s" s="2">
-        <v>23</v>
+        <v>132</v>
       </c>
       <c r="AG234" t="s" s="2">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="AH234" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI234" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AJ234" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK234" t="s" s="2">
-        <v>23</v>
+        <v>134</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>535</v>
+        <v>681</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>535</v>
+        <v>681</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -28898,18 +28932,20 @@
         <v>23</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>128</v>
+        <v>203</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>129</v>
+        <v>678</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O235" s="2"/>
+        <v>679</v>
+      </c>
+      <c r="O235" t="s" s="2">
+        <v>680</v>
+      </c>
       <c r="P235" s="2"/>
       <c r="Q235" t="s" s="2">
         <v>23</v>
@@ -28946,42 +28982,42 @@
         <v>23</v>
       </c>
       <c r="AC235" t="s" s="2">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="AD235" t="s" s="2">
-        <v>210</v>
+        <v>23</v>
       </c>
       <c r="AE235" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>132</v>
+        <v>23</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>211</v>
+        <v>681</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AI235" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>23</v>
+        <v>682</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>134</v>
+        <v>97</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>547</v>
+        <v>689</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>547</v>
+        <v>689</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -28989,7 +29025,7 @@
       </c>
       <c r="F236" s="2"/>
       <c r="G236" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H236" t="s" s="2">
         <v>85</v>
@@ -29001,19 +29037,19 @@
         <v>23</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L236" t="s" s="2">
         <v>99</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>544</v>
+        <v>684</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>545</v>
+        <v>685</v>
       </c>
       <c r="O236" t="s" s="2">
-        <v>546</v>
+        <v>686</v>
       </c>
       <c r="P236" s="2"/>
       <c r="Q236" t="s" s="2">
@@ -29021,7 +29057,7 @@
       </c>
       <c r="R236" s="2"/>
       <c r="S236" t="s" s="2">
-        <v>899</v>
+        <v>23</v>
       </c>
       <c r="T236" t="s" s="2">
         <v>23</v>
@@ -29039,13 +29075,13 @@
         <v>23</v>
       </c>
       <c r="Y236" t="s" s="2">
-        <v>23</v>
+        <v>374</v>
       </c>
       <c r="Z236" t="s" s="2">
-        <v>23</v>
+        <v>687</v>
       </c>
       <c r="AA236" t="s" s="2">
-        <v>23</v>
+        <v>688</v>
       </c>
       <c r="AB236" t="s" s="2">
         <v>23</v>
@@ -29063,10 +29099,10 @@
         <v>23</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>547</v>
+        <v>689</v>
       </c>
       <c r="AH236" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="AI236" t="s" s="2">
         <v>85</v>
@@ -29075,18 +29111,18 @@
         <v>23</v>
       </c>
       <c r="AK236" t="s" s="2">
-        <v>23</v>
+        <v>97</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>553</v>
+        <v>694</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>553</v>
+        <v>694</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -29094,7 +29130,7 @@
       </c>
       <c r="F237" s="2"/>
       <c r="G237" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H237" t="s" s="2">
         <v>85</v>
@@ -29106,18 +29142,20 @@
         <v>23</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>428</v>
+        <v>154</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>551</v>
+        <v>691</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O237" s="2"/>
+        <v>692</v>
+      </c>
+      <c r="O237" t="s" s="2">
+        <v>693</v>
+      </c>
       <c r="P237" s="2"/>
       <c r="Q237" t="s" s="2">
         <v>23</v>
@@ -29166,18 +29204,640 @@
         <v>23</v>
       </c>
       <c r="AG237" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="AH237" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI237" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ237" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK237" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="B238" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="C238" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="D238" s="2"/>
+      <c r="E238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F238" s="2"/>
+      <c r="G238" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H238" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K238" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L238" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M238" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="N238" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="O238" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="P238" s="2"/>
+      <c r="Q238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R238" s="2"/>
+      <c r="S238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG238" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AH238" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI238" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ238" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK238" t="s" s="2">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B239" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="C239" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="D239" s="2"/>
+      <c r="E239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F239" s="2"/>
+      <c r="G239" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H239" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="I239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L239" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="M239" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="N239" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O239" s="2"/>
+      <c r="P239" s="2"/>
+      <c r="Q239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R239" s="2"/>
+      <c r="S239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF239" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG239" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AH239" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI239" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ239" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK239" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B240" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="C240" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="D240" s="2"/>
+      <c r="E240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F240" s="2"/>
+      <c r="G240" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H240" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L240" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="M240" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="N240" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="O240" s="2"/>
+      <c r="P240" s="2"/>
+      <c r="Q240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R240" s="2"/>
+      <c r="S240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG240" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="AH240" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI240" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ240" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK240" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B241" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C241" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="D241" s="2"/>
+      <c r="E241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F241" s="2"/>
+      <c r="G241" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H241" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L241" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="M241" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="N241" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="O241" s="2"/>
+      <c r="P241" s="2"/>
+      <c r="Q241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R241" s="2"/>
+      <c r="S241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC241" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AD241" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AE241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF241" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AG241" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="AH241" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI241" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AJ241" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK241" t="s" s="2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B242" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="C242" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="D242" s="2"/>
+      <c r="E242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F242" s="2"/>
+      <c r="G242" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H242" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L242" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="M242" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N242" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O242" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="P242" s="2"/>
+      <c r="Q242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R242" s="2"/>
+      <c r="S242" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="T242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG242" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="AH242" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI242" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ242" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK242" t="s" s="2">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s" s="2">
+        <v>907</v>
+      </c>
+      <c r="B243" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AH237" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI237" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK237" t="s" s="2">
+      <c r="C243" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="D243" s="2"/>
+      <c r="E243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F243" s="2"/>
+      <c r="G243" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H243" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="L243" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M243" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N243" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="O243" s="2"/>
+      <c r="P243" s="2"/>
+      <c r="Q243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R243" s="2"/>
+      <c r="S243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG243" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AH243" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI243" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK243" t="s" s="2">
         <v>97</v>
       </c>
     </row>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:25:52+00:00</t>
+    <t>2026-08-28T08:10:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:10:45+00:00</t>
+    <t>2026-08-28T11:38:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -731,7 +731,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -787,7 +787,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
 </t>
   </si>
   <si>
@@ -804,7 +804,7 @@
 Informant</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1978,7 +1978,7 @@
     <t>List.source</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
@@ -2213,7 +2213,7 @@
     <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/core/r4/ValueSet/ElgaListEmptyReasonVS</t>
+    <t>https://fhir.hl7.at/elga/ediag/r4/ValueSet/at-ediag-list-emptyreason-vs</t>
   </si>
   <si>
     <t>at-elga-ediag-procedure</t>
@@ -4423,7 +4423,7 @@
     <col min="24" max="24" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="106.67578125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="54.46484375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="55.875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:38:22+00:00</t>
+    <t>2026-08-28T12:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:52:33+00:00</t>
+    <t>2026-08-31T10:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:02:50+00:00</t>
+    <t>2026-09-01T06:51:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T06:51:10+00:00</t>
+    <t>2026-09-01T11:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:42:45+00:00</t>
+    <t>2026-09-01T12:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:48:31+00:00</t>
+    <t>2026-09-01T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:57:21+00:00</t>
+    <t>2026-09-03T13:31:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T13:31:10+00:00</t>
+    <t>2026-09-07T04:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T04:47:29+00:00</t>
+    <t>2026-09-07T06:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T06:52:33+00:00</t>
+    <t>2026-09-07T07:43:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:43:01+00:00</t>
+    <t>2026-09-07T07:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:56:25+00:00</t>
+    <t>2026-09-07T09:23:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T09:23:06+00:00</t>
+    <t>2026-09-07T10:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:17:45+00:00</t>
+    <t>2026-09-07T10:50:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -501,7 +501,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Allergie in einem internem Dokumentationssystem</t>
+    <t>Zuordnung der Allergie in einem internen Dokumentationssystem</t>
   </si>
   <si>
     <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -543,7 +543,7 @@
     <t>AllergyIntolerance.verificationStatus</t>
   </si>
   <si>
-    <t>ToDo; Presumed, gibt es hierzu aktuelle Infos? kardinalität von clinicalStatus &amp; verificationStatus muss noch erarbeitet werden. Möglicher Status; unconfirmed | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Allergie. Möglicher Status; unconfirmed | confirmed | refuted | entered-in-error</t>
   </si>
   <si>
     <t>Assertion about certainty associated with the propensity, or potential risk, of a reaction to the identified substance (including pharmaceutical product).</t>
@@ -1127,7 +1127,7 @@
     <t>Condition.identifier</t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internem Dokumentationssystem</t>
+    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem</t>
   </si>
   <si>
     <t>Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -1139,8 +1139,7 @@
     <t>Condition.clinicalStatus</t>
   </si>
   <si>
-    <t>Klinischer Status der Diagnose (wie:Status post), 
-mögliche Codes: active | recurrence | relapse | inactive | remission | resolved</t>
+    <t>Klinischer Status der Diagnose (wie:Status post), mögliche Codes: active | recurrence | relapse | inactive | remission | resolved</t>
   </si>
   <si>
     <t>The clinical status of the condition.</t>
@@ -1162,7 +1161,7 @@
     <t>Condition.verificationStatus</t>
   </si>
   <si>
-    <t>Status der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error</t>
   </si>
   <si>
     <t>The verification status to support the clinical status of the condition.</t>
@@ -1860,7 +1859,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Status des Liste.</t>
+    <t>Status der Liste.</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -2342,7 +2341,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis der Ressource auf eine andere, übergreordnete Ressource</t>
+    <t>Verweis der Ressource auf eine andere, übergeordnete Ressource</t>
   </si>
   <si>
     <t>A larger event of which this particular procedure is a component or step.</t>
@@ -2461,7 +2460,7 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen/dokumentiert hat</t>
+    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen bzw. dokumentiert hat</t>
   </si>
   <si>
     <t>Procedure.asserter</t>
@@ -2476,7 +2475,7 @@
     <t>Procedure.performer</t>
   </si>
   <si>
-    <t>Diese Person hat die Prozedur durchgeführt</t>
+    <t>Person, die die Prozedur durchgeführt hat</t>
   </si>
   <si>
     <t>Limited to "real" people rather than equipment.</t>
@@ -2560,7 +2559,7 @@
     <t>Procedure.reasonCode</t>
   </si>
   <si>
-    <t>Code, des med. Grundes für die Durchführung der Prozedur</t>
+    <t>Code des medizinischen Grundes für die Durchführung der Prozedur</t>
   </si>
   <si>
     <t>The coded reason why the procedure was performed. This may be a coded entity of some type, or may simply be present as text.</t>
@@ -2582,7 +2581,7 @@
 </t>
   </si>
   <si>
-    <t>Begründung dass die Prozedur durchgeführt worden ist - Verweis auf eine andere R. wie Condition, Observation,...</t>
+    <t>Begründung für die Durchführung der Prozedur; Verweis auf eine andere Ressource wie Condition, Observation,...</t>
   </si>
   <si>
     <t>The justification of why the procedure was performed.</t>
@@ -2638,7 +2637,7 @@
     <t>Procedure.complication</t>
   </si>
   <si>
-    <t>Komplikation/en während dem Eingriff</t>
+    <t>Komplikation während dem Eingriff</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period. These are generally tracked separately from the notes, which will typically describe the procedure itself rather than any 'post procedure' issues.</t>
@@ -2657,7 +2656,7 @@
 </t>
   </si>
   <si>
-    <t>Eine Diagnose die durch die durchgeführte Prozedur entstanden ist</t>
+    <t>Diagnose, die durch die durchgeführte Prozedur entstanden ist</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period.</t>
@@ -2684,7 +2683,7 @@
     <t>Procedure.note</t>
   </si>
   <si>
-    <t>Freitext zur Prozedur für Zusatzinformation</t>
+    <t>Freitext zur Prozedur als Zusatzinformation</t>
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
@@ -2708,7 +2707,7 @@
     <t>Procedure.focalDevice</t>
   </si>
   <si>
-    <t>Prozedurendurchführendes Gerät</t>
+    <t>Gerät, das zur Durchführung der Prozedur verwendet wurde</t>
   </si>
   <si>
     <t>A device that is implanted, removed or otherwise manipulated (calibration, battery replacement, fitting a prosthesis, attaching a wound-vac, etc.) as a focal portion of the Procedure.</t>
@@ -2758,7 +2757,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf verwendete Materialien während der Prozedur (z.b. Medikamente)</t>
+    <t>Verweis auf während der Prozedur verwendete Materialien, z. B. Medikamente</t>
   </si>
   <si>
     <t>Identifies medications, devices and any other substance used as part of the procedure.</t>
@@ -2773,7 +2772,7 @@
     <t>Procedure.usedCode</t>
   </si>
   <si>
-    <t>Code der Materialien, die während der Prozedur verwendetet wurden</t>
+    <t>Code der während der Prozedur verwendeten Materialien</t>
   </si>
   <si>
     <t>Identifies coded items that were used as part of the procedure.</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8338" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8338" uniqueCount="914">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:50:55+00:00</t>
+    <t>2026-09-08T06:03:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1880,7 +1880,7 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>Die Liste wird laufend gepflegt, hat daher den fixen Wert: working.</t>
+    <t>Die Liste wird laufend gepflegt und hat daher den festen Wert: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -1981,8 +1981,8 @@
 </t>
   </si>
   <si>
-    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. Im Falle eines GDA: eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA-Anwendung 
-des Patienten zuzugreifen. Im Falle eines Patienten: eindeutig identifiziert durch den Z-PI.</t>
+    <t>Person, die die Liste erstellt hat und für den Inhalt verantwortlich ist. Im Falle eines GDA ist sie eindeutig über den GDA-Index identifiziert und zum Zugriff auf die ELGA-Anwendung des Patienten berechtigt. 
+ Im Falle eines Patienten erfolgt die eindeutige Identifizierung über den Z-PI.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -2073,7 +2073,7 @@
     <t>List.entry.deleted</t>
   </si>
   <si>
-    <t>Kennzeichnung, dass der Eintrag gelöscht wurde, ist nicht erlaubt (siehe Invariant lst-2).</t>
+    <t>Eine Kennzeichnung des Eintrags als gelöscht ist nicht zulässig (siehe Invariant list-emptyreason-required).</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -2095,7 +2095,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme des Eintrags in die Liste wird nicht dokumentiert, da die Liste laufend gepflegt wird und das Datum der letzten Aktualisierung der Liste (List.date) dokumentiert wird.</t>
+    <t>Das Datum der Aufnahme des Eintrags in die Liste wird nicht dokumentiert, da die Liste laufend gepflegt wird. Dokumentiert wird das Datum der letzten Aktualisierung der Liste (List.date).</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -2279,6 +2279,9 @@
     <t>Procedure.identifier</t>
   </si>
   <si>
+    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem.</t>
+  </si>
+  <si>
     <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
   </si>
   <si>
@@ -2295,7 +2298,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll</t>
+    <t>Verweis auf eine standardisierte FHIR-Ressource, ein Template oder einen Leitfaden, der beschreibt, wie die Prozedur durchgeführt werden soll.</t>
   </si>
   <si>
     <t>The URL pointing to a FHIR-defined protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
@@ -2304,7 +2307,7 @@
     <t>Procedure.instantiatesUri</t>
   </si>
   <si>
-    <t>Verweis auf ein externes Dokument</t>
+    <t>Verweis auf ein externes Dokument.</t>
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, order set or other definition that is adhered to in whole or in part by this Procedure.</t>
@@ -2324,7 +2327,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf eine Anforderung</t>
+    <t>Verweis auf eine Anforderung.</t>
   </si>
   <si>
     <t>A reference to a resource that contains details of the request for this procedure.</t>
@@ -2341,7 +2344,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis der Ressource auf eine andere, übergeordnete Ressource</t>
+    <t>Verweis der Ressource auf eine andere, übergeordnete Ressource.</t>
   </si>
   <si>
     <t>A larger event of which this particular procedure is a component or step.</t>
@@ -2353,7 +2356,7 @@
     <t>Procedure.status</t>
   </si>
   <si>
-    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren</t>
+    <t>Nur tatsächlich durchgeführte (completed) oder irrtümlich dokumentierte (entered-in-error) Prozeduren.</t>
   </si>
   <si>
     <t>A code specifying the state of the procedure. Generally, this will be the in-progress or completed state.</t>
@@ -2373,7 +2376,7 @@
 Cancelled Reason</t>
   </si>
   <si>
-    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung</t>
+    <t>ToDo: Korrekturvermerk wird von digimed übernommen, ist noch in Abstimmung.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the procedure.</t>
@@ -2391,7 +2394,7 @@
     <t>Procedure.category</t>
   </si>
   <si>
-    <t>Kategorisierung nach Verfahren</t>
+    <t>Kategorisierung nach Verfahren.</t>
   </si>
   <si>
     <t>A code that classifies the procedure for searching, sorting and display purposes (e.g. "Surgical Procedure").</t>
@@ -2406,7 +2409,7 @@
     <t>Procedure.code</t>
   </si>
   <si>
-    <t>Prozedurencode der durchgeführten Prozedur</t>
+    <t>Prozedurencode der durchgeführten Prozedur.</t>
   </si>
   <si>
     <t>The specific procedure that is performed. Use text if the exact nature of the procedure cannot be coded (e.g. "Laparoscopic Appendectomy").</t>
@@ -2430,7 +2433,7 @@
     <t>Procedure.subject</t>
   </si>
   <si>
-    <t>Person, auf die sich die Prozedur bezieht</t>
+    <t>Person, auf die sich die Prozedur bezieht.</t>
   </si>
   <si>
     <t>The person, animal or group on which the procedure was performed.</t>
@@ -2439,6 +2442,9 @@
     <t>Procedure.encounter</t>
   </si>
   <si>
+    <t>Behandlungskontakt.</t>
+  </si>
+  <si>
     <t>The Encounter during which this Procedure was created or performed or to which the creation of this record is tightly associated.</t>
   </si>
   <si>
@@ -2448,7 +2454,7 @@
     <t>Procedure.performed[x]</t>
   </si>
   <si>
-    <t>Zeitpunkt der Durchführung</t>
+    <t>Zeitpunkt der Durchführung.</t>
   </si>
   <si>
     <t>Estimated or actual date, date-time, period, or age when the procedure was performed.  Allows a period to support complex procedures that span more than one date, and also allows for the length of the procedure to be captured.</t>
@@ -2460,13 +2466,13 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen bzw. dokumentiert hat</t>
+    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Procedure.asserter</t>
   </si>
   <si>
-    <t>Quelle der Information zur Prozedur (z. B. behandelnde Person, Patient oder Dritter)</t>
+    <t>Quelle der Information zur Prozedur (z. B. behandelnde Person, Patient oder Dritter).</t>
   </si>
   <si>
     <t>Individual who is making the procedure statement.</t>
@@ -2475,7 +2481,7 @@
     <t>Procedure.performer</t>
   </si>
   <si>
-    <t>Person, die die Prozedur durchgeführt hat</t>
+    <t>Person, die die Prozedur durchgeführt hat.</t>
   </si>
   <si>
     <t>Limited to "real" people rather than equipment.</t>
@@ -2547,7 +2553,7 @@
 </t>
   </si>
   <si>
-    <t>Durchführungsort</t>
+    <t>Durchführungsort.</t>
   </si>
   <si>
     <t>The location where the procedure actually happened.  E.g. a newborn at home, a tracheostomy at a restaurant.</t>
@@ -2559,7 +2565,7 @@
     <t>Procedure.reasonCode</t>
   </si>
   <si>
-    <t>Code des medizinischen Grundes für die Durchführung der Prozedur</t>
+    <t>Code des medizinischen Grundes für die Durchführung der Prozedur.</t>
   </si>
   <si>
     <t>The coded reason why the procedure was performed. This may be a coded entity of some type, or may simply be present as text.</t>
@@ -2581,7 +2587,7 @@
 </t>
   </si>
   <si>
-    <t>Begründung für die Durchführung der Prozedur; Verweis auf eine andere Ressource wie Condition, Observation,...</t>
+    <t>Begründung für die Durchführung der Prozedur; Verweis auf eine andere Ressource wie z.B. Condition oder Observation.</t>
   </si>
   <si>
     <t>The justification of why the procedure was performed.</t>
@@ -2594,7 +2600,7 @@
     <t>Procedure.bodySite</t>
   </si>
   <si>
-    <t>Betroffene Körperstelle</t>
+    <t>Betroffene Körperstelle.</t>
   </si>
   <si>
     <t>Detailed and structured anatomical location information. Multiple locations are allowed - e.g. multiple punch biopsies of a lesion.</t>
@@ -2606,7 +2612,7 @@
     <t>Procedure.outcome</t>
   </si>
   <si>
-    <t>Ergebnis der Prozedur</t>
+    <t>Ergebnis der Prozedur.</t>
   </si>
   <si>
     <t>The outcome of the procedure - did it resolve the reasons for the procedure being performed?</t>
@@ -2628,6 +2634,9 @@
 </t>
   </si>
   <si>
+    <t>Verweis auf ELGA-Befunde als medizinische Evidenz.</t>
+  </si>
+  <si>
     <t>This could be a histology result, pathology report, surgical report, etc.</t>
   </si>
   <si>
@@ -2637,7 +2646,7 @@
     <t>Procedure.complication</t>
   </si>
   <si>
-    <t>Komplikation während dem Eingriff</t>
+    <t>Komplikation während dem Eingriff.</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period. These are generally tracked separately from the notes, which will typically describe the procedure itself rather than any 'post procedure' issues.</t>
@@ -2656,7 +2665,7 @@
 </t>
   </si>
   <si>
-    <t>Diagnose, die durch die durchgeführte Prozedur entstanden ist</t>
+    <t>Diagnose, die durch die durchgeführte Prozedur entstanden ist.</t>
   </si>
   <si>
     <t>Any complications that occurred during the procedure, or in the immediate post-performance period.</t>
@@ -2668,7 +2677,7 @@
     <t>Procedure.followUp</t>
   </si>
   <si>
-    <t>Nachkontrolle (Code)</t>
+    <t>Nachkontrolle (Code).</t>
   </si>
   <si>
     <t>If the procedure required specific follow up - e.g. removal of sutures. The follow up may be represented as a simple note or could potentially be more complex, in which case the CarePlan resource can be used.</t>
@@ -2683,7 +2692,7 @@
     <t>Procedure.note</t>
   </si>
   <si>
-    <t>Freitext zur Prozedur als Zusatzinformation</t>
+    <t>Freitext zur Prozedur als Zusatzinformation.</t>
   </si>
   <si>
     <t>Any other notes and comments about the procedure.</t>
@@ -2707,7 +2716,7 @@
     <t>Procedure.focalDevice</t>
   </si>
   <si>
-    <t>Gerät, das zur Durchführung der Prozedur verwendet wurde</t>
+    <t>Gerät, das zur Durchführung der Prozedur verwendet wurde.</t>
   </si>
   <si>
     <t>A device that is implanted, removed or otherwise manipulated (calibration, battery replacement, fitting a prosthesis, attaching a wound-vac, etc.) as a focal portion of the Procedure.</t>
@@ -2757,7 +2766,7 @@
 </t>
   </si>
   <si>
-    <t>Verweis auf während der Prozedur verwendete Materialien, z. B. Medikamente</t>
+    <t>Verweis auf während der Prozedur verwendete Materialien, z. B. Medikamente.</t>
   </si>
   <si>
     <t>Identifies medications, devices and any other substance used as part of the procedure.</t>
@@ -2772,7 +2781,7 @@
     <t>Procedure.usedCode</t>
   </si>
   <si>
-    <t>Code der während der Prozedur verwendeten Materialien</t>
+    <t>Code der während der Prozedur verwendeten Materialien.</t>
   </si>
   <si>
     <t>Identifies coded items that were used as part of the procedure.</t>
@@ -3873,7 +3882,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
     </row>
     <row r="116">
@@ -3881,7 +3890,7 @@
         <v>4</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>891</v>
+        <v>894</v>
       </c>
     </row>
     <row r="117">
@@ -3897,7 +3906,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>892</v>
+        <v>895</v>
       </c>
     </row>
     <row r="119">
@@ -3905,7 +3914,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>893</v>
+        <v>896</v>
       </c>
     </row>
     <row r="120">
@@ -4035,7 +4044,7 @@
         <v>530</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>894</v>
+        <v>897</v>
       </c>
     </row>
     <row r="137">
@@ -4051,7 +4060,7 @@
         <v>2</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
     </row>
     <row r="139">
@@ -4059,7 +4068,7 @@
         <v>4</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>896</v>
+        <v>899</v>
       </c>
     </row>
     <row r="140">
@@ -4075,7 +4084,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>897</v>
+        <v>900</v>
       </c>
     </row>
     <row r="142">
@@ -4083,7 +4092,7 @@
         <v>10</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>898</v>
+        <v>901</v>
       </c>
     </row>
     <row r="143">
@@ -4181,7 +4190,7 @@
         <v>32</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
     </row>
     <row r="156">
@@ -4189,7 +4198,7 @@
         <v>34</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>900</v>
+        <v>903</v>
       </c>
     </row>
     <row r="157">
@@ -4221,7 +4230,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
     </row>
     <row r="161">
@@ -4229,7 +4238,7 @@
         <v>4</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>908</v>
+        <v>911</v>
       </c>
     </row>
     <row r="162">
@@ -4245,7 +4254,7 @@
         <v>8</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>909</v>
+        <v>912</v>
       </c>
     </row>
     <row r="164">
@@ -4383,7 +4392,7 @@
         <v>530</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>910</v>
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -23095,16 +23104,16 @@
         <v>154</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>353</v>
+        <v>727</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="P179" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="Q179" t="s" s="2">
         <v>23</v>
@@ -23173,10 +23182,10 @@
         <v>706</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -23199,13 +23208,13 @@
         <v>86</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
@@ -23256,7 +23265,7 @@
         <v>23</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>77</v>
@@ -23276,10 +23285,10 @@
         <v>706</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -23305,13 +23314,13 @@
         <v>99</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P181" s="2"/>
       <c r="Q181" t="s" s="2">
@@ -23361,7 +23370,7 @@
         <v>23</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>77</v>
@@ -23381,14 +23390,14 @@
         <v>706</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="F182" s="2"/>
       <c r="G182" t="s" s="2">
@@ -23407,13 +23416,13 @@
         <v>86</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
@@ -23464,7 +23473,7 @@
         <v>23</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>77</v>
@@ -23484,14 +23493,14 @@
         <v>706</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F183" s="2"/>
       <c r="G183" t="s" s="2">
@@ -23510,16 +23519,16 @@
         <v>86</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="P183" s="2"/>
       <c r="Q183" t="s" s="2">
@@ -23569,7 +23578,7 @@
         <v>23</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>77</v>
@@ -23589,10 +23598,10 @@
         <v>706</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -23618,13 +23627,13 @@
         <v>105</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="P184" s="2"/>
       <c r="Q184" t="s" s="2">
@@ -23654,7 +23663,7 @@
       </c>
       <c r="Z184" s="2"/>
       <c r="AA184" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="AB184" t="s" s="2">
         <v>23</v>
@@ -23672,7 +23681,7 @@
         <v>23</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="AH184" t="s" s="2">
         <v>85</v>
@@ -23692,14 +23701,14 @@
         <v>706</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" t="s" s="2">
@@ -23721,13 +23730,13 @@
         <v>160</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="P185" s="2"/>
       <c r="Q185" t="s" s="2">
@@ -23756,10 +23765,10 @@
         <v>199</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="AA185" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AB185" t="s" s="2">
         <v>23</v>
@@ -23777,7 +23786,7 @@
         <v>23</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>77</v>
@@ -23797,10 +23806,10 @@
         <v>706</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -23826,10 +23835,10 @@
         <v>160</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" s="2"/>
@@ -23859,10 +23868,10 @@
         <v>199</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="AA186" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AB186" t="s" s="2">
         <v>23</v>
@@ -23880,7 +23889,7 @@
         <v>23</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AH186" t="s" s="2">
         <v>77</v>
@@ -23900,10 +23909,10 @@
         <v>706</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -23929,10 +23938,10 @@
         <v>160</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -23965,7 +23974,7 @@
       </c>
       <c r="Z187" s="2"/>
       <c r="AA187" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AB187" t="s" s="2">
         <v>23</v>
@@ -23983,7 +23992,7 @@
         <v>23</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>77</v>
@@ -24003,10 +24012,10 @@
         <v>706</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -24106,10 +24115,10 @@
         <v>706</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -24211,10 +24220,10 @@
         <v>706</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -24318,10 +24327,10 @@
         <v>706</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -24425,10 +24434,10 @@
         <v>706</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -24454,10 +24463,10 @@
         <v>227</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
@@ -24508,7 +24517,7 @@
         <v>23</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>85</v>
@@ -24528,10 +24537,10 @@
         <v>706</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -24557,13 +24566,13 @@
         <v>231</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>232</v>
+        <v>779</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="P193" s="2"/>
       <c r="Q193" t="s" s="2">
@@ -24613,7 +24622,7 @@
         <v>23</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>77</v>
@@ -24633,10 +24642,10 @@
         <v>706</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -24662,13 +24671,13 @@
         <v>239</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="N194" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="O194" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="P194" s="2"/>
       <c r="Q194" t="s" s="2">
@@ -24718,7 +24727,7 @@
         <v>23</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>77</v>
@@ -24738,10 +24747,10 @@
         <v>706</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -24767,7 +24776,7 @@
         <v>244</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="N195" t="s" s="2">
         <v>246</v>
@@ -24821,7 +24830,7 @@
         <v>23</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>77</v>
@@ -24841,10 +24850,10 @@
         <v>706</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -24870,10 +24879,10 @@
         <v>249</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" s="2"/>
@@ -24924,7 +24933,7 @@
         <v>23</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>77</v>
@@ -24944,10 +24953,10 @@
         <v>706</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -24973,10 +24982,10 @@
         <v>263</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
@@ -25027,7 +25036,7 @@
         <v>23</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>77</v>
@@ -25047,10 +25056,10 @@
         <v>706</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -25150,10 +25159,10 @@
         <v>706</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -25255,10 +25264,10 @@
         <v>706</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -25362,10 +25371,10 @@
         <v>706</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -25391,14 +25400,14 @@
         <v>160</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="Q201" t="s" s="2">
         <v>23</v>
@@ -25426,10 +25435,10 @@
         <v>199</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="AA201" t="s" s="2">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="AB201" t="s" s="2">
         <v>23</v>
@@ -25447,7 +25456,7 @@
         <v>23</v>
       </c>
       <c r="AG201" t="s" s="2">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="AH201" t="s" s="2">
         <v>77</v>
@@ -25467,10 +25476,10 @@
         <v>706</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -25493,17 +25502,17 @@
         <v>86</v>
       </c>
       <c r="L202" t="s" s="2">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="N202" t="s" s="2">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="Q202" t="s" s="2">
         <v>23</v>
@@ -25552,7 +25561,7 @@
         <v>23</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>85</v>
@@ -25572,10 +25581,10 @@
         <v>706</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -25598,17 +25607,17 @@
         <v>23</v>
       </c>
       <c r="L203" t="s" s="2">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="N203" t="s" s="2">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="Q203" t="s" s="2">
         <v>23</v>
@@ -25657,7 +25666,7 @@
         <v>23</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>77</v>
@@ -25677,10 +25686,10 @@
         <v>706</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -25703,17 +25712,17 @@
         <v>86</v>
       </c>
       <c r="L204" t="s" s="2">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="N204" t="s" s="2">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="Q204" t="s" s="2">
         <v>23</v>
@@ -25762,7 +25771,7 @@
         <v>23</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>77</v>
@@ -25782,10 +25791,10 @@
         <v>706</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -25811,13 +25820,13 @@
         <v>160</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="N205" t="s" s="2">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="O205" t="s" s="2">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
@@ -25846,10 +25855,10 @@
         <v>199</v>
       </c>
       <c r="Z205" t="s" s="2">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="AA205" t="s" s="2">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="AB205" t="s" s="2">
         <v>23</v>
@@ -25867,7 +25876,7 @@
         <v>23</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>77</v>
@@ -25887,10 +25896,10 @@
         <v>706</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -25913,16 +25922,16 @@
         <v>86</v>
       </c>
       <c r="L206" t="s" s="2">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="M206" t="s" s="2">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="N206" t="s" s="2">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="O206" t="s" s="2">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="P206" s="2"/>
       <c r="Q206" t="s" s="2">
@@ -25972,7 +25981,7 @@
         <v>23</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>77</v>
@@ -25992,10 +26001,10 @@
         <v>706</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -26021,13 +26030,13 @@
         <v>160</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="O207" t="s" s="2">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="P207" s="2"/>
       <c r="Q207" t="s" s="2">
@@ -26077,7 +26086,7 @@
         <v>23</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>77</v>
@@ -26097,10 +26106,10 @@
         <v>706</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -26126,13 +26135,13 @@
         <v>160</v>
       </c>
       <c r="M208" t="s" s="2">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="N208" t="s" s="2">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="O208" t="s" s="2">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="P208" s="2"/>
       <c r="Q208" t="s" s="2">
@@ -26161,10 +26170,10 @@
         <v>199</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="AA208" t="s" s="2">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="AB208" t="s" s="2">
         <v>23</v>
@@ -26182,7 +26191,7 @@
         <v>23</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>77</v>
@@ -26202,10 +26211,10 @@
         <v>706</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -26228,16 +26237,16 @@
         <v>23</v>
       </c>
       <c r="L209" t="s" s="2">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>499</v>
+        <v>841</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="O209" t="s" s="2">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="P209" s="2"/>
       <c r="Q209" t="s" s="2">
@@ -26287,7 +26296,7 @@
         <v>23</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>77</v>
@@ -26307,10 +26316,10 @@
         <v>706</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -26336,13 +26345,13 @@
         <v>160</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="P210" s="2"/>
       <c r="Q210" t="s" s="2">
@@ -26371,7 +26380,7 @@
         <v>199</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>845</v>
+        <v>848</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>387</v>
@@ -26392,7 +26401,7 @@
         <v>23</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>841</v>
+        <v>844</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>77</v>
@@ -26412,10 +26421,10 @@
         <v>706</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -26438,17 +26447,17 @@
         <v>23</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>849</v>
+        <v>852</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="Q211" t="s" s="2">
         <v>23</v>
@@ -26497,7 +26506,7 @@
         <v>23</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="AH211" t="s" s="2">
         <v>77</v>
@@ -26517,10 +26526,10 @@
         <v>706</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -26546,10 +26555,10 @@
         <v>160</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" s="2"/>
@@ -26579,28 +26588,28 @@
         <v>199</v>
       </c>
       <c r="Z212" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="AA212" t="s" s="2">
+        <v>858</v>
+      </c>
+      <c r="AB212" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC212" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD212" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE212" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF212" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG212" t="s" s="2">
         <v>854</v>
-      </c>
-      <c r="AA212" t="s" s="2">
-        <v>855</v>
-      </c>
-      <c r="AB212" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC212" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD212" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE212" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF212" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG212" t="s" s="2">
-        <v>851</v>
       </c>
       <c r="AH212" t="s" s="2">
         <v>77</v>
@@ -26620,10 +26629,10 @@
         <v>706</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -26649,10 +26658,10 @@
         <v>258</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>858</v>
+        <v>861</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" s="2"/>
@@ -26703,7 +26712,7 @@
         <v>23</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>77</v>
@@ -26723,10 +26732,10 @@
         <v>706</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>859</v>
+        <v>862</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -26826,10 +26835,10 @@
         <v>706</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>860</v>
+        <v>863</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -26931,10 +26940,10 @@
         <v>706</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>861</v>
+        <v>864</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -27036,10 +27045,10 @@
         <v>706</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>862</v>
+        <v>865</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -27139,10 +27148,10 @@
         <v>706</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>863</v>
+        <v>866</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -27242,10 +27251,10 @@
         <v>706</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -27271,10 +27280,10 @@
         <v>263</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>865</v>
+        <v>868</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>866</v>
+        <v>869</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" s="2"/>
@@ -27325,7 +27334,7 @@
         <v>23</v>
       </c>
       <c r="AG219" t="s" s="2">
-        <v>864</v>
+        <v>867</v>
       </c>
       <c r="AH219" t="s" s="2">
         <v>77</v>
@@ -27345,10 +27354,10 @@
         <v>706</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>867</v>
+        <v>870</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -27448,10 +27457,10 @@
         <v>706</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>868</v>
+        <v>871</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
@@ -27553,10 +27562,10 @@
         <v>706</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
@@ -27660,10 +27669,10 @@
         <v>706</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>870</v>
+        <v>873</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -27689,10 +27698,10 @@
         <v>160</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>871</v>
+        <v>874</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>872</v>
+        <v>875</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
@@ -27722,28 +27731,28 @@
         <v>109</v>
       </c>
       <c r="Z223" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="AA223" t="s" s="2">
+        <v>877</v>
+      </c>
+      <c r="AB223" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC223" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD223" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE223" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF223" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG223" t="s" s="2">
         <v>873</v>
-      </c>
-      <c r="AA223" t="s" s="2">
-        <v>874</v>
-      </c>
-      <c r="AB223" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC223" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD223" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE223" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF223" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG223" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>77</v>
@@ -27763,10 +27772,10 @@
         <v>706</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -27789,13 +27798,13 @@
         <v>23</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>878</v>
+        <v>881</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" s="2"/>
@@ -27846,7 +27855,7 @@
         <v>23</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>875</v>
+        <v>878</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>85</v>
@@ -27866,10 +27875,10 @@
         <v>706</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -27892,19 +27901,19 @@
         <v>23</v>
       </c>
       <c r="L225" t="s" s="2">
-        <v>880</v>
+        <v>883</v>
       </c>
       <c r="M225" t="s" s="2">
-        <v>881</v>
+        <v>884</v>
       </c>
       <c r="N225" t="s" s="2">
-        <v>882</v>
+        <v>885</v>
       </c>
       <c r="O225" t="s" s="2">
-        <v>883</v>
+        <v>886</v>
       </c>
       <c r="P225" t="s" s="2">
-        <v>884</v>
+        <v>887</v>
       </c>
       <c r="Q225" t="s" s="2">
         <v>23</v>
@@ -27953,7 +27962,7 @@
         <v>23</v>
       </c>
       <c r="AG225" t="s" s="2">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="AH225" t="s" s="2">
         <v>77</v>
@@ -27973,10 +27982,10 @@
         <v>706</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -28002,13 +28011,13 @@
         <v>160</v>
       </c>
       <c r="M226" t="s" s="2">
+        <v>889</v>
+      </c>
+      <c r="N226" t="s" s="2">
+        <v>890</v>
+      </c>
+      <c r="O226" t="s" s="2">
         <v>886</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>887</v>
-      </c>
-      <c r="O226" t="s" s="2">
-        <v>883</v>
       </c>
       <c r="P226" s="2"/>
       <c r="Q226" t="s" s="2">
@@ -28037,28 +28046,28 @@
         <v>199</v>
       </c>
       <c r="Z226" t="s" s="2">
+        <v>891</v>
+      </c>
+      <c r="AA226" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="AB226" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC226" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD226" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE226" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF226" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG226" t="s" s="2">
         <v>888</v>
-      </c>
-      <c r="AA226" t="s" s="2">
-        <v>889</v>
-      </c>
-      <c r="AB226" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC226" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD226" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE226" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF226" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG226" t="s" s="2">
-        <v>885</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>77</v>
@@ -28075,7 +28084,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>129</v>
@@ -28107,7 +28116,7 @@
         <v>79</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="N227" t="s" s="2">
         <v>272</v>
@@ -28178,7 +28187,7 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B228" t="s" s="2">
         <v>534</v>
@@ -28281,7 +28290,7 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B229" t="s" s="2">
         <v>535</v>
@@ -28384,7 +28393,7 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B230" t="s" s="2">
         <v>547</v>
@@ -28430,7 +28439,7 @@
       </c>
       <c r="R230" s="2"/>
       <c r="S230" t="s" s="2">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="T230" t="s" s="2">
         <v>23</v>
@@ -28489,7 +28498,7 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>890</v>
+        <v>893</v>
       </c>
       <c r="B231" t="s" s="2">
         <v>553</v>
@@ -28592,13 +28601,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -28624,13 +28633,13 @@
         <v>79</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="P232" s="2"/>
       <c r="Q232" t="s" s="2">
@@ -28680,7 +28689,7 @@
         <v>23</v>
       </c>
       <c r="AG232" t="s" s="2">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="AH232" t="s" s="2">
         <v>77</v>
@@ -28692,18 +28701,18 @@
         <v>140</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>904</v>
+        <v>907</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -28800,13 +28809,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -28905,7 +28914,7 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>681</v>
@@ -29010,7 +29019,7 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B236" t="s" s="2">
         <v>689</v>
@@ -29115,7 +29124,7 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B237" t="s" s="2">
         <v>694</v>
@@ -29220,7 +29229,7 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B238" t="s" s="2">
         <v>699</v>
@@ -29325,7 +29334,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>129</v>
@@ -29428,7 +29437,7 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B240" t="s" s="2">
         <v>534</v>
@@ -29531,7 +29540,7 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B241" t="s" s="2">
         <v>535</v>
@@ -29634,7 +29643,7 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B242" t="s" s="2">
         <v>547</v>
@@ -29680,7 +29689,7 @@
       </c>
       <c r="R242" s="2"/>
       <c r="S242" t="s" s="2">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="T242" t="s" s="2">
         <v>23</v>
@@ -29739,7 +29748,7 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B243" t="s" s="2">
         <v>553</v>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:03:03+00:00</t>
+    <t>2026-09-08T06:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -501,7 +501,7 @@
 </t>
   </si>
   <si>
-    <t>Zuordnung der Allergie in einem internen Dokumentationssystem</t>
+    <t>Zuordnung der Allergie in einem internen Dokumentationssystem.</t>
   </si>
   <si>
     <t>Business identifiers assigned to this AllergyIntolerance by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -520,7 +520,7 @@
 </t>
   </si>
   <si>
-    <t>Status der Allergie; active | inactive | resolved</t>
+    <t>Status der Allergie; mögliche Codes: active | inactive | resolved.</t>
   </si>
   <si>
     <t>The clinical status of the allergy or intolerance.</t>
@@ -543,7 +543,7 @@
     <t>AllergyIntolerance.verificationStatus</t>
   </si>
   <si>
-    <t>Verifizierungsstatus der Allergie. Möglicher Status; unconfirmed | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Allergie; mögliche Codes: unconfirmed | confirmed | refuted | entered-in-error.</t>
   </si>
   <si>
     <t>Assertion about certainty associated with the propensity, or potential risk, of a reaction to the identified substance (including pharmaceutical product).</t>
@@ -565,7 +565,7 @@
 Class</t>
   </si>
   <si>
-    <t>Identifikation ob es eine Allergie oder Intoleranz ist</t>
+    <t>Kennzeichnung, ob es sich um eine Allergie oder Intoleranz handelt.</t>
   </si>
   <si>
     <t>Identification of the underlying physiological mechanism for the reaction risk.</t>
@@ -587,7 +587,7 @@
 TypeReaction TypeClass</t>
   </si>
   <si>
-    <t>Differenzierung nach Kontext - Medikamente, Lebensmittel, Umwelt,.. - falls nur med. rele. dann ist es nicht notwendig, fachlich klären</t>
+    <t>ToDo - falls nur med. rele. dann ist es nicht notwendig, fachlich klären: Differenzierung nach Kontext z. B. Medikamente, Lebensmittel oder Umwelt.</t>
   </si>
   <si>
     <t>Category of the identified substance.</t>
@@ -609,7 +609,7 @@
 SeriousnessContra-indicationRisk</t>
   </si>
   <si>
-    <t>Einschätzung der Schwere (Anaphylaxie)</t>
+    <t>Einschätzung des Schweregrads, z. B. im Hinblick auf eine Anaphylaxie.</t>
   </si>
   <si>
     <t>Estimate of the potential clinical harm, or seriousness, of the reaction to the identified substance.</t>
@@ -631,7 +631,7 @@
 </t>
   </si>
   <si>
-    <t>Allergiecode, Text verboten</t>
+    <t>Allergiecode; Freitext ist nicht zulässig.</t>
   </si>
   <si>
     <t>Code for an allergy or intolerance statement (either a positive or a negated/excluded statement).  This may be a code for a substance or pharmaceutical product that is considered to be responsible for the adverse reaction risk (e.g., "Latex"), an allergy or intolerance condition (e.g., "Latex allergy"), or a negated/excluded code for a specific substance or class (e.g., "No latex allergy") or a general or categorical negated statement (e.g.,  "No known allergy", "No known drug allergies").  Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
@@ -735,7 +735,7 @@
 </t>
   </si>
   <si>
-    <t>Betroffene Person, auf die sich die Allergie bezieht</t>
+    <t>Betroffene Person, auf die sich die Allergie bezieht.</t>
   </si>
   <si>
     <t>The patient who has the allergy or intolerance.</t>
@@ -748,7 +748,7 @@
 </t>
   </si>
   <si>
-    <t>Behandlungskontakt</t>
+    <t>Behandlungskontakt.</t>
   </si>
   <si>
     <t>The encounter when the allergy or intolerance was asserted.</t>
@@ -761,7 +761,7 @@
 AgePeriodRangestring</t>
   </si>
   <si>
-    <t>Erstes Aufzeichnungsdatum der Allergie(symptomatik)</t>
+    <t>Erstes Aufzeichnungsdatum der Allergie bzw. Allergiesymptomatik.</t>
   </si>
   <si>
     <t>Estimated or actual date,  date-time, or age when allergy or intolerance was identified.</t>
@@ -774,7 +774,7 @@
 </t>
   </si>
   <si>
-    <t>Dokumentationsdatum</t>
+    <t>Dokumentationsdatum.</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular AllergyIntolerance record was created in the system, which is often a system-generated date.</t>
@@ -791,7 +791,7 @@
 </t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, die die Allergie ins System erfasst/dokumentiert</t>
+    <t>Gesundheitsdiensteanbieter, der die Allergie im System erfasst bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -808,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t>Person (fachliche Quelle + related Person oder Patient selbst), die/der die Allergie bestätigt</t>
+    <t>Quelle der Information zur Allergie, z. B. Patient, behandelnde Person oder Dritter.</t>
   </si>
   <si>
     <t>The source of the information about the allergy that is recorded.</t>
@@ -820,7 +820,7 @@
     <t>AllergyIntolerance.lastOccurrence</t>
   </si>
   <si>
-    <t>Letztes Auftreten der Symptomatik - siehe manifestation</t>
+    <t>Letztes Auftreten der Symptomatik; siehe Manifestation.</t>
   </si>
   <si>
     <t>Represents the date and/or time of the last known occurrence of a reaction event.</t>
@@ -836,7 +836,7 @@
 </t>
   </si>
   <si>
-    <t>Zusätzliche Informationen oder Freitext zur Allergie wird in reaction beschrieben</t>
+    <t>Zusätzliche Informationen; Freitext wird in reaction beschrieben.</t>
   </si>
   <si>
     <t>Additional narrative about the propensity for the Adverse Reaction, not captured in other fields.</t>
@@ -852,7 +852,7 @@
 </t>
   </si>
   <si>
-    <t>Details über die Allergiereaktion</t>
+    <t>Details zur allergischen Reaktion.</t>
   </si>
   <si>
     <t>Details about each adverse reaction event linked to exposure to the identified substance.</t>
@@ -874,7 +874,7 @@
 </t>
   </si>
   <si>
-    <t>Zeitlicher Verlauf der Manifestation</t>
+    <t>Zeitlicher Verlauf der Manifestation.</t>
   </si>
   <si>
     <t>Zeitlicher Verlauf der Manifestation (&lt;6h, 6-24h, &gt;24h, unknown)</t>
@@ -900,7 +900,7 @@
     <t>AllergyIntolerance.reaction.substance</t>
   </si>
   <si>
-    <t>Spezifische Substanz die zur Allergie führt, wird in allergyintoleranz.code gelöst</t>
+    <t>Spezifische Substanz, die zur Allergie führt; wird über AllergyIntolerance.code abgebildet.</t>
   </si>
   <si>
     <t>Identification of the specific substance (or pharmaceutical product) considered to be responsible for the Adverse Reaction event. Note: the substance for a specific reaction may be different from the substance identified as the cause of the risk, but it must be consistent with it. For instance, it may be a more specific substance (e.g. a brand medication) or a composite product that includes the identified substance. It must be clinically safe to only process the 'code' and ignore the 'reaction.substance'.  If a receiving system is unable to confirm that AllergyIntolerance.reaction.substance falls within the semantic scope of AllergyIntolerance.code, then the receiving system should ignore AllergyIntolerance.reaction.substance.</t>
@@ -922,7 +922,7 @@
 Signs</t>
   </si>
   <si>
-    <t>Aufgezeichnete klinische allergische Symptome</t>
+    <t>Aufgezeichnete klinische Symptome der allergischen Reaktion.</t>
   </si>
   <si>
     <t>Clinical symptoms and/or signs that are observed or associated with the adverse reaction event.</t>
@@ -944,7 +944,7 @@
 Text</t>
   </si>
   <si>
-    <t>Textbasierte Zusammenfassung der allergischen Reaktion</t>
+    <t>Textbasierte Zusammenfassung der allergischen Reaktion.</t>
   </si>
   <si>
     <t>Text description about the reaction as a whole, including details of the manifestation if required.</t>
@@ -956,7 +956,7 @@
     <t>AllergyIntolerance.reaction.onset</t>
   </si>
   <si>
-    <t>Beginn der Reaktion</t>
+    <t>Beginn der Reaktion.</t>
   </si>
   <si>
     <t>Record of the date and/or time of the onset of the Reaction.</t>
@@ -965,7 +965,7 @@
     <t>AllergyIntolerance.reaction.severity</t>
   </si>
   <si>
-    <t>Beschreibt ob die Reaktion mild, moderat,... war</t>
+    <t>Schweregrad der Reaktion, z. B. mild oder moderat.</t>
   </si>
   <si>
     <t>Clinical assessment of the severity of the reaction event as a whole, potentially considering multiple different manifestations.</t>
@@ -983,7 +983,7 @@
     <t>AllergyIntolerance.reaction.exposureRoute</t>
   </si>
   <si>
-    <t>Art der Exposition der betroffenen Person gegenüber der Substanz</t>
+    <t>Art der Exposition der betroffenen Person gegenüber der Substanz.</t>
   </si>
   <si>
     <t>Identification of the route by which the subject was exposed to the substance.</t>
@@ -1001,7 +1001,7 @@
     <t>AllergyIntolerance.reaction.note</t>
   </si>
   <si>
-    <t>Freitext zu Allergie und Intoleranzen als Zusatzinformation</t>
+    <t>Freitext zu Allergie und Intoleranzen als Zusatzinformation.</t>
   </si>
   <si>
     <t>Additional text about the adverse reaction event not captured in other fields.</t>
@@ -1444,6 +1444,9 @@
   </si>
   <si>
     <t>Condition.encounter</t>
+  </si>
+  <si>
+    <t>Behandlungskontakt</t>
   </si>
   <si>
     <t>The Encounter during which this Condition was created or to which the creation of this record is tightly associated.</t>
@@ -2440,9 +2443,6 @@
   </si>
   <si>
     <t>Procedure.encounter</t>
-  </si>
-  <si>
-    <t>Behandlungskontakt.</t>
   </si>
   <si>
     <t>The Encounter during which this Procedure was created or performed or to which the creation of this record is tightly associated.</t>
@@ -3348,7 +3348,7 @@
         <v>2</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="47">
@@ -3356,7 +3356,7 @@
         <v>4</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="48">
@@ -3372,7 +3372,7 @@
         <v>8</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
     </row>
     <row r="50">
@@ -3388,7 +3388,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="52">
@@ -3470,7 +3470,7 @@
         <v>30</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="63">
@@ -3486,7 +3486,7 @@
         <v>34</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="65">
@@ -3507,26 +3507,26 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
     </row>
     <row r="70">
@@ -3542,7 +3542,7 @@
         <v>2</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
     </row>
     <row r="72">
@@ -3550,7 +3550,7 @@
         <v>4</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="73">
@@ -3566,7 +3566,7 @@
         <v>8</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="75">
@@ -3574,7 +3574,7 @@
         <v>10</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
     </row>
     <row r="76">
@@ -3636,7 +3636,7 @@
         <v>24</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
     </row>
     <row r="84">
@@ -3672,7 +3672,7 @@
         <v>32</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="89">
@@ -3680,7 +3680,7 @@
         <v>34</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
     </row>
     <row r="90">
@@ -3712,7 +3712,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="94">
@@ -3720,7 +3720,7 @@
         <v>4</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="95">
@@ -3736,7 +3736,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="97">
@@ -3744,7 +3744,7 @@
         <v>10</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="98">
@@ -3806,7 +3806,7 @@
         <v>24</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="106">
@@ -3842,7 +3842,7 @@
         <v>32</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="111">
@@ -3850,7 +3850,7 @@
         <v>34</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="112">
@@ -4004,7 +4004,7 @@
         <v>30</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="132">
@@ -4020,7 +4020,7 @@
         <v>34</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="134">
@@ -4041,7 +4041,7 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B136" t="s" s="2">
         <v>897</v>
@@ -4182,7 +4182,7 @@
         <v>30</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="155">
@@ -4270,7 +4270,7 @@
         <v>12</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
     </row>
     <row r="166">
@@ -4352,7 +4352,7 @@
         <v>30</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
     </row>
     <row r="177">
@@ -4368,7 +4368,7 @@
         <v>34</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="179">
@@ -4389,7 +4389,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>913</v>
@@ -13603,13 +13603,13 @@
         <v>231</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>232</v>
+        <v>457</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P88" s="2"/>
       <c r="Q88" t="s" s="2">
@@ -13679,10 +13679,10 @@
         <v>332</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -13708,13 +13708,13 @@
         <v>239</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="P89" s="2"/>
       <c r="Q89" t="s" s="2">
@@ -13764,7 +13764,7 @@
         <v>23</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>77</v>
@@ -13784,10 +13784,10 @@
         <v>332</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -13813,13 +13813,13 @@
         <v>239</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
@@ -13869,7 +13869,7 @@
         <v>23</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>77</v>
@@ -13878,7 +13878,7 @@
         <v>85</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>97</v>
@@ -13889,10 +13889,10 @@
         <v>332</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -13918,10 +13918,10 @@
         <v>239</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -13972,7 +13972,7 @@
         <v>23</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>77</v>
@@ -13992,10 +13992,10 @@
         <v>332</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -14021,7 +14021,7 @@
         <v>244</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>246</v>
@@ -14075,7 +14075,7 @@
         <v>23</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>77</v>
@@ -14095,10 +14095,10 @@
         <v>332</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -14124,10 +14124,10 @@
         <v>249</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
@@ -14178,7 +14178,7 @@
         <v>23</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>77</v>
@@ -14198,10 +14198,10 @@
         <v>332</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -14227,10 +14227,10 @@
         <v>263</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
@@ -14281,7 +14281,7 @@
         <v>23</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>77</v>
@@ -14293,7 +14293,7 @@
         <v>23</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="95">
@@ -14301,10 +14301,10 @@
         <v>332</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -14404,10 +14404,10 @@
         <v>332</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -14509,10 +14509,10 @@
         <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -14616,10 +14616,10 @@
         <v>332</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -14645,10 +14645,10 @@
         <v>160</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
@@ -14678,10 +14678,10 @@
         <v>199</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AA98" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AB98" t="s" s="2">
         <v>23</v>
@@ -14699,7 +14699,7 @@
         <v>23</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>77</v>
@@ -14708,7 +14708,7 @@
         <v>85</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>97</v>
@@ -14719,10 +14719,10 @@
         <v>332</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -14745,13 +14745,13 @@
         <v>23</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -14802,7 +14802,7 @@
         <v>23</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>77</v>
@@ -14811,7 +14811,7 @@
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>97</v>
@@ -14822,10 +14822,10 @@
         <v>332</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -14851,10 +14851,10 @@
         <v>160</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -14884,10 +14884,10 @@
         <v>199</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA100" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AB100" t="s" s="2">
         <v>23</v>
@@ -14905,7 +14905,7 @@
         <v>23</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>77</v>
@@ -14925,10 +14925,10 @@
         <v>332</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -14954,13 +14954,13 @@
         <v>263</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P101" s="2"/>
       <c r="Q101" t="s" s="2">
@@ -15010,7 +15010,7 @@
         <v>23</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>77</v>
@@ -15022,7 +15022,7 @@
         <v>23</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="102">
@@ -15030,10 +15030,10 @@
         <v>332</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -15133,10 +15133,10 @@
         <v>332</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -15238,10 +15238,10 @@
         <v>332</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -15345,10 +15345,10 @@
         <v>332</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -15374,10 +15374,10 @@
         <v>160</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
@@ -15407,10 +15407,10 @@
         <v>199</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AA105" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AB105" t="s" s="2">
         <v>23</v>
@@ -15428,7 +15428,7 @@
         <v>23</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>77</v>
@@ -15437,7 +15437,7 @@
         <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>97</v>
@@ -15448,10 +15448,10 @@
         <v>332</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -15474,13 +15474,13 @@
         <v>86</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
@@ -15531,7 +15531,7 @@
         <v>23</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>77</v>
@@ -15540,7 +15540,7 @@
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>97</v>
@@ -15551,10 +15551,10 @@
         <v>332</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -15580,10 +15580,10 @@
         <v>258</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
@@ -15634,7 +15634,7 @@
         <v>23</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>77</v>
@@ -15654,10 +15654,10 @@
         <v>332</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -15757,10 +15757,10 @@
         <v>332</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -15862,10 +15862,10 @@
         <v>332</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -15967,10 +15967,10 @@
         <v>332</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -16070,10 +16070,10 @@
         <v>332</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -16170,7 +16170,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>129</v>
@@ -16273,13 +16273,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -16376,13 +16376,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -16479,16 +16479,16 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B116" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="C116" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="C116" t="s" s="2">
-        <v>535</v>
-      </c>
       <c r="D116" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="E116" t="s" s="2">
         <v>23</v>
@@ -16584,13 +16584,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -16687,13 +16687,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -16790,13 +16790,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -16822,13 +16822,13 @@
         <v>99</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P119" s="2"/>
       <c r="Q119" t="s" s="2">
@@ -16836,7 +16836,7 @@
       </c>
       <c r="R119" s="2"/>
       <c r="S119" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>23</v>
@@ -16878,7 +16878,7 @@
         <v>23</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>85</v>
@@ -16895,13 +16895,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -16924,13 +16924,13 @@
         <v>23</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
@@ -16981,7 +16981,7 @@
         <v>23</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>77</v>
@@ -16998,16 +16998,16 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D121" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="E121" t="s" s="2">
         <v>23</v>
@@ -17103,13 +17103,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -17206,13 +17206,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -17309,13 +17309,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -17341,13 +17341,13 @@
         <v>99</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P124" s="2"/>
       <c r="Q124" t="s" s="2">
@@ -17355,7 +17355,7 @@
       </c>
       <c r="R124" s="2"/>
       <c r="S124" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>23</v>
@@ -17397,7 +17397,7 @@
         <v>23</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>85</v>
@@ -17414,13 +17414,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -17446,10 +17446,10 @@
         <v>239</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
@@ -17500,7 +17500,7 @@
         <v>23</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>77</v>
@@ -17517,16 +17517,16 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D126" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="E126" t="s" s="2">
         <v>23</v>
@@ -17622,13 +17622,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -17725,13 +17725,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -17828,13 +17828,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -17860,13 +17860,13 @@
         <v>99</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P129" s="2"/>
       <c r="Q129" t="s" s="2">
@@ -17874,7 +17874,7 @@
       </c>
       <c r="R129" s="2"/>
       <c r="S129" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>23</v>
@@ -17916,7 +17916,7 @@
         <v>23</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>85</v>
@@ -17933,13 +17933,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -17965,10 +17965,10 @@
         <v>203</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
@@ -18019,7 +18019,7 @@
         <v>23</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>77</v>
@@ -18036,13 +18036,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -18068,13 +18068,13 @@
         <v>99</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P131" s="2"/>
       <c r="Q131" t="s" s="2">
@@ -18082,7 +18082,7 @@
       </c>
       <c r="R131" s="2"/>
       <c r="S131" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>23</v>
@@ -18124,7 +18124,7 @@
         <v>23</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>85</v>
@@ -18141,13 +18141,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -18170,13 +18170,13 @@
         <v>23</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
@@ -18227,7 +18227,7 @@
         <v>23</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>77</v>
@@ -18244,17 +18244,17 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" t="s" s="2">
@@ -18276,10 +18276,10 @@
         <v>79</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
@@ -18330,7 +18330,7 @@
         <v>23</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>77</v>
@@ -18342,18 +18342,18 @@
         <v>23</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -18452,13 +18452,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -18555,13 +18555,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -18660,13 +18660,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -18765,13 +18765,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -18870,13 +18870,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -18975,13 +18975,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -19010,7 +19010,7 @@
         <v>208</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="O140" t="s" s="2">
         <v>150</v>
@@ -19080,13 +19080,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -19187,13 +19187,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -19219,10 +19219,10 @@
         <v>154</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
@@ -19273,7 +19273,7 @@
         <v>23</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>77</v>
@@ -19290,13 +19290,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -19322,13 +19322,13 @@
         <v>105</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O143" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P143" s="2"/>
       <c r="Q143" t="s" s="2">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="R143" s="2"/>
       <c r="S143" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>23</v>
@@ -19357,10 +19357,10 @@
         <v>164</v>
       </c>
       <c r="Z143" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AA143" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AB143" t="s" s="2">
         <v>23</v>
@@ -19378,7 +19378,7 @@
         <v>23</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>85</v>
@@ -19395,13 +19395,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -19427,23 +19427,23 @@
         <v>105</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="P144" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="Q144" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R144" s="2"/>
       <c r="S144" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>23</v>
@@ -19464,10 +19464,10 @@
         <v>164</v>
       </c>
       <c r="Z144" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AA144" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AB144" t="s" s="2">
         <v>23</v>
@@ -19485,7 +19485,7 @@
         <v>23</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>85</v>
@@ -19502,13 +19502,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -19534,14 +19534,14 @@
         <v>203</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="Q145" t="s" s="2">
         <v>23</v>
@@ -19554,7 +19554,7 @@
         <v>23</v>
       </c>
       <c r="U145" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="V145" t="s" s="2">
         <v>23</v>
@@ -19590,7 +19590,7 @@
         <v>23</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>77</v>
@@ -19607,13 +19607,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -19639,16 +19639,16 @@
         <v>160</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P146" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="Q146" t="s" s="2">
         <v>23</v>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="Z146" s="2"/>
       <c r="AA146" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AB146" t="s" s="2">
         <v>23</v>
@@ -19695,7 +19695,7 @@
         <v>23</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>77</v>
@@ -19712,13 +19712,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -19744,16 +19744,16 @@
         <v>227</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="P147" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Q147" t="s" s="2">
         <v>23</v>
@@ -19802,7 +19802,7 @@
         <v>23</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>77</v>
@@ -19819,13 +19819,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -19851,10 +19851,10 @@
         <v>231</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
@@ -19905,7 +19905,7 @@
         <v>23</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>77</v>
@@ -19922,13 +19922,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -19954,16 +19954,16 @@
         <v>239</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="P149" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="Q149" t="s" s="2">
         <v>23</v>
@@ -20012,7 +20012,7 @@
         <v>23</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>77</v>
@@ -20029,13 +20029,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -20058,19 +20058,19 @@
         <v>86</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="P150" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="Q150" t="s" s="2">
         <v>23</v>
@@ -20119,7 +20119,7 @@
         <v>23</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>77</v>
@@ -20136,13 +20136,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -20168,16 +20168,16 @@
         <v>160</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="P151" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="Q151" t="s" s="2">
         <v>23</v>
@@ -20205,10 +20205,10 @@
         <v>109</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AA151" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AB151" t="s" s="2">
         <v>23</v>
@@ -20226,7 +20226,7 @@
         <v>23</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>77</v>
@@ -20243,13 +20243,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -20275,10 +20275,10 @@
         <v>258</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -20329,7 +20329,7 @@
         <v>23</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>77</v>
@@ -20346,13 +20346,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -20378,13 +20378,13 @@
         <v>263</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="N153" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="O153" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="P153" s="2"/>
       <c r="Q153" t="s" s="2">
@@ -20434,7 +20434,7 @@
         <v>23</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>77</v>
@@ -20443,7 +20443,7 @@
         <v>78</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>97</v>
@@ -20451,13 +20451,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -20554,13 +20554,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -20659,13 +20659,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -20766,13 +20766,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -20798,16 +20798,16 @@
         <v>160</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="N157" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="O157" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="P157" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Q157" t="s" s="2">
         <v>23</v>
@@ -20835,10 +20835,10 @@
         <v>199</v>
       </c>
       <c r="Z157" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AA157" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AB157" t="s" s="2">
         <v>23</v>
@@ -20856,7 +20856,7 @@
         <v>23</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>77</v>
@@ -20873,13 +20873,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -20905,68 +20905,68 @@
         <v>428</v>
       </c>
       <c r="M158" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="N158" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="O158" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="P158" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="Q158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R158" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="S158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG158" t="s" s="2">
         <v>661</v>
       </c>
-      <c r="N158" t="s" s="2">
-        <v>662</v>
-      </c>
-      <c r="O158" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="P158" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="Q158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R158" t="s" s="2">
-        <v>665</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>660</v>
-      </c>
       <c r="AH158" t="s" s="2">
         <v>77</v>
       </c>
@@ -20974,7 +20974,7 @@
         <v>85</v>
       </c>
       <c r="AJ158" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>97</v>
@@ -20982,13 +20982,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -21014,14 +21014,14 @@
         <v>239</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="Q159" t="s" s="2">
         <v>23</v>
@@ -21070,7 +21070,7 @@
         <v>23</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>77</v>
@@ -21087,13 +21087,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -21116,13 +21116,13 @@
         <v>23</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="N160" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
@@ -21173,7 +21173,7 @@
         <v>23</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>85</v>
@@ -21190,13 +21190,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -21293,13 +21293,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -21398,13 +21398,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -21430,13 +21430,13 @@
         <v>203</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="P163" s="2"/>
       <c r="Q163" t="s" s="2">
@@ -21486,7 +21486,7 @@
         <v>23</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>77</v>
@@ -21495,7 +21495,7 @@
         <v>85</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>97</v>
@@ -21503,13 +21503,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -21535,13 +21535,13 @@
         <v>99</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P164" s="2"/>
       <c r="Q164" t="s" s="2">
@@ -21570,10 +21570,10 @@
         <v>374</v>
       </c>
       <c r="Z164" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AA164" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AB164" t="s" s="2">
         <v>23</v>
@@ -21591,7 +21591,7 @@
         <v>23</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>77</v>
@@ -21608,13 +21608,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -21640,13 +21640,13 @@
         <v>154</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
@@ -21696,7 +21696,7 @@
         <v>23</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>77</v>
@@ -21713,13 +21713,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -21745,13 +21745,13 @@
         <v>203</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N166" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O166" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P166" s="2"/>
       <c r="Q166" t="s" s="2">
@@ -21801,7 +21801,7 @@
         <v>23</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>77</v>
@@ -21818,13 +21818,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -21850,16 +21850,16 @@
         <v>160</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="P167" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="Q167" t="s" s="2">
         <v>23</v>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="Z167" s="2"/>
       <c r="AA167" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="AB167" t="s" s="2">
         <v>23</v>
@@ -21906,7 +21906,7 @@
         <v>23</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>77</v>
@@ -21915,7 +21915,7 @@
         <v>85</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>97</v>
@@ -21923,13 +21923,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -21955,10 +21955,10 @@
         <v>79</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="N168" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
@@ -22009,7 +22009,7 @@
         <v>23</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>77</v>
@@ -22021,18 +22021,18 @@
         <v>23</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -22131,13 +22131,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -22234,13 +22234,13 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -22339,13 +22339,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -22444,13 +22444,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -22549,13 +22549,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -22654,13 +22654,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -22755,13 +22755,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B176" t="s" s="2">
+        <v>724</v>
+      </c>
+      <c r="C176" t="s" s="2">
         <v>723</v>
-      </c>
-      <c r="C176" t="s" s="2">
-        <v>722</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>136</v>
@@ -22860,13 +22860,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>142</v>
@@ -22965,13 +22965,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -23072,13 +23072,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -23104,16 +23104,16 @@
         <v>154</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="O179" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="P179" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Q179" t="s" s="2">
         <v>23</v>
@@ -23162,7 +23162,7 @@
         <v>23</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AH179" t="s" s="2">
         <v>77</v>
@@ -23179,13 +23179,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -23208,13 +23208,13 @@
         <v>86</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
@@ -23265,7 +23265,7 @@
         <v>23</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>77</v>
@@ -23282,13 +23282,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -23314,13 +23314,13 @@
         <v>99</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="O181" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="P181" s="2"/>
       <c r="Q181" t="s" s="2">
@@ -23370,7 +23370,7 @@
         <v>23</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>77</v>
@@ -23387,17 +23387,17 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="F182" s="2"/>
       <c r="G182" t="s" s="2">
@@ -23416,13 +23416,13 @@
         <v>86</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
@@ -23473,7 +23473,7 @@
         <v>23</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>77</v>
@@ -23490,17 +23490,17 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="F183" s="2"/>
       <c r="G183" t="s" s="2">
@@ -23519,16 +23519,16 @@
         <v>86</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="O183" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="P183" s="2"/>
       <c r="Q183" t="s" s="2">
@@ -23578,7 +23578,7 @@
         <v>23</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>77</v>
@@ -23595,13 +23595,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -23627,13 +23627,13 @@
         <v>105</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="P184" s="2"/>
       <c r="Q184" t="s" s="2">
@@ -23663,7 +23663,7 @@
       </c>
       <c r="Z184" s="2"/>
       <c r="AA184" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="AB184" t="s" s="2">
         <v>23</v>
@@ -23681,7 +23681,7 @@
         <v>23</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="AH184" t="s" s="2">
         <v>85</v>
@@ -23698,17 +23698,17 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" t="s" s="2">
@@ -23730,13 +23730,13 @@
         <v>160</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="N185" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="O185" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="P185" s="2"/>
       <c r="Q185" t="s" s="2">
@@ -23765,10 +23765,10 @@
         <v>199</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="AA185" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="AB185" t="s" s="2">
         <v>23</v>
@@ -23786,7 +23786,7 @@
         <v>23</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>77</v>
@@ -23803,13 +23803,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -23835,10 +23835,10 @@
         <v>160</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" s="2"/>
@@ -23868,10 +23868,10 @@
         <v>199</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="AA186" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="AB186" t="s" s="2">
         <v>23</v>
@@ -23889,7 +23889,7 @@
         <v>23</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="AH186" t="s" s="2">
         <v>77</v>
@@ -23906,13 +23906,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -23938,10 +23938,10 @@
         <v>160</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -23974,7 +23974,7 @@
       </c>
       <c r="Z187" s="2"/>
       <c r="AA187" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AB187" t="s" s="2">
         <v>23</v>
@@ -23992,7 +23992,7 @@
         <v>23</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>77</v>
@@ -24009,13 +24009,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -24112,13 +24112,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -24217,13 +24217,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -24324,13 +24324,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -24431,13 +24431,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -24463,10 +24463,10 @@
         <v>227</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
@@ -24517,7 +24517,7 @@
         <v>23</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>85</v>
@@ -24534,13 +24534,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -24566,7 +24566,7 @@
         <v>231</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>779</v>
+        <v>232</v>
       </c>
       <c r="N193" t="s" s="2">
         <v>780</v>
@@ -24622,7 +24622,7 @@
         <v>23</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>77</v>
@@ -24639,7 +24639,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>782</v>
@@ -24744,7 +24744,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>786</v>
@@ -24847,7 +24847,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>788</v>
@@ -24950,7 +24950,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>791</v>
@@ -25053,7 +25053,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>794</v>
@@ -25156,7 +25156,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>795</v>
@@ -25261,7 +25261,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>796</v>
@@ -25368,7 +25368,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>797</v>
@@ -25473,7 +25473,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>803</v>
@@ -25578,7 +25578,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>808</v>
@@ -25683,7 +25683,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>813</v>
@@ -25788,7 +25788,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>818</v>
@@ -25893,7 +25893,7 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B206" t="s" s="2">
         <v>824</v>
@@ -25998,7 +25998,7 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B207" t="s" s="2">
         <v>829</v>
@@ -26103,7 +26103,7 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>833</v>
@@ -26208,7 +26208,7 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B209" t="s" s="2">
         <v>839</v>
@@ -26313,7 +26313,7 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>844</v>
@@ -26418,7 +26418,7 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B211" t="s" s="2">
         <v>849</v>
@@ -26523,7 +26523,7 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B212" t="s" s="2">
         <v>854</v>
@@ -26626,7 +26626,7 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B213" t="s" s="2">
         <v>859</v>
@@ -26729,7 +26729,7 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B214" t="s" s="2">
         <v>862</v>
@@ -26832,7 +26832,7 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B215" t="s" s="2">
         <v>863</v>
@@ -26937,7 +26937,7 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B216" t="s" s="2">
         <v>864</v>
@@ -27042,7 +27042,7 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B217" t="s" s="2">
         <v>865</v>
@@ -27145,7 +27145,7 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B218" t="s" s="2">
         <v>866</v>
@@ -27248,7 +27248,7 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B219" t="s" s="2">
         <v>867</v>
@@ -27351,7 +27351,7 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B220" t="s" s="2">
         <v>870</v>
@@ -27454,7 +27454,7 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B221" t="s" s="2">
         <v>871</v>
@@ -27559,7 +27559,7 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B222" t="s" s="2">
         <v>872</v>
@@ -27666,7 +27666,7 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B223" t="s" s="2">
         <v>873</v>
@@ -27769,7 +27769,7 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B224" t="s" s="2">
         <v>878</v>
@@ -27872,7 +27872,7 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B225" t="s" s="2">
         <v>882</v>
@@ -27979,7 +27979,7 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B226" t="s" s="2">
         <v>888</v>
@@ -28190,10 +28190,10 @@
         <v>893</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -28293,10 +28293,10 @@
         <v>893</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -28396,10 +28396,10 @@
         <v>893</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -28425,13 +28425,13 @@
         <v>99</v>
       </c>
       <c r="M230" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N230" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O230" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P230" s="2"/>
       <c r="Q230" t="s" s="2">
@@ -28481,7 +28481,7 @@
         <v>23</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AH230" t="s" s="2">
         <v>85</v>
@@ -28501,10 +28501,10 @@
         <v>893</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -28530,10 +28530,10 @@
         <v>160</v>
       </c>
       <c r="M231" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N231" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O231" s="2"/>
       <c r="P231" s="2"/>
@@ -28584,7 +28584,7 @@
         <v>23</v>
       </c>
       <c r="AG231" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AH231" t="s" s="2">
         <v>77</v>
@@ -28917,10 +28917,10 @@
         <v>898</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -28946,13 +28946,13 @@
         <v>203</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="O235" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="P235" s="2"/>
       <c r="Q235" t="s" s="2">
@@ -29002,7 +29002,7 @@
         <v>23</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>77</v>
@@ -29011,7 +29011,7 @@
         <v>85</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="AK235" t="s" s="2">
         <v>97</v>
@@ -29022,10 +29022,10 @@
         <v>898</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -29051,13 +29051,13 @@
         <v>99</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="O236" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="P236" s="2"/>
       <c r="Q236" t="s" s="2">
@@ -29086,10 +29086,10 @@
         <v>374</v>
       </c>
       <c r="Z236" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="AA236" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="AB236" t="s" s="2">
         <v>23</v>
@@ -29107,7 +29107,7 @@
         <v>23</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>77</v>
@@ -29127,10 +29127,10 @@
         <v>898</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -29156,13 +29156,13 @@
         <v>154</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="N237" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="O237" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="P237" s="2"/>
       <c r="Q237" t="s" s="2">
@@ -29212,7 +29212,7 @@
         <v>23</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="AH237" t="s" s="2">
         <v>77</v>
@@ -29232,10 +29232,10 @@
         <v>898</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" t="s" s="2">
@@ -29261,13 +29261,13 @@
         <v>203</v>
       </c>
       <c r="M238" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="N238" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="O238" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="P238" s="2"/>
       <c r="Q238" t="s" s="2">
@@ -29317,7 +29317,7 @@
         <v>23</v>
       </c>
       <c r="AG238" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AH238" t="s" s="2">
         <v>77</v>
@@ -29440,10 +29440,10 @@
         <v>910</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" t="s" s="2">
@@ -29543,10 +29543,10 @@
         <v>910</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" t="s" s="2">
@@ -29646,10 +29646,10 @@
         <v>910</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" t="s" s="2">
@@ -29675,13 +29675,13 @@
         <v>99</v>
       </c>
       <c r="M242" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N242" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O242" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P242" s="2"/>
       <c r="Q242" t="s" s="2">
@@ -29731,7 +29731,7 @@
         <v>23</v>
       </c>
       <c r="AG242" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AH242" t="s" s="2">
         <v>85</v>
@@ -29751,10 +29751,10 @@
         <v>910</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" t="s" s="2">
@@ -29780,10 +29780,10 @@
         <v>428</v>
       </c>
       <c r="M243" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N243" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="O243" s="2"/>
       <c r="P243" s="2"/>
@@ -29834,7 +29834,7 @@
         <v>23</v>
       </c>
       <c r="AG243" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AH243" t="s" s="2">
         <v>77</v>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8338" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8338" uniqueCount="911">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:16:43+00:00</t>
+    <t>2026-09-08T06:28:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -791,7 +791,7 @@
 </t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, der die Allergie im System erfasst bzw. dokumentiert hat.</t>
+    <t>GDA, der die Allergie im System erfasst bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Individual who recorded the record and takes responsibility for its content.</t>
@@ -1127,7 +1127,7 @@
     <t>Condition.identifier</t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem</t>
+    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem.</t>
   </si>
   <si>
     <t>Business identifiers assigned to this condition by the performer or other systems which remain constant as the resource is updated and propagates from server to server.</t>
@@ -1139,7 +1139,7 @@
     <t>Condition.clinicalStatus</t>
   </si>
   <si>
-    <t>Klinischer Status der Diagnose (wie:Status post), mögliche Codes: active | recurrence | relapse | inactive | remission | resolved</t>
+    <t>Klinischer Status der Diagnose (z. B. Status post); mögliche Codes: active | recurrence | relapse | inactive | remission | resolved.</t>
   </si>
   <si>
     <t>The clinical status of the condition.</t>
@@ -1161,7 +1161,7 @@
     <t>Condition.verificationStatus</t>
   </si>
   <si>
-    <t>Verifizierungsstatus der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error</t>
+    <t>Verifizierungsstatus der Diagnose, mögliche Codes: unconfirmed | provisional | differential | confirmed | refuted | entered-in-error.</t>
   </si>
   <si>
     <t>The verification status to support the clinical status of the condition.</t>
@@ -1202,7 +1202,7 @@
     <t>Condition.severity</t>
   </si>
   <si>
-    <t>Schweregrad der Erkrankung</t>
+    <t>Schweregrad der Erkrankung.</t>
   </si>
   <si>
     <t>A subjective assessment of the severity of the condition as evaluated by the clinician.</t>
@@ -1221,7 +1221,7 @@
 </t>
   </si>
   <si>
-    <t>Diagnosecode (Codierservice), Text verboten, Codesystem 1.SNOMED 2.Orphanet</t>
+    <t>Diagnosecode (Codierservice); Freitext ist nicht zulässig. Codesysteme: 1. SNOMED CT, 2. Orphanet.</t>
   </si>
   <si>
     <t>Identification of the condition, problem or diagnosis.</t>
@@ -1412,7 +1412,7 @@
     <t>Condition.bodySite</t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose der Körper-Lokalisation</t>
+    <t>Zuordnung der Diagnose zu einer Körperstelle.</t>
   </si>
   <si>
     <t>The anatomical location where this condition manifests itself.</t>
@@ -1434,7 +1434,7 @@
 </t>
   </si>
   <si>
-    <t>Person, auf die sich die Diagnose bezieht</t>
+    <t>Person, auf die sich die Diagnose bezieht.</t>
   </si>
   <si>
     <t>Indicates the patient or group who the condition record is associated with.</t>
@@ -1446,9 +1446,6 @@
     <t>Condition.encounter</t>
   </si>
   <si>
-    <t>Behandlungskontakt</t>
-  </si>
-  <si>
     <t>The Encounter during which this Condition was created or to which the creation of this record is tightly associated.</t>
   </si>
   <si>
@@ -1458,7 +1455,7 @@
     <t>Condition.onset[x]</t>
   </si>
   <si>
-    <t>Beginn der Erkrankung/Diagnosezeitpunkt</t>
+    <t>Beginn der Erkrankung bzw. Diagnosezeitpunkt.</t>
   </si>
   <si>
     <t>Estimated or actual date or date-time  the condition began, in the opinion of the clinician.</t>
@@ -1470,7 +1467,7 @@
     <t>Condition.abatement[x]</t>
   </si>
   <si>
-    <t>Ende der Erkrankung</t>
+    <t>Ende der Erkrankung.</t>
   </si>
   <si>
     <t>The date or estimated date that the condition resolved or went into remission. This is called "abatement" because of the many overloaded connotations associated with "remission" or "resolution" - Conditions are never really resolved, but they can abate.</t>
@@ -1486,7 +1483,7 @@
     <t>Condition.recordedDate</t>
   </si>
   <si>
-    <t>Zeitpunkt der Diagnosendokumentation</t>
+    <t>Zeitpunkt der Dokumentation der Diagnose.</t>
   </si>
   <si>
     <t>The recordedDate represents when this particular Condition record was created in the system, which is often a system-generated date.</t>
@@ -1495,13 +1492,13 @@
     <t>Condition.recorder</t>
   </si>
   <si>
-    <t>Ansonsten Gesundheitsdiensteanbieter, der die Diagnose eingetragen hat</t>
+    <t>GDA, der die Diagnose eingetragen hat.</t>
   </si>
   <si>
     <t>Condition.asserter</t>
   </si>
   <si>
-    <t>Quelle der Information zur Diagnose (z. B. behandelnde Person, Patient oder Dritter)</t>
+    <t>Quelle der Information zur Diagnose (z. B. behandelnde GDA, Patient oder Dritter).</t>
   </si>
   <si>
     <t>Individual who is making the condition statement.</t>
@@ -1510,7 +1507,7 @@
     <t>Condition.stage</t>
   </si>
   <si>
-    <t>Stadium der Erkrankung</t>
+    <t>Stadium der Erkrankung.</t>
   </si>
   <si>
     <t>Clinical stage or grade of a condition. May include formal severity assessments.</t>
@@ -1579,7 +1576,7 @@
     <t>Condition.evidence</t>
   </si>
   <si>
-    <t>Verweis auf ELGA-Befunde als medizinische Evidenz</t>
+    <t>Verweis auf ELGA-Befunde als medizinische Evidenz.</t>
   </si>
   <si>
     <t>Supporting evidence / manifestations that are the basis of the Condition's verification status, such as evidence that confirmed or refuted the condition.</t>
@@ -1636,7 +1633,7 @@
     <t>Condition.note</t>
   </si>
   <si>
-    <t>Freitext zur Diagnose für Zusatzinformation</t>
+    <t>Freitext zur Diagnose als Zusatzinformation.</t>
   </si>
   <si>
     <t>Additional information about the Condition. This is a general notes/comments entry  for description of the Condition, its diagnosis and prognosis.</t>
@@ -2282,9 +2279,6 @@
     <t>Procedure.identifier</t>
   </si>
   <si>
-    <t>Zuordnung der Diagnose in einem internen Dokumentationssystem.</t>
-  </si>
-  <si>
     <t>Business identifiers assigned to this procedure by the performer or other systems which remain constant as the resource is updated and is propagated from server to server.</t>
   </si>
   <si>
@@ -2466,7 +2460,7 @@
     <t>Procedure.recorder</t>
   </si>
   <si>
-    <t>Gesundheitsdiensteanbieter, der die Prozedur eingetragen bzw. dokumentiert hat.</t>
+    <t>GDA, der die Prozedur eingetragen bzw. dokumentiert hat.</t>
   </si>
   <si>
     <t>Procedure.asserter</t>
@@ -2632,9 +2626,6 @@
   <si>
     <t xml:space="preserve">Reference(DiagnosticReport|4.0.1|DocumentReference|4.0.1|Composition|4.0.1)
 </t>
-  </si>
-  <si>
-    <t>Verweis auf ELGA-Befunde als medizinische Evidenz.</t>
   </si>
   <si>
     <t>This could be a histology result, pathology report, surgical report, etc.</t>
@@ -3348,7 +3339,7 @@
         <v>2</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="47">
@@ -3356,7 +3347,7 @@
         <v>4</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="48">
@@ -3372,7 +3363,7 @@
         <v>8</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="50">
@@ -3388,7 +3379,7 @@
         <v>12</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="52">
@@ -3470,7 +3461,7 @@
         <v>30</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="63">
@@ -3486,7 +3477,7 @@
         <v>34</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="65">
@@ -3507,26 +3498,26 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B67" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="B67" t="s" s="2">
-        <v>532</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
     </row>
     <row r="70">
@@ -3542,7 +3533,7 @@
         <v>2</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="72">
@@ -3550,7 +3541,7 @@
         <v>4</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="73">
@@ -3566,7 +3557,7 @@
         <v>8</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="75">
@@ -3574,7 +3565,7 @@
         <v>10</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="76">
@@ -3636,7 +3627,7 @@
         <v>24</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="84">
@@ -3672,7 +3663,7 @@
         <v>32</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="89">
@@ -3680,7 +3671,7 @@
         <v>34</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="90">
@@ -3712,7 +3703,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="94">
@@ -3720,7 +3711,7 @@
         <v>4</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
     </row>
     <row r="95">
@@ -3736,7 +3727,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="97">
@@ -3744,7 +3735,7 @@
         <v>10</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="98">
@@ -3806,7 +3797,7 @@
         <v>24</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>711</v>
+        <v>710</v>
       </c>
     </row>
     <row r="106">
@@ -3842,7 +3833,7 @@
         <v>32</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="111">
@@ -3850,7 +3841,7 @@
         <v>34</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>713</v>
+        <v>712</v>
       </c>
     </row>
     <row r="112">
@@ -3882,7 +3873,7 @@
         <v>2</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>893</v>
+        <v>890</v>
       </c>
     </row>
     <row r="116">
@@ -3890,7 +3881,7 @@
         <v>4</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>894</v>
+        <v>891</v>
       </c>
     </row>
     <row r="117">
@@ -3906,7 +3897,7 @@
         <v>8</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>895</v>
+        <v>892</v>
       </c>
     </row>
     <row r="119">
@@ -3914,7 +3905,7 @@
         <v>10</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>896</v>
+        <v>893</v>
       </c>
     </row>
     <row r="120">
@@ -4004,7 +3995,7 @@
         <v>30</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="132">
@@ -4020,7 +4011,7 @@
         <v>34</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="134">
@@ -4041,10 +4032,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>897</v>
+        <v>894</v>
       </c>
     </row>
     <row r="137">
@@ -4060,7 +4051,7 @@
         <v>2</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
     </row>
     <row r="139">
@@ -4068,7 +4059,7 @@
         <v>4</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>899</v>
+        <v>896</v>
       </c>
     </row>
     <row r="140">
@@ -4084,7 +4075,7 @@
         <v>8</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>900</v>
+        <v>897</v>
       </c>
     </row>
     <row r="142">
@@ -4092,7 +4083,7 @@
         <v>10</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>901</v>
+        <v>898</v>
       </c>
     </row>
     <row r="143">
@@ -4182,7 +4173,7 @@
         <v>30</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="155">
@@ -4190,7 +4181,7 @@
         <v>32</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>902</v>
+        <v>899</v>
       </c>
     </row>
     <row r="156">
@@ -4198,7 +4189,7 @@
         <v>34</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>903</v>
+        <v>900</v>
       </c>
     </row>
     <row r="157">
@@ -4230,7 +4221,7 @@
         <v>2</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>910</v>
+        <v>907</v>
       </c>
     </row>
     <row r="161">
@@ -4238,7 +4229,7 @@
         <v>4</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>911</v>
+        <v>908</v>
       </c>
     </row>
     <row r="162">
@@ -4254,7 +4245,7 @@
         <v>8</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>912</v>
+        <v>909</v>
       </c>
     </row>
     <row r="164">
@@ -4270,7 +4261,7 @@
         <v>12</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="166">
@@ -4352,7 +4343,7 @@
         <v>30</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="177">
@@ -4368,7 +4359,7 @@
         <v>34</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="179">
@@ -4389,10 +4380,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>913</v>
+        <v>910</v>
       </c>
     </row>
   </sheetData>
@@ -13603,13 +13594,13 @@
         <v>231</v>
       </c>
       <c r="M88" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="N88" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N88" t="s" s="2">
+      <c r="O88" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P88" s="2"/>
       <c r="Q88" t="s" s="2">
@@ -13679,10 +13670,10 @@
         <v>332</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D89" s="2"/>
       <c r="E89" t="s" s="2">
@@ -13708,13 +13699,13 @@
         <v>239</v>
       </c>
       <c r="M89" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N89" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="N89" t="s" s="2">
+      <c r="O89" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="P89" s="2"/>
       <c r="Q89" t="s" s="2">
@@ -13764,7 +13755,7 @@
         <v>23</v>
       </c>
       <c r="AG89" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AH89" t="s" s="2">
         <v>77</v>
@@ -13784,10 +13775,10 @@
         <v>332</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D90" s="2"/>
       <c r="E90" t="s" s="2">
@@ -13813,13 +13804,13 @@
         <v>239</v>
       </c>
       <c r="M90" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="P90" s="2"/>
       <c r="Q90" t="s" s="2">
@@ -13869,7 +13860,7 @@
         <v>23</v>
       </c>
       <c r="AG90" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="AH90" t="s" s="2">
         <v>77</v>
@@ -13878,7 +13869,7 @@
         <v>85</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>97</v>
@@ -13889,10 +13880,10 @@
         <v>332</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="D91" s="2"/>
       <c r="E91" t="s" s="2">
@@ -13918,10 +13909,10 @@
         <v>239</v>
       </c>
       <c r="M91" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" s="2"/>
@@ -13972,7 +13963,7 @@
         <v>23</v>
       </c>
       <c r="AG91" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="AH91" t="s" s="2">
         <v>77</v>
@@ -13992,10 +13983,10 @@
         <v>332</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="D92" s="2"/>
       <c r="E92" t="s" s="2">
@@ -14021,7 +14012,7 @@
         <v>244</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>246</v>
@@ -14075,7 +14066,7 @@
         <v>23</v>
       </c>
       <c r="AG92" t="s" s="2">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="AH92" t="s" s="2">
         <v>77</v>
@@ -14095,10 +14086,10 @@
         <v>332</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D93" s="2"/>
       <c r="E93" t="s" s="2">
@@ -14124,10 +14115,10 @@
         <v>249</v>
       </c>
       <c r="M93" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" s="2"/>
@@ -14178,7 +14169,7 @@
         <v>23</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>77</v>
@@ -14198,10 +14189,10 @@
         <v>332</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D94" s="2"/>
       <c r="E94" t="s" s="2">
@@ -14227,10 +14218,10 @@
         <v>263</v>
       </c>
       <c r="M94" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="N94" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
@@ -14281,7 +14272,7 @@
         <v>23</v>
       </c>
       <c r="AG94" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AH94" t="s" s="2">
         <v>77</v>
@@ -14293,7 +14284,7 @@
         <v>23</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="95">
@@ -14301,10 +14292,10 @@
         <v>332</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="D95" s="2"/>
       <c r="E95" t="s" s="2">
@@ -14404,10 +14395,10 @@
         <v>332</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D96" s="2"/>
       <c r="E96" t="s" s="2">
@@ -14509,10 +14500,10 @@
         <v>332</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -14616,10 +14607,10 @@
         <v>332</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -14645,10 +14636,10 @@
         <v>160</v>
       </c>
       <c r="M98" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="N98" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" s="2"/>
@@ -14678,37 +14669,37 @@
         <v>199</v>
       </c>
       <c r="Z98" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="AA98" t="s" s="2">
         <v>487</v>
       </c>
-      <c r="AA98" t="s" s="2">
+      <c r="AB98" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
         <v>488</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>489</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>97</v>
@@ -14719,10 +14710,10 @@
         <v>332</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -14745,13 +14736,13 @@
         <v>23</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" s="2"/>
@@ -14802,7 +14793,7 @@
         <v>23</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>77</v>
@@ -14811,7 +14802,7 @@
         <v>78</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>97</v>
@@ -14822,10 +14813,10 @@
         <v>332</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -14851,10 +14842,10 @@
         <v>160</v>
       </c>
       <c r="M100" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="N100" t="s" s="2">
         <v>495</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>496</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -14884,11 +14875,11 @@
         <v>199</v>
       </c>
       <c r="Z100" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="AA100" t="s" s="2">
         <v>497</v>
       </c>
-      <c r="AA100" t="s" s="2">
-        <v>498</v>
-      </c>
       <c r="AB100" t="s" s="2">
         <v>23</v>
       </c>
@@ -14905,7 +14896,7 @@
         <v>23</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>77</v>
@@ -14925,10 +14916,10 @@
         <v>332</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -14954,13 +14945,13 @@
         <v>263</v>
       </c>
       <c r="M101" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N101" t="s" s="2">
         <v>500</v>
       </c>
-      <c r="N101" t="s" s="2">
+      <c r="O101" t="s" s="2">
         <v>501</v>
-      </c>
-      <c r="O101" t="s" s="2">
-        <v>502</v>
       </c>
       <c r="P101" s="2"/>
       <c r="Q101" t="s" s="2">
@@ -15010,7 +15001,7 @@
         <v>23</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="AH101" t="s" s="2">
         <v>77</v>
@@ -15022,7 +15013,7 @@
         <v>23</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="102">
@@ -15030,10 +15021,10 @@
         <v>332</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -15133,10 +15124,10 @@
         <v>332</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -15238,10 +15229,10 @@
         <v>332</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -15345,10 +15336,10 @@
         <v>332</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -15374,10 +15365,10 @@
         <v>160</v>
       </c>
       <c r="M105" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="N105" t="s" s="2">
         <v>508</v>
-      </c>
-      <c r="N105" t="s" s="2">
-        <v>509</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
@@ -15407,11 +15398,11 @@
         <v>199</v>
       </c>
       <c r="Z105" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AA105" t="s" s="2">
         <v>510</v>
       </c>
-      <c r="AA105" t="s" s="2">
-        <v>511</v>
-      </c>
       <c r="AB105" t="s" s="2">
         <v>23</v>
       </c>
@@ -15428,7 +15419,7 @@
         <v>23</v>
       </c>
       <c r="AG105" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AH105" t="s" s="2">
         <v>77</v>
@@ -15437,7 +15428,7 @@
         <v>78</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AK105" t="s" s="2">
         <v>97</v>
@@ -15448,10 +15439,10 @@
         <v>332</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -15474,13 +15465,13 @@
         <v>86</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>514</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" s="2"/>
@@ -15531,7 +15522,7 @@
         <v>23</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>77</v>
@@ -15540,7 +15531,7 @@
         <v>78</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>97</v>
@@ -15551,10 +15542,10 @@
         <v>332</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -15580,10 +15571,10 @@
         <v>258</v>
       </c>
       <c r="M107" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" s="2"/>
@@ -15634,7 +15625,7 @@
         <v>23</v>
       </c>
       <c r="AG107" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="AH107" t="s" s="2">
         <v>77</v>
@@ -15654,10 +15645,10 @@
         <v>332</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -15757,10 +15748,10 @@
         <v>332</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -15862,10 +15853,10 @@
         <v>332</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D110" s="2"/>
       <c r="E110" t="s" s="2">
@@ -15967,10 +15958,10 @@
         <v>332</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -16070,10 +16061,10 @@
         <v>332</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -16170,7 +16161,7 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B113" t="s" s="2">
         <v>129</v>
@@ -16273,13 +16264,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -16376,13 +16367,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -16479,16 +16470,16 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B116" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="C116" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="D116" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="D116" t="s" s="2">
-        <v>538</v>
       </c>
       <c r="E116" t="s" s="2">
         <v>23</v>
@@ -16584,13 +16575,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B117" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C117" t="s" s="2">
         <v>539</v>
-      </c>
-      <c r="C117" t="s" s="2">
-        <v>540</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -16687,13 +16678,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B118" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="C118" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -16790,13 +16781,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B119" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="C119" t="s" s="2">
         <v>543</v>
-      </c>
-      <c r="C119" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -16822,13 +16813,13 @@
         <v>99</v>
       </c>
       <c r="M119" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N119" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N119" t="s" s="2">
+      <c r="O119" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P119" s="2"/>
       <c r="Q119" t="s" s="2">
@@ -16836,7 +16827,7 @@
       </c>
       <c r="R119" s="2"/>
       <c r="S119" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="T119" t="s" s="2">
         <v>23</v>
@@ -16878,7 +16869,7 @@
         <v>23</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>85</v>
@@ -16895,13 +16886,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B120" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="C120" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="C120" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -16924,13 +16915,13 @@
         <v>23</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>551</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
@@ -16981,7 +16972,7 @@
         <v>23</v>
       </c>
       <c r="AG120" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AH120" t="s" s="2">
         <v>77</v>
@@ -16998,16 +16989,16 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B121" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C121" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="D121" t="s" s="2">
         <v>555</v>
-      </c>
-      <c r="C121" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="D121" t="s" s="2">
-        <v>556</v>
       </c>
       <c r="E121" t="s" s="2">
         <v>23</v>
@@ -17103,13 +17094,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -17206,13 +17197,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -17309,13 +17300,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -17341,13 +17332,13 @@
         <v>99</v>
       </c>
       <c r="M124" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N124" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N124" t="s" s="2">
+      <c r="O124" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O124" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P124" s="2"/>
       <c r="Q124" t="s" s="2">
@@ -17355,7 +17346,7 @@
       </c>
       <c r="R124" s="2"/>
       <c r="S124" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="T124" t="s" s="2">
         <v>23</v>
@@ -17397,7 +17388,7 @@
         <v>23</v>
       </c>
       <c r="AG124" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AH124" t="s" s="2">
         <v>85</v>
@@ -17414,13 +17405,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -17446,10 +17437,10 @@
         <v>239</v>
       </c>
       <c r="M125" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N125" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O125" s="2"/>
       <c r="P125" s="2"/>
@@ -17500,7 +17491,7 @@
         <v>23</v>
       </c>
       <c r="AG125" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AH125" t="s" s="2">
         <v>77</v>
@@ -17517,16 +17508,16 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B126" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="D126" t="s" s="2">
         <v>561</v>
-      </c>
-      <c r="C126" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="D126" t="s" s="2">
-        <v>562</v>
       </c>
       <c r="E126" t="s" s="2">
         <v>23</v>
@@ -17622,13 +17613,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -17725,13 +17716,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -17828,13 +17819,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -17860,13 +17851,13 @@
         <v>99</v>
       </c>
       <c r="M129" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N129" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N129" t="s" s="2">
+      <c r="O129" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P129" s="2"/>
       <c r="Q129" t="s" s="2">
@@ -17874,7 +17865,7 @@
       </c>
       <c r="R129" s="2"/>
       <c r="S129" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>23</v>
@@ -17916,7 +17907,7 @@
         <v>23</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>85</v>
@@ -17933,13 +17924,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -17965,10 +17956,10 @@
         <v>203</v>
       </c>
       <c r="M130" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N130" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N130" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" s="2"/>
@@ -18019,7 +18010,7 @@
         <v>23</v>
       </c>
       <c r="AG130" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AH130" t="s" s="2">
         <v>77</v>
@@ -18036,13 +18027,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -18068,13 +18059,13 @@
         <v>99</v>
       </c>
       <c r="M131" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N131" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N131" t="s" s="2">
+      <c r="O131" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O131" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P131" s="2"/>
       <c r="Q131" t="s" s="2">
@@ -18082,7 +18073,7 @@
       </c>
       <c r="R131" s="2"/>
       <c r="S131" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>23</v>
@@ -18124,7 +18115,7 @@
         <v>23</v>
       </c>
       <c r="AG131" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AH131" t="s" s="2">
         <v>85</v>
@@ -18141,13 +18132,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -18170,13 +18161,13 @@
         <v>23</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="M132" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N132" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N132" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" s="2"/>
@@ -18227,7 +18218,7 @@
         <v>23</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>77</v>
@@ -18244,17 +18235,17 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="F133" s="2"/>
       <c r="G133" t="s" s="2">
@@ -18276,10 +18267,10 @@
         <v>79</v>
       </c>
       <c r="M133" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="N133" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="O133" s="2"/>
       <c r="P133" s="2"/>
@@ -18330,7 +18321,7 @@
         <v>23</v>
       </c>
       <c r="AG133" t="s" s="2">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="AH133" t="s" s="2">
         <v>77</v>
@@ -18342,18 +18333,18 @@
         <v>23</v>
       </c>
       <c r="AK133" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -18452,13 +18443,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -18555,13 +18546,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -18660,13 +18651,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -18765,13 +18756,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -18870,13 +18861,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -18975,13 +18966,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -19010,7 +19001,7 @@
         <v>208</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="O140" t="s" s="2">
         <v>150</v>
@@ -19080,13 +19071,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -19187,13 +19178,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -19219,10 +19210,10 @@
         <v>154</v>
       </c>
       <c r="M142" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="N142" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="N142" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" s="2"/>
@@ -19273,7 +19264,7 @@
         <v>23</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>77</v>
@@ -19290,13 +19281,13 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C143" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="D143" s="2"/>
       <c r="E143" t="s" s="2">
@@ -19322,13 +19313,13 @@
         <v>105</v>
       </c>
       <c r="M143" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N143" t="s" s="2">
         <v>592</v>
       </c>
-      <c r="N143" t="s" s="2">
+      <c r="O143" t="s" s="2">
         <v>593</v>
-      </c>
-      <c r="O143" t="s" s="2">
-        <v>594</v>
       </c>
       <c r="P143" s="2"/>
       <c r="Q143" t="s" s="2">
@@ -19336,7 +19327,7 @@
       </c>
       <c r="R143" s="2"/>
       <c r="S143" t="s" s="2">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="T143" t="s" s="2">
         <v>23</v>
@@ -19357,11 +19348,11 @@
         <v>164</v>
       </c>
       <c r="Z143" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AA143" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AA143" t="s" s="2">
-        <v>597</v>
-      </c>
       <c r="AB143" t="s" s="2">
         <v>23</v>
       </c>
@@ -19378,7 +19369,7 @@
         <v>23</v>
       </c>
       <c r="AG143" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AH143" t="s" s="2">
         <v>85</v>
@@ -19395,13 +19386,13 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C144" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="D144" s="2"/>
       <c r="E144" t="s" s="2">
@@ -19427,23 +19418,23 @@
         <v>105</v>
       </c>
       <c r="M144" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N144" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="N144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>600</v>
       </c>
-      <c r="O144" t="s" s="2">
+      <c r="P144" t="s" s="2">
         <v>601</v>
-      </c>
-      <c r="P144" t="s" s="2">
-        <v>602</v>
       </c>
       <c r="Q144" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R144" s="2"/>
       <c r="S144" t="s" s="2">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>23</v>
@@ -19464,11 +19455,11 @@
         <v>164</v>
       </c>
       <c r="Z144" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="AA144" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="AA144" t="s" s="2">
-        <v>605</v>
-      </c>
       <c r="AB144" t="s" s="2">
         <v>23</v>
       </c>
@@ -19485,7 +19476,7 @@
         <v>23</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>85</v>
@@ -19502,13 +19493,13 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -19534,14 +19525,14 @@
         <v>203</v>
       </c>
       <c r="M145" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="N145" t="s" s="2">
         <v>607</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>608</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="Q145" t="s" s="2">
         <v>23</v>
@@ -19554,7 +19545,7 @@
         <v>23</v>
       </c>
       <c r="U145" t="s" s="2">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="V145" t="s" s="2">
         <v>23</v>
@@ -19590,7 +19581,7 @@
         <v>23</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>77</v>
@@ -19607,13 +19598,13 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -19639,16 +19630,16 @@
         <v>160</v>
       </c>
       <c r="M146" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N146" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="N146" t="s" s="2">
+      <c r="O146" t="s" s="2">
         <v>613</v>
       </c>
-      <c r="O146" t="s" s="2">
+      <c r="P146" t="s" s="2">
         <v>614</v>
-      </c>
-      <c r="P146" t="s" s="2">
-        <v>615</v>
       </c>
       <c r="Q146" t="s" s="2">
         <v>23</v>
@@ -19677,7 +19668,7 @@
       </c>
       <c r="Z146" s="2"/>
       <c r="AA146" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="AB146" t="s" s="2">
         <v>23</v>
@@ -19695,7 +19686,7 @@
         <v>23</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>77</v>
@@ -19712,13 +19703,13 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -19744,16 +19735,16 @@
         <v>227</v>
       </c>
       <c r="M147" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N147" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="N147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="O147" t="s" s="2">
+      <c r="P147" t="s" s="2">
         <v>620</v>
-      </c>
-      <c r="P147" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="Q147" t="s" s="2">
         <v>23</v>
@@ -19802,7 +19793,7 @@
         <v>23</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>77</v>
@@ -19819,13 +19810,13 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -19851,10 +19842,10 @@
         <v>231</v>
       </c>
       <c r="M148" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" s="2"/>
@@ -19905,7 +19896,7 @@
         <v>23</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>77</v>
@@ -19922,13 +19913,13 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -19954,16 +19945,16 @@
         <v>239</v>
       </c>
       <c r="M149" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="O149" t="s" s="2">
+      <c r="P149" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="P149" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="Q149" t="s" s="2">
         <v>23</v>
@@ -20012,7 +20003,7 @@
         <v>23</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>77</v>
@@ -20029,13 +20020,13 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -20058,19 +20049,19 @@
         <v>86</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="N150" t="s" s="2">
+      <c r="O150" t="s" s="2">
         <v>633</v>
       </c>
-      <c r="O150" t="s" s="2">
+      <c r="P150" t="s" s="2">
         <v>634</v>
-      </c>
-      <c r="P150" t="s" s="2">
-        <v>635</v>
       </c>
       <c r="Q150" t="s" s="2">
         <v>23</v>
@@ -20119,7 +20110,7 @@
         <v>23</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>77</v>
@@ -20136,13 +20127,13 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -20168,16 +20159,16 @@
         <v>160</v>
       </c>
       <c r="M151" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="N151" t="s" s="2">
+      <c r="O151" t="s" s="2">
         <v>638</v>
       </c>
-      <c r="O151" t="s" s="2">
+      <c r="P151" t="s" s="2">
         <v>639</v>
-      </c>
-      <c r="P151" t="s" s="2">
-        <v>640</v>
       </c>
       <c r="Q151" t="s" s="2">
         <v>23</v>
@@ -20205,11 +20196,11 @@
         <v>109</v>
       </c>
       <c r="Z151" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="AA151" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="AA151" t="s" s="2">
-        <v>642</v>
-      </c>
       <c r="AB151" t="s" s="2">
         <v>23</v>
       </c>
@@ -20226,7 +20217,7 @@
         <v>23</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>77</v>
@@ -20243,13 +20234,13 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -20275,10 +20266,10 @@
         <v>258</v>
       </c>
       <c r="M152" t="s" s="2">
+        <v>643</v>
+      </c>
+      <c r="N152" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="N152" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="O152" s="2"/>
       <c r="P152" s="2"/>
@@ -20329,7 +20320,7 @@
         <v>23</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>77</v>
@@ -20346,13 +20337,13 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -20378,13 +20369,13 @@
         <v>263</v>
       </c>
       <c r="M153" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="N153" t="s" s="2">
         <v>647</v>
       </c>
-      <c r="N153" t="s" s="2">
+      <c r="O153" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="O153" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="P153" s="2"/>
       <c r="Q153" t="s" s="2">
@@ -20434,7 +20425,7 @@
         <v>23</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>77</v>
@@ -20443,7 +20434,7 @@
         <v>78</v>
       </c>
       <c r="AJ153" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AK153" t="s" s="2">
         <v>97</v>
@@ -20451,13 +20442,13 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -20554,13 +20545,13 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -20659,13 +20650,13 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -20766,13 +20757,13 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -20798,16 +20789,16 @@
         <v>160</v>
       </c>
       <c r="M157" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="N157" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>656</v>
       </c>
-      <c r="O157" t="s" s="2">
+      <c r="P157" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="P157" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="Q157" t="s" s="2">
         <v>23</v>
@@ -20835,11 +20826,11 @@
         <v>199</v>
       </c>
       <c r="Z157" t="s" s="2">
+        <v>658</v>
+      </c>
+      <c r="AA157" t="s" s="2">
         <v>659</v>
       </c>
-      <c r="AA157" t="s" s="2">
-        <v>660</v>
-      </c>
       <c r="AB157" t="s" s="2">
         <v>23</v>
       </c>
@@ -20856,7 +20847,7 @@
         <v>23</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>77</v>
@@ -20873,13 +20864,13 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -20905,76 +20896,76 @@
         <v>428</v>
       </c>
       <c r="M158" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="N158" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="N158" t="s" s="2">
+      <c r="O158" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="O158" t="s" s="2">
+      <c r="P158" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="P158" t="s" s="2">
+      <c r="Q158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R158" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="Q158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R158" t="s" s="2">
+      <c r="S158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF158" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG158" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="AH158" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI158" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ158" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="S158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF158" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG158" t="s" s="2">
-        <v>661</v>
-      </c>
-      <c r="AH158" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI158" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ158" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="AK158" t="s" s="2">
         <v>97</v>
@@ -20982,13 +20973,13 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -21014,14 +21005,14 @@
         <v>239</v>
       </c>
       <c r="M159" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="N159" t="s" s="2">
         <v>669</v>
-      </c>
-      <c r="N159" t="s" s="2">
-        <v>670</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="Q159" t="s" s="2">
         <v>23</v>
@@ -21070,7 +21061,7 @@
         <v>23</v>
       </c>
       <c r="AG159" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AH159" t="s" s="2">
         <v>77</v>
@@ -21087,13 +21078,13 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -21116,13 +21107,13 @@
         <v>23</v>
       </c>
       <c r="L160" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="M160" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="M160" t="s" s="2">
+      <c r="N160" t="s" s="2">
         <v>674</v>
-      </c>
-      <c r="N160" t="s" s="2">
-        <v>675</v>
       </c>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
@@ -21173,7 +21164,7 @@
         <v>23</v>
       </c>
       <c r="AG160" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AH160" t="s" s="2">
         <v>85</v>
@@ -21190,13 +21181,13 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -21293,13 +21284,13 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -21398,13 +21389,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -21430,13 +21421,13 @@
         <v>203</v>
       </c>
       <c r="M163" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="N163" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="N163" t="s" s="2">
+      <c r="O163" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="O163" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="P163" s="2"/>
       <c r="Q163" t="s" s="2">
@@ -21486,16 +21477,16 @@
         <v>23</v>
       </c>
       <c r="AG163" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AH163" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI163" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ163" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="AH163" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI163" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ163" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>97</v>
@@ -21503,13 +21494,13 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -21535,13 +21526,13 @@
         <v>99</v>
       </c>
       <c r="M164" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="N164" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="N164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="O164" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="P164" s="2"/>
       <c r="Q164" t="s" s="2">
@@ -21570,28 +21561,28 @@
         <v>374</v>
       </c>
       <c r="Z164" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AA164" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="AA164" t="s" s="2">
+      <c r="AB164" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC164" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD164" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE164" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF164" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG164" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="AB164" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC164" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD164" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE164" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF164" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG164" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>77</v>
@@ -21608,13 +21599,13 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -21640,13 +21631,13 @@
         <v>154</v>
       </c>
       <c r="M165" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N165" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="N165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
@@ -21696,7 +21687,7 @@
         <v>23</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>77</v>
@@ -21713,13 +21704,13 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -21745,13 +21736,13 @@
         <v>203</v>
       </c>
       <c r="M166" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="N166" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="N166" t="s" s="2">
+      <c r="O166" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="O166" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="P166" s="2"/>
       <c r="Q166" t="s" s="2">
@@ -21801,7 +21792,7 @@
         <v>23</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>77</v>
@@ -21818,13 +21809,13 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -21850,16 +21841,16 @@
         <v>160</v>
       </c>
       <c r="M167" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>703</v>
       </c>
-      <c r="O167" t="s" s="2">
+      <c r="P167" t="s" s="2">
         <v>704</v>
-      </c>
-      <c r="P167" t="s" s="2">
-        <v>705</v>
       </c>
       <c r="Q167" t="s" s="2">
         <v>23</v>
@@ -21888,7 +21879,7 @@
       </c>
       <c r="Z167" s="2"/>
       <c r="AA167" t="s" s="2">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="AB167" t="s" s="2">
         <v>23</v>
@@ -21906,7 +21897,7 @@
         <v>23</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>77</v>
@@ -21915,7 +21906,7 @@
         <v>85</v>
       </c>
       <c r="AJ167" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="AK167" t="s" s="2">
         <v>97</v>
@@ -21923,13 +21914,13 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -21955,10 +21946,10 @@
         <v>79</v>
       </c>
       <c r="M168" t="s" s="2">
+        <v>713</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>714</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>715</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
@@ -22009,7 +22000,7 @@
         <v>23</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>77</v>
@@ -22021,18 +22012,18 @@
         <v>23</v>
       </c>
       <c r="AK168" t="s" s="2">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -22131,13 +22122,13 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -22234,13 +22225,13 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -22339,13 +22330,13 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -22444,13 +22435,13 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -22549,13 +22540,13 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -22654,13 +22645,13 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -22755,13 +22746,13 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D176" t="s" s="2">
         <v>136</v>
@@ -22860,13 +22851,13 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D177" t="s" s="2">
         <v>142</v>
@@ -22965,13 +22956,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D178" s="2"/>
       <c r="E178" t="s" s="2">
@@ -23072,13 +23063,13 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D179" s="2"/>
       <c r="E179" t="s" s="2">
@@ -23104,16 +23095,16 @@
         <v>154</v>
       </c>
       <c r="M179" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N179" t="s" s="2">
+        <v>727</v>
+      </c>
+      <c r="O179" t="s" s="2">
         <v>728</v>
       </c>
-      <c r="N179" t="s" s="2">
+      <c r="P179" t="s" s="2">
         <v>729</v>
-      </c>
-      <c r="O179" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="P179" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="Q179" t="s" s="2">
         <v>23</v>
@@ -23162,7 +23153,7 @@
         <v>23</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="AH179" t="s" s="2">
         <v>77</v>
@@ -23179,13 +23170,13 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D180" s="2"/>
       <c r="E180" t="s" s="2">
@@ -23208,13 +23199,13 @@
         <v>86</v>
       </c>
       <c r="L180" t="s" s="2">
+        <v>731</v>
+      </c>
+      <c r="M180" t="s" s="2">
+        <v>732</v>
+      </c>
+      <c r="N180" t="s" s="2">
         <v>733</v>
-      </c>
-      <c r="M180" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="N180" t="s" s="2">
-        <v>735</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" s="2"/>
@@ -23265,7 +23256,7 @@
         <v>23</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>77</v>
@@ -23282,13 +23273,13 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" t="s" s="2">
@@ -23314,13 +23305,13 @@
         <v>99</v>
       </c>
       <c r="M181" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="N181" t="s" s="2">
+        <v>736</v>
+      </c>
+      <c r="O181" t="s" s="2">
         <v>737</v>
-      </c>
-      <c r="N181" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="O181" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="P181" s="2"/>
       <c r="Q181" t="s" s="2">
@@ -23370,7 +23361,7 @@
         <v>23</v>
       </c>
       <c r="AG181" t="s" s="2">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="AH181" t="s" s="2">
         <v>77</v>
@@ -23387,17 +23378,17 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" t="s" s="2">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="F182" s="2"/>
       <c r="G182" t="s" s="2">
@@ -23416,13 +23407,13 @@
         <v>86</v>
       </c>
       <c r="L182" t="s" s="2">
+        <v>740</v>
+      </c>
+      <c r="M182" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="N182" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="M182" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="N182" t="s" s="2">
-        <v>744</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" s="2"/>
@@ -23473,7 +23464,7 @@
         <v>23</v>
       </c>
       <c r="AG182" t="s" s="2">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="AH182" t="s" s="2">
         <v>77</v>
@@ -23490,17 +23481,17 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" t="s" s="2">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F183" s="2"/>
       <c r="G183" t="s" s="2">
@@ -23519,16 +23510,16 @@
         <v>86</v>
       </c>
       <c r="L183" t="s" s="2">
+        <v>745</v>
+      </c>
+      <c r="M183" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="N183" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="M183" t="s" s="2">
+      <c r="O183" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="N183" t="s" s="2">
-        <v>749</v>
-      </c>
-      <c r="O183" t="s" s="2">
-        <v>750</v>
       </c>
       <c r="P183" s="2"/>
       <c r="Q183" t="s" s="2">
@@ -23578,7 +23569,7 @@
         <v>23</v>
       </c>
       <c r="AG183" t="s" s="2">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="AH183" t="s" s="2">
         <v>77</v>
@@ -23595,13 +23586,13 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" t="s" s="2">
@@ -23627,13 +23618,13 @@
         <v>105</v>
       </c>
       <c r="M184" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="N184" t="s" s="2">
+        <v>751</v>
+      </c>
+      <c r="O184" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="N184" t="s" s="2">
-        <v>753</v>
-      </c>
-      <c r="O184" t="s" s="2">
-        <v>754</v>
       </c>
       <c r="P184" s="2"/>
       <c r="Q184" t="s" s="2">
@@ -23663,7 +23654,7 @@
       </c>
       <c r="Z184" s="2"/>
       <c r="AA184" t="s" s="2">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="AB184" t="s" s="2">
         <v>23</v>
@@ -23681,7 +23672,7 @@
         <v>23</v>
       </c>
       <c r="AG184" t="s" s="2">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="AH184" t="s" s="2">
         <v>85</v>
@@ -23698,17 +23689,17 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" t="s" s="2">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" t="s" s="2">
@@ -23730,13 +23721,13 @@
         <v>160</v>
       </c>
       <c r="M185" t="s" s="2">
+        <v>756</v>
+      </c>
+      <c r="N185" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="O185" t="s" s="2">
         <v>758</v>
-      </c>
-      <c r="N185" t="s" s="2">
-        <v>759</v>
-      </c>
-      <c r="O185" t="s" s="2">
-        <v>760</v>
       </c>
       <c r="P185" s="2"/>
       <c r="Q185" t="s" s="2">
@@ -23765,10 +23756,10 @@
         <v>199</v>
       </c>
       <c r="Z185" t="s" s="2">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="AA185" t="s" s="2">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="AB185" t="s" s="2">
         <v>23</v>
@@ -23786,7 +23777,7 @@
         <v>23</v>
       </c>
       <c r="AG185" t="s" s="2">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="AH185" t="s" s="2">
         <v>77</v>
@@ -23803,13 +23794,13 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" t="s" s="2">
@@ -23835,10 +23826,10 @@
         <v>160</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="N186" t="s" s="2">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="O186" s="2"/>
       <c r="P186" s="2"/>
@@ -23868,10 +23859,10 @@
         <v>199</v>
       </c>
       <c r="Z186" t="s" s="2">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="AA186" t="s" s="2">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="AB186" t="s" s="2">
         <v>23</v>
@@ -23889,7 +23880,7 @@
         <v>23</v>
       </c>
       <c r="AG186" t="s" s="2">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="AH186" t="s" s="2">
         <v>77</v>
@@ -23906,13 +23897,13 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" t="s" s="2">
@@ -23938,10 +23929,10 @@
         <v>160</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="N187" t="s" s="2">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="O187" s="2"/>
       <c r="P187" t="s" s="2">
@@ -23974,7 +23965,7 @@
       </c>
       <c r="Z187" s="2"/>
       <c r="AA187" t="s" s="2">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="AB187" t="s" s="2">
         <v>23</v>
@@ -23992,7 +23983,7 @@
         <v>23</v>
       </c>
       <c r="AG187" t="s" s="2">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="AH187" t="s" s="2">
         <v>77</v>
@@ -24009,13 +24000,13 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" t="s" s="2">
@@ -24112,13 +24103,13 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" t="s" s="2">
@@ -24217,13 +24208,13 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" t="s" s="2">
@@ -24324,13 +24315,13 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" t="s" s="2">
@@ -24431,13 +24422,13 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" t="s" s="2">
@@ -24463,10 +24454,10 @@
         <v>227</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="N192" t="s" s="2">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="O192" s="2"/>
       <c r="P192" s="2"/>
@@ -24517,7 +24508,7 @@
         <v>23</v>
       </c>
       <c r="AG192" t="s" s="2">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="AH192" t="s" s="2">
         <v>85</v>
@@ -24534,13 +24525,13 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" t="s" s="2">
@@ -24569,10 +24560,10 @@
         <v>232</v>
       </c>
       <c r="N193" t="s" s="2">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="O193" t="s" s="2">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="P193" s="2"/>
       <c r="Q193" t="s" s="2">
@@ -24622,7 +24613,7 @@
         <v>23</v>
       </c>
       <c r="AG193" t="s" s="2">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="AH193" t="s" s="2">
         <v>77</v>
@@ -24639,13 +24630,13 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" t="s" s="2">
@@ -24671,13 +24662,13 @@
         <v>239</v>
       </c>
       <c r="M194" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="N194" t="s" s="2">
+        <v>782</v>
+      </c>
+      <c r="O194" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="N194" t="s" s="2">
-        <v>784</v>
-      </c>
-      <c r="O194" t="s" s="2">
-        <v>785</v>
       </c>
       <c r="P194" s="2"/>
       <c r="Q194" t="s" s="2">
@@ -24727,7 +24718,7 @@
         <v>23</v>
       </c>
       <c r="AG194" t="s" s="2">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="AH194" t="s" s="2">
         <v>77</v>
@@ -24744,13 +24735,13 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" t="s" s="2">
@@ -24776,7 +24767,7 @@
         <v>244</v>
       </c>
       <c r="M195" t="s" s="2">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="N195" t="s" s="2">
         <v>246</v>
@@ -24830,7 +24821,7 @@
         <v>23</v>
       </c>
       <c r="AG195" t="s" s="2">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="AH195" t="s" s="2">
         <v>77</v>
@@ -24847,13 +24838,13 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" t="s" s="2">
@@ -24879,10 +24870,10 @@
         <v>249</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="N196" t="s" s="2">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="O196" s="2"/>
       <c r="P196" s="2"/>
@@ -24933,7 +24924,7 @@
         <v>23</v>
       </c>
       <c r="AG196" t="s" s="2">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="AH196" t="s" s="2">
         <v>77</v>
@@ -24950,13 +24941,13 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" t="s" s="2">
@@ -24982,10 +24973,10 @@
         <v>263</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="N197" t="s" s="2">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="O197" s="2"/>
       <c r="P197" s="2"/>
@@ -25036,7 +25027,7 @@
         <v>23</v>
       </c>
       <c r="AG197" t="s" s="2">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="AH197" t="s" s="2">
         <v>77</v>
@@ -25053,13 +25044,13 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" t="s" s="2">
@@ -25156,13 +25147,13 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" t="s" s="2">
@@ -25261,13 +25252,13 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" t="s" s="2">
@@ -25368,13 +25359,13 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" t="s" s="2">
@@ -25400,14 +25391,14 @@
         <v>160</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="N201" t="s" s="2">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="O201" s="2"/>
       <c r="P201" t="s" s="2">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="Q201" t="s" s="2">
         <v>23</v>
@@ -25435,10 +25426,10 @@
         <v>199</v>
       </c>
       <c r="Z201" t="s" s="2">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="AA201" t="s" s="2">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="AB201" t="s" s="2">
         <v>23</v>
@@ -25456,7 +25447,7 @@
         <v>23</v>
       </c>
       <c r="AG201" t="s" s="2">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="AH201" t="s" s="2">
         <v>77</v>
@@ -25473,13 +25464,13 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" t="s" s="2">
@@ -25502,17 +25493,17 @@
         <v>86</v>
       </c>
       <c r="L202" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="M202" t="s" s="2">
+        <v>803</v>
+      </c>
+      <c r="N202" t="s" s="2">
         <v>804</v>
-      </c>
-      <c r="M202" t="s" s="2">
-        <v>805</v>
-      </c>
-      <c r="N202" t="s" s="2">
-        <v>806</v>
       </c>
       <c r="O202" s="2"/>
       <c r="P202" t="s" s="2">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="Q202" t="s" s="2">
         <v>23</v>
@@ -25561,7 +25552,7 @@
         <v>23</v>
       </c>
       <c r="AG202" t="s" s="2">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="AH202" t="s" s="2">
         <v>85</v>
@@ -25578,13 +25569,13 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" t="s" s="2">
@@ -25607,17 +25598,17 @@
         <v>23</v>
       </c>
       <c r="L203" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="M203" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="N203" t="s" s="2">
         <v>809</v>
-      </c>
-      <c r="M203" t="s" s="2">
-        <v>810</v>
-      </c>
-      <c r="N203" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="O203" s="2"/>
       <c r="P203" t="s" s="2">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="Q203" t="s" s="2">
         <v>23</v>
@@ -25666,7 +25657,7 @@
         <v>23</v>
       </c>
       <c r="AG203" t="s" s="2">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="AH203" t="s" s="2">
         <v>77</v>
@@ -25683,13 +25674,13 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" t="s" s="2">
@@ -25712,17 +25703,17 @@
         <v>86</v>
       </c>
       <c r="L204" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="M204" t="s" s="2">
+        <v>813</v>
+      </c>
+      <c r="N204" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="M204" t="s" s="2">
-        <v>815</v>
-      </c>
-      <c r="N204" t="s" s="2">
-        <v>816</v>
       </c>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="Q204" t="s" s="2">
         <v>23</v>
@@ -25771,7 +25762,7 @@
         <v>23</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="AH204" t="s" s="2">
         <v>77</v>
@@ -25788,13 +25779,13 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" t="s" s="2">
@@ -25820,13 +25811,13 @@
         <v>160</v>
       </c>
       <c r="M205" t="s" s="2">
+        <v>817</v>
+      </c>
+      <c r="N205" t="s" s="2">
+        <v>818</v>
+      </c>
+      <c r="O205" t="s" s="2">
         <v>819</v>
-      </c>
-      <c r="N205" t="s" s="2">
-        <v>820</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>821</v>
       </c>
       <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
@@ -25855,10 +25846,10 @@
         <v>199</v>
       </c>
       <c r="Z205" t="s" s="2">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="AA205" t="s" s="2">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AB205" t="s" s="2">
         <v>23</v>
@@ -25876,7 +25867,7 @@
         <v>23</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>77</v>
@@ -25893,13 +25884,13 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -25922,16 +25913,16 @@
         <v>86</v>
       </c>
       <c r="L206" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="M206" t="s" s="2">
+        <v>824</v>
+      </c>
+      <c r="N206" t="s" s="2">
         <v>825</v>
       </c>
-      <c r="M206" t="s" s="2">
+      <c r="O206" t="s" s="2">
         <v>826</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>827</v>
-      </c>
-      <c r="O206" t="s" s="2">
-        <v>828</v>
       </c>
       <c r="P206" s="2"/>
       <c r="Q206" t="s" s="2">
@@ -25981,7 +25972,7 @@
         <v>23</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>77</v>
@@ -25998,13 +25989,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -26030,13 +26021,13 @@
         <v>160</v>
       </c>
       <c r="M207" t="s" s="2">
+        <v>828</v>
+      </c>
+      <c r="N207" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="O207" t="s" s="2">
         <v>830</v>
-      </c>
-      <c r="N207" t="s" s="2">
-        <v>831</v>
-      </c>
-      <c r="O207" t="s" s="2">
-        <v>832</v>
       </c>
       <c r="P207" s="2"/>
       <c r="Q207" t="s" s="2">
@@ -26086,7 +26077,7 @@
         <v>23</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>77</v>
@@ -26103,13 +26094,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -26135,13 +26126,13 @@
         <v>160</v>
       </c>
       <c r="M208" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="N208" t="s" s="2">
+        <v>833</v>
+      </c>
+      <c r="O208" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="N208" t="s" s="2">
-        <v>835</v>
-      </c>
-      <c r="O208" t="s" s="2">
-        <v>836</v>
       </c>
       <c r="P208" s="2"/>
       <c r="Q208" t="s" s="2">
@@ -26170,10 +26161,10 @@
         <v>199</v>
       </c>
       <c r="Z208" t="s" s="2">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="AA208" t="s" s="2">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="AB208" t="s" s="2">
         <v>23</v>
@@ -26191,7 +26182,7 @@
         <v>23</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>77</v>
@@ -26208,13 +26199,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -26237,16 +26228,16 @@
         <v>23</v>
       </c>
       <c r="L209" t="s" s="2">
+        <v>838</v>
+      </c>
+      <c r="M209" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="N209" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="O209" t="s" s="2">
         <v>840</v>
-      </c>
-      <c r="M209" t="s" s="2">
-        <v>841</v>
-      </c>
-      <c r="N209" t="s" s="2">
-        <v>842</v>
-      </c>
-      <c r="O209" t="s" s="2">
-        <v>843</v>
       </c>
       <c r="P209" s="2"/>
       <c r="Q209" t="s" s="2">
@@ -26296,7 +26287,7 @@
         <v>23</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>77</v>
@@ -26313,13 +26304,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -26345,13 +26336,13 @@
         <v>160</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="N210" t="s" s="2">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="O210" t="s" s="2">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="P210" s="2"/>
       <c r="Q210" t="s" s="2">
@@ -26380,7 +26371,7 @@
         <v>199</v>
       </c>
       <c r="Z210" t="s" s="2">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="AA210" t="s" s="2">
         <v>387</v>
@@ -26401,7 +26392,7 @@
         <v>23</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>77</v>
@@ -26418,13 +26409,13 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -26447,17 +26438,17 @@
         <v>23</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" t="s" s="2">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="Q211" t="s" s="2">
         <v>23</v>
@@ -26506,7 +26497,7 @@
         <v>23</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="AH211" t="s" s="2">
         <v>77</v>
@@ -26523,13 +26514,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -26555,10 +26546,10 @@
         <v>160</v>
       </c>
       <c r="M212" t="s" s="2">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="N212" t="s" s="2">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" s="2"/>
@@ -26588,10 +26579,10 @@
         <v>199</v>
       </c>
       <c r="Z212" t="s" s="2">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="AA212" t="s" s="2">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="AB212" t="s" s="2">
         <v>23</v>
@@ -26609,7 +26600,7 @@
         <v>23</v>
       </c>
       <c r="AG212" t="s" s="2">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="AH212" t="s" s="2">
         <v>77</v>
@@ -26626,13 +26617,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -26658,10 +26649,10 @@
         <v>258</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="N213" t="s" s="2">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="O213" s="2"/>
       <c r="P213" s="2"/>
@@ -26712,7 +26703,7 @@
         <v>23</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>77</v>
@@ -26729,13 +26720,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -26832,13 +26823,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -26937,13 +26928,13 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -27042,13 +27033,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -27145,13 +27136,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -27248,13 +27239,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -27280,10 +27271,10 @@
         <v>263</v>
       </c>
       <c r="M219" t="s" s="2">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="N219" t="s" s="2">
-        <v>869</v>
+        <v>866</v>
       </c>
       <c r="O219" s="2"/>
       <c r="P219" s="2"/>
@@ -27334,7 +27325,7 @@
         <v>23</v>
       </c>
       <c r="AG219" t="s" s="2">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="AH219" t="s" s="2">
         <v>77</v>
@@ -27351,13 +27342,13 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -27454,13 +27445,13 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
@@ -27559,13 +27550,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
@@ -27666,13 +27657,13 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -27698,10 +27689,10 @@
         <v>160</v>
       </c>
       <c r="M223" t="s" s="2">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="N223" t="s" s="2">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
@@ -27731,10 +27722,10 @@
         <v>109</v>
       </c>
       <c r="Z223" t="s" s="2">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="AA223" t="s" s="2">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="AB223" t="s" s="2">
         <v>23</v>
@@ -27752,7 +27743,7 @@
         <v>23</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>77</v>
@@ -27769,13 +27760,13 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -27798,13 +27789,13 @@
         <v>23</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="M224" t="s" s="2">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="N224" t="s" s="2">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" s="2"/>
@@ -27855,7 +27846,7 @@
         <v>23</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>85</v>
@@ -27872,13 +27863,13 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -27901,19 +27892,19 @@
         <v>23</v>
       </c>
       <c r="L225" t="s" s="2">
+        <v>880</v>
+      </c>
+      <c r="M225" t="s" s="2">
+        <v>881</v>
+      </c>
+      <c r="N225" t="s" s="2">
+        <v>882</v>
+      </c>
+      <c r="O225" t="s" s="2">
         <v>883</v>
       </c>
-      <c r="M225" t="s" s="2">
+      <c r="P225" t="s" s="2">
         <v>884</v>
-      </c>
-      <c r="N225" t="s" s="2">
-        <v>885</v>
-      </c>
-      <c r="O225" t="s" s="2">
-        <v>886</v>
-      </c>
-      <c r="P225" t="s" s="2">
-        <v>887</v>
       </c>
       <c r="Q225" t="s" s="2">
         <v>23</v>
@@ -27962,7 +27953,7 @@
         <v>23</v>
       </c>
       <c r="AG225" t="s" s="2">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="AH225" t="s" s="2">
         <v>77</v>
@@ -27979,13 +27970,13 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -28011,13 +28002,13 @@
         <v>160</v>
       </c>
       <c r="M226" t="s" s="2">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="N226" t="s" s="2">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="O226" t="s" s="2">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="P226" s="2"/>
       <c r="Q226" t="s" s="2">
@@ -28046,10 +28037,10 @@
         <v>199</v>
       </c>
       <c r="Z226" t="s" s="2">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="AA226" t="s" s="2">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="AB226" t="s" s="2">
         <v>23</v>
@@ -28067,7 +28058,7 @@
         <v>23</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>888</v>
+        <v>885</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>77</v>
@@ -28084,7 +28075,7 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B227" t="s" s="2">
         <v>129</v>
@@ -28116,7 +28107,7 @@
         <v>79</v>
       </c>
       <c r="M227" t="s" s="2">
-        <v>896</v>
+        <v>893</v>
       </c>
       <c r="N227" t="s" s="2">
         <v>272</v>
@@ -28187,13 +28178,13 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -28290,13 +28281,13 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -28393,13 +28384,13 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -28425,13 +28416,13 @@
         <v>99</v>
       </c>
       <c r="M230" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N230" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N230" t="s" s="2">
+      <c r="O230" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O230" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P230" s="2"/>
       <c r="Q230" t="s" s="2">
@@ -28439,7 +28430,7 @@
       </c>
       <c r="R230" s="2"/>
       <c r="S230" t="s" s="2">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="T230" t="s" s="2">
         <v>23</v>
@@ -28481,7 +28472,7 @@
         <v>23</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AH230" t="s" s="2">
         <v>85</v>
@@ -28498,13 +28489,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -28530,10 +28521,10 @@
         <v>160</v>
       </c>
       <c r="M231" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N231" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N231" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O231" s="2"/>
       <c r="P231" s="2"/>
@@ -28584,7 +28575,7 @@
         <v>23</v>
       </c>
       <c r="AG231" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AH231" t="s" s="2">
         <v>77</v>
@@ -28601,13 +28592,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -28633,13 +28624,13 @@
         <v>79</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="O232" t="s" s="2">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="P232" s="2"/>
       <c r="Q232" t="s" s="2">
@@ -28689,7 +28680,7 @@
         <v>23</v>
       </c>
       <c r="AG232" t="s" s="2">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="AH232" t="s" s="2">
         <v>77</v>
@@ -28701,18 +28692,18 @@
         <v>140</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>907</v>
+        <v>904</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -28809,13 +28800,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -28914,13 +28905,13 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -28946,13 +28937,13 @@
         <v>203</v>
       </c>
       <c r="M235" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="N235" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="N235" t="s" s="2">
+      <c r="O235" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="O235" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="P235" s="2"/>
       <c r="Q235" t="s" s="2">
@@ -29002,16 +28993,16 @@
         <v>23</v>
       </c>
       <c r="AG235" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="AH235" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI235" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ235" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="AH235" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI235" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ235" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="AK235" t="s" s="2">
         <v>97</v>
@@ -29019,13 +29010,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -29051,13 +29042,13 @@
         <v>99</v>
       </c>
       <c r="M236" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="N236" t="s" s="2">
         <v>685</v>
       </c>
-      <c r="N236" t="s" s="2">
+      <c r="O236" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="P236" s="2"/>
       <c r="Q236" t="s" s="2">
@@ -29086,28 +29077,28 @@
         <v>374</v>
       </c>
       <c r="Z236" t="s" s="2">
+        <v>687</v>
+      </c>
+      <c r="AA236" t="s" s="2">
         <v>688</v>
       </c>
-      <c r="AA236" t="s" s="2">
+      <c r="AB236" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC236" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD236" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE236" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF236" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG236" t="s" s="2">
         <v>689</v>
-      </c>
-      <c r="AB236" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC236" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD236" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE236" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF236" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG236" t="s" s="2">
-        <v>690</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>77</v>
@@ -29124,13 +29115,13 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -29156,13 +29147,13 @@
         <v>154</v>
       </c>
       <c r="M237" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N237" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="N237" t="s" s="2">
+      <c r="O237" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="P237" s="2"/>
       <c r="Q237" t="s" s="2">
@@ -29212,7 +29203,7 @@
         <v>23</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AH237" t="s" s="2">
         <v>77</v>
@@ -29229,13 +29220,13 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" t="s" s="2">
@@ -29261,13 +29252,13 @@
         <v>203</v>
       </c>
       <c r="M238" t="s" s="2">
+        <v>696</v>
+      </c>
+      <c r="N238" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="N238" t="s" s="2">
+      <c r="O238" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="O238" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="P238" s="2"/>
       <c r="Q238" t="s" s="2">
@@ -29317,7 +29308,7 @@
         <v>23</v>
       </c>
       <c r="AG238" t="s" s="2">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="AH238" t="s" s="2">
         <v>77</v>
@@ -29334,7 +29325,7 @@
     </row>
     <row r="239">
       <c r="A239" t="s" s="2">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B239" t="s" s="2">
         <v>129</v>
@@ -29437,13 +29428,13 @@
     </row>
     <row r="240">
       <c r="A240" t="s" s="2">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" t="s" s="2">
@@ -29540,13 +29531,13 @@
     </row>
     <row r="241">
       <c r="A241" t="s" s="2">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" t="s" s="2">
@@ -29643,13 +29634,13 @@
     </row>
     <row r="242">
       <c r="A242" t="s" s="2">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" t="s" s="2">
@@ -29675,13 +29666,13 @@
         <v>99</v>
       </c>
       <c r="M242" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N242" t="s" s="2">
         <v>545</v>
       </c>
-      <c r="N242" t="s" s="2">
+      <c r="O242" t="s" s="2">
         <v>546</v>
-      </c>
-      <c r="O242" t="s" s="2">
-        <v>547</v>
       </c>
       <c r="P242" s="2"/>
       <c r="Q242" t="s" s="2">
@@ -29689,7 +29680,7 @@
       </c>
       <c r="R242" s="2"/>
       <c r="S242" t="s" s="2">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="T242" t="s" s="2">
         <v>23</v>
@@ -29731,7 +29722,7 @@
         <v>23</v>
       </c>
       <c r="AG242" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AH242" t="s" s="2">
         <v>85</v>
@@ -29748,13 +29739,13 @@
     </row>
     <row r="243">
       <c r="A243" t="s" s="2">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" t="s" s="2">
@@ -29780,10 +29771,10 @@
         <v>428</v>
       </c>
       <c r="M243" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N243" t="s" s="2">
         <v>552</v>
-      </c>
-      <c r="N243" t="s" s="2">
-        <v>553</v>
       </c>
       <c r="O243" s="2"/>
       <c r="P243" s="2"/>
@@ -29834,7 +29825,7 @@
         <v>23</v>
       </c>
       <c r="AG243" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="AH243" t="s" s="2">
         <v>77</v>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:28:20+00:00</t>
+    <t>2026-09-08T06:46:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8338" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8067" uniqueCount="899">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:46:13+00:00</t>
+    <t>2026-09-08T10:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1732,7 +1732,7 @@
     <t>Extension.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner) {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reference}
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner)
 </t>
   </si>
   <si>
@@ -2797,43 +2797,6 @@
   </si>
   <si>
     <t>element:AllergyIntolerance.reaction</t>
-  </si>
-  <si>
-    <t>at-elga-ediag-reference</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reference</t>
-  </si>
-  <si>
-    <t>AtEdiagReference</t>
-  </si>
-  <si>
-    <t>AT ELGA e-Diagnose Reference</t>
-  </si>
-  <si>
-    <t>Reference</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Reference</t>
-  </si>
-  <si>
-    <t>AT e-Diagnose Reference</t>
-  </si>
-  <si>
-    <t>A reference from one resource to another.</t>
-  </si>
-  <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
-    <t>Reference.id</t>
-  </si>
-  <si>
-    <t>Reference.extension</t>
   </si>
   <si>
     <t>at-elga-ediag-reported</t>
@@ -2979,7 +2942,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B181"/>
+  <dimension ref="A1:B159"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -4083,7 +4046,7 @@
         <v>10</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>898</v>
+        <v>138</v>
       </c>
     </row>
     <row r="143">
@@ -4091,7 +4054,7 @@
         <v>12</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>13</v>
+        <v>527</v>
       </c>
     </row>
     <row r="144">
@@ -4145,7 +4108,7 @@
         <v>24</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>25</v>
+        <v>139</v>
       </c>
     </row>
     <row r="151">
@@ -4181,7 +4144,7 @@
         <v>32</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>899</v>
+        <v>129</v>
       </c>
     </row>
     <row r="156">
@@ -4189,7 +4152,7 @@
         <v>34</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>900</v>
+        <v>529</v>
       </c>
     </row>
     <row r="157">
@@ -4209,181 +4172,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B159" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="B160" t="s" s="2">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>908</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s" s="2">
-        <v>8</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s" s="2">
-        <v>10</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s" s="2">
-        <v>12</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s" s="2">
-        <v>14</v>
-      </c>
-      <c r="B166" s="2"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="s" s="2">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s" s="2">
-        <v>17</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B169" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s" s="2">
-        <v>19</v>
-      </c>
-      <c r="B170" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="B171" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="B172" t="s" s="2">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s" s="2">
-        <v>26</v>
-      </c>
-      <c r="B173" s="2"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="s" s="2">
-        <v>27</v>
-      </c>
-      <c r="B174" s="2"/>
-    </row>
-    <row r="175">
-      <c r="A175" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B175" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B176" t="s" s="2">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B177" t="s" s="2">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B178" t="s" s="2">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B179" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B180" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s" s="2">
+      <c r="A159" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="B181" t="s" s="2">
-        <v>910</v>
+      <c r="B159" t="s" s="2">
+        <v>898</v>
       </c>
     </row>
   </sheetData>
@@ -4393,7 +4186,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK243"/>
+  <dimension ref="A1:AK236"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="27.57421875" customWidth="true" bestFit="true"/>
@@ -28595,10 +28388,10 @@
         <v>895</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>899</v>
+        <v>129</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>899</v>
+        <v>129</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -28624,14 +28417,12 @@
         <v>79</v>
       </c>
       <c r="M232" t="s" s="2">
-        <v>901</v>
+        <v>138</v>
       </c>
       <c r="N232" t="s" s="2">
-        <v>902</v>
-      </c>
-      <c r="O232" t="s" s="2">
-        <v>903</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="O232" s="2"/>
       <c r="P232" s="2"/>
       <c r="Q232" t="s" s="2">
         <v>23</v>
@@ -28680,7 +28471,7 @@
         <v>23</v>
       </c>
       <c r="AG232" t="s" s="2">
-        <v>899</v>
+        <v>129</v>
       </c>
       <c r="AH232" t="s" s="2">
         <v>77</v>
@@ -28692,7 +28483,7 @@
         <v>140</v>
       </c>
       <c r="AK232" t="s" s="2">
-        <v>904</v>
+        <v>134</v>
       </c>
     </row>
     <row r="233">
@@ -28700,10 +28491,10 @@
         <v>895</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>905</v>
+        <v>534</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>905</v>
+        <v>534</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -28803,21 +28594,21 @@
         <v>895</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>906</v>
+        <v>535</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>906</v>
+        <v>535</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
-        <v>147</v>
+        <v>23</v>
       </c>
       <c r="F234" s="2"/>
       <c r="G234" t="s" s="2">
         <v>77</v>
       </c>
       <c r="H234" t="s" s="2">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I234" t="s" s="2">
         <v>23</v>
@@ -28832,14 +28623,12 @@
         <v>128</v>
       </c>
       <c r="M234" t="s" s="2">
-        <v>208</v>
+        <v>129</v>
       </c>
       <c r="N234" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="O234" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="O234" s="2"/>
       <c r="P234" s="2"/>
       <c r="Q234" t="s" s="2">
         <v>23</v>
@@ -28908,10 +28697,10 @@
         <v>895</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>681</v>
+        <v>547</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>681</v>
+        <v>547</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -28919,10 +28708,10 @@
       </c>
       <c r="F235" s="2"/>
       <c r="G235" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="H235" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="I235" t="s" s="2">
         <v>23</v>
@@ -28931,19 +28720,19 @@
         <v>23</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L235" t="s" s="2">
-        <v>203</v>
+        <v>99</v>
       </c>
       <c r="M235" t="s" s="2">
-        <v>678</v>
+        <v>544</v>
       </c>
       <c r="N235" t="s" s="2">
-        <v>679</v>
+        <v>545</v>
       </c>
       <c r="O235" t="s" s="2">
-        <v>680</v>
+        <v>546</v>
       </c>
       <c r="P235" s="2"/>
       <c r="Q235" t="s" s="2">
@@ -28951,7 +28740,7 @@
       </c>
       <c r="R235" s="2"/>
       <c r="S235" t="s" s="2">
-        <v>23</v>
+        <v>896</v>
       </c>
       <c r="T235" t="s" s="2">
         <v>23</v>
@@ -28993,19 +28782,19 @@
         <v>23</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>681</v>
+        <v>547</v>
       </c>
       <c r="AH235" t="s" s="2">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="AI235" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ235" t="s" s="2">
-        <v>682</v>
+        <v>23</v>
       </c>
       <c r="AK235" t="s" s="2">
-        <v>97</v>
+        <v>23</v>
       </c>
     </row>
     <row r="236">
@@ -29013,10 +28802,10 @@
         <v>895</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>689</v>
+        <v>553</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>689</v>
+        <v>553</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -29036,20 +28825,18 @@
         <v>23</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>86</v>
+        <v>23</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>99</v>
+        <v>428</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>684</v>
+        <v>551</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>685</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>686</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="O236" s="2"/>
       <c r="P236" s="2"/>
       <c r="Q236" t="s" s="2">
         <v>23</v>
@@ -29074,13 +28861,13 @@
         <v>23</v>
       </c>
       <c r="Y236" t="s" s="2">
-        <v>374</v>
+        <v>23</v>
       </c>
       <c r="Z236" t="s" s="2">
-        <v>687</v>
+        <v>23</v>
       </c>
       <c r="AA236" t="s" s="2">
-        <v>688</v>
+        <v>23</v>
       </c>
       <c r="AB236" t="s" s="2">
         <v>23</v>
@@ -29098,7 +28885,7 @@
         <v>23</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>689</v>
+        <v>553</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>77</v>
@@ -29110,733 +28897,6 @@
         <v>23</v>
       </c>
       <c r="AK236" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="237">
-      <c r="A237" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="B237" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="C237" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="D237" s="2"/>
-      <c r="E237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F237" s="2"/>
-      <c r="G237" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H237" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K237" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L237" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="M237" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>692</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="P237" s="2"/>
-      <c r="Q237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R237" s="2"/>
-      <c r="S237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG237" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="AH237" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI237" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ237" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK237" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="238">
-      <c r="A238" t="s" s="2">
-        <v>895</v>
-      </c>
-      <c r="B238" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="C238" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="D238" s="2"/>
-      <c r="E238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F238" s="2"/>
-      <c r="G238" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H238" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K238" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L238" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M238" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="N238" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="O238" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="P238" s="2"/>
-      <c r="Q238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R238" s="2"/>
-      <c r="S238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG238" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AH238" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI238" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ238" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK238" t="s" s="2">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B239" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="C239" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="D239" s="2"/>
-      <c r="E239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F239" s="2"/>
-      <c r="G239" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H239" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="I239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L239" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="M239" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="N239" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O239" s="2"/>
-      <c r="P239" s="2"/>
-      <c r="Q239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R239" s="2"/>
-      <c r="S239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF239" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG239" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="AH239" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI239" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ239" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK239" t="s" s="2">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B240" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="C240" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="D240" s="2"/>
-      <c r="E240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F240" s="2"/>
-      <c r="G240" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H240" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L240" t="s" s="2">
-        <v>203</v>
-      </c>
-      <c r="M240" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="N240" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="O240" s="2"/>
-      <c r="P240" s="2"/>
-      <c r="Q240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R240" s="2"/>
-      <c r="S240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG240" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="AH240" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI240" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ240" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK240" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B241" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="C241" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="D241" s="2"/>
-      <c r="E241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F241" s="2"/>
-      <c r="G241" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H241" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L241" t="s" s="2">
-        <v>128</v>
-      </c>
-      <c r="M241" t="s" s="2">
-        <v>129</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="O241" s="2"/>
-      <c r="P241" s="2"/>
-      <c r="Q241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R241" s="2"/>
-      <c r="S241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC241" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="AD241" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="AE241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF241" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="AG241" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="AH241" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI241" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AJ241" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK241" t="s" s="2">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B242" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="C242" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="D242" s="2"/>
-      <c r="E242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F242" s="2"/>
-      <c r="G242" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="H242" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L242" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="M242" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="N242" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="O242" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="P242" s="2"/>
-      <c r="Q242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R242" s="2"/>
-      <c r="S242" t="s" s="2">
-        <v>908</v>
-      </c>
-      <c r="T242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG242" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="AH242" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AI242" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ242" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK242" t="s" s="2">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" t="s" s="2">
-        <v>907</v>
-      </c>
-      <c r="B243" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="C243" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="D243" s="2"/>
-      <c r="E243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F243" s="2"/>
-      <c r="G243" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H243" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="L243" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="M243" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="N243" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="O243" s="2"/>
-      <c r="P243" s="2"/>
-      <c r="Q243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R243" s="2"/>
-      <c r="S243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG243" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AH243" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI243" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK243" t="s" s="2">
         <v>97</v>
       </c>
     </row>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:19:13+00:00</t>
+    <t>2026-09-08T10:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:46:31+00:00</t>
+    <t>2026-09-08T11:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:50:41+00:00</t>
+    <t>2026-09-08T12:56:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:56:54+00:00</t>
+    <t>2026-09-09T04:29:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T04:29:28+00:00</t>
+    <t>2026-09-09T07:41:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T07:41:46+00:00</t>
+    <t>2026-09-09T08:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T08:03:40+00:00</t>
+    <t>2026-09-09T09:18:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:18:29+00:00</t>
+    <t>2026-09-09T14:48:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:48:33+00:00</t>
+    <t>2026-09-10T08:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T08:40:11+00:00</t>
+    <t>2026-09-10T09:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:01:10+00:00</t>
+    <t>2026-09-10T09:35:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1977,7 +1977,7 @@
     <t>List.source</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|Device)
 </t>
   </si>
   <si>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:35:03+00:00</t>
+    <t>2026-09-10T09:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:50:09+00:00</t>
+    <t>2026-09-10T10:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:02:23+00:00</t>
+    <t>2026-09-10T11:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:15:10+00:00</t>
+    <t>2026-09-10T11:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:24:50+00:00</t>
+    <t>2026-09-10T11:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:47:23+00:00</t>
+    <t>2026-09-10T14:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:22:40+00:00</t>
+    <t>2026-09-11T07:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Diagnose-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:57:50+00:00</t>
+    <t>2026-09-11T08:25:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
